--- a/Car_Wash_Advisory_Companies.xlsx
+++ b/Car_Wash_Advisory_Companies.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="575">
   <si>
     <t>Company Name</t>
   </si>
@@ -1645,6 +1645,12 @@
     <t>https://fullspeedautomotive.com/</t>
   </si>
   <si>
+    <t>Gleaux Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.gleauxcarwash.com/</t>
+  </si>
+  <si>
     <t>Magic Brush Car Wash</t>
   </si>
   <si>
@@ -1682,6 +1688,12 @@
   </si>
   <si>
     <t>https://cleansweepcarwash.com/</t>
+  </si>
+  <si>
+    <t>Luv-A-Wash</t>
+  </si>
+  <si>
+    <t>https://luvawash.com/</t>
   </si>
   <si>
     <t>Peak Shine Car Wash</t>
@@ -9328,19 +9340,17 @@
         <v>544</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="C176" s="2">
-        <v>2021.0</v>
+        <v>2019.0</v>
       </c>
       <c r="D176" s="2">
         <v>5.0</v>
       </c>
-      <c r="E176" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="E176" s="1"/>
       <c r="F176" s="1" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>545</v>
@@ -9370,10 +9380,10 @@
         <v>546</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C177" s="2">
-        <v>2002.0</v>
+        <v>2021.0</v>
       </c>
       <c r="D177" s="2">
         <v>5.0</v>
@@ -9382,7 +9392,7 @@
         <v>29</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>547</v>
@@ -9412,10 +9422,10 @@
         <v>548</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="C178" s="2">
-        <v>2022.0</v>
+        <v>2002.0</v>
       </c>
       <c r="D178" s="2">
         <v>5.0</v>
@@ -9424,10 +9434,10 @@
         <v>29</v>
       </c>
       <c r="F178" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G178" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="G178" s="3" t="s">
-        <v>550</v>
       </c>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
@@ -9451,13 +9461,13 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>189</v>
+        <v>98</v>
       </c>
       <c r="C179" s="2">
-        <v>2017.0</v>
+        <v>2022.0</v>
       </c>
       <c r="D179" s="2">
         <v>5.0</v>
@@ -9466,7 +9476,7 @@
         <v>29</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>189</v>
+        <v>551</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>552</v>
@@ -9496,17 +9506,19 @@
         <v>553</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>33</v>
+        <v>189</v>
       </c>
       <c r="C180" s="2">
-        <v>2018.0</v>
+        <v>2017.0</v>
       </c>
       <c r="D180" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="E180" s="1"/>
+        <v>5.0</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="F180" s="1" t="s">
-        <v>33</v>
+        <v>189</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>554</v>
@@ -9536,19 +9548,17 @@
         <v>555</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>206</v>
+        <v>33</v>
       </c>
       <c r="C181" s="2">
-        <v>1993.0</v>
+        <v>2018.0</v>
       </c>
       <c r="D181" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="E181" s="1"/>
       <c r="F181" s="1" t="s">
-        <v>206</v>
+        <v>33</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>556</v>
@@ -9578,17 +9588,19 @@
         <v>557</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>57</v>
+        <v>206</v>
       </c>
       <c r="C182" s="2">
-        <v>2025.0</v>
+        <v>1993.0</v>
       </c>
       <c r="D182" s="2">
         <v>3.0</v>
       </c>
-      <c r="E182" s="1"/>
+      <c r="E182" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="F182" s="1" t="s">
-        <v>57</v>
+        <v>206</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>558</v>
@@ -9618,17 +9630,17 @@
         <v>559</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>206</v>
+        <v>87</v>
       </c>
       <c r="C183" s="2">
-        <v>2006.0</v>
+        <v>2009.0</v>
       </c>
       <c r="D183" s="2">
         <v>3.0</v>
       </c>
       <c r="E183" s="1"/>
       <c r="F183" s="1" t="s">
-        <v>206</v>
+        <v>87</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>560</v>
@@ -9658,19 +9670,17 @@
         <v>561</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C184" s="2">
-        <v>2018.0</v>
+        <v>2025.0</v>
       </c>
       <c r="D184" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="E184" s="1"/>
       <c r="F184" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>562</v>
@@ -9700,17 +9710,17 @@
         <v>563</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="C185" s="2">
-        <v>2005.0</v>
+        <v>2006.0</v>
       </c>
       <c r="D185" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>564</v>
@@ -9740,20 +9750,22 @@
         <v>565</v>
       </c>
       <c r="B186" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C186" s="2">
+        <v>2018.0</v>
+      </c>
+      <c r="D186" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G186" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="C186" s="2">
-        <v>2003.0</v>
-      </c>
-      <c r="D186" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E186" s="1"/>
-      <c r="F186" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
@@ -9777,21 +9789,23 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="C187" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="C187" s="2">
+        <v>2005.0</v>
+      </c>
       <c r="D187" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E187" s="1"/>
       <c r="F187" s="1" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
@@ -9814,13 +9828,25 @@
       <c r="Z187" s="1"/>
     </row>
     <row r="188">
-      <c r="A188" s="1"/>
-      <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
+      <c r="A188" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C188" s="2">
+        <v>2003.0</v>
+      </c>
+      <c r="D188" s="2">
+        <v>1.0</v>
+      </c>
       <c r="E188" s="1"/>
-      <c r="F188" s="1"/>
-      <c r="G188" s="1"/>
+      <c r="F188" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>571</v>
+      </c>
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
@@ -9842,13 +9868,23 @@
       <c r="Z188" s="1"/>
     </row>
     <row r="189">
-      <c r="A189" s="1"/>
-      <c r="B189" s="1"/>
+      <c r="A189" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>573</v>
+      </c>
       <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
+      <c r="D189" s="2">
+        <v>1.0</v>
+      </c>
       <c r="E189" s="1"/>
-      <c r="F189" s="1"/>
-      <c r="G189" s="1"/>
+      <c r="F189" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>574</v>
+      </c>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
@@ -32764,7 +32800,9 @@
     <hyperlink r:id="rId183" ref="G185"/>
     <hyperlink r:id="rId184" ref="G186"/>
     <hyperlink r:id="rId185" ref="G187"/>
+    <hyperlink r:id="rId186" ref="G188"/>
+    <hyperlink r:id="rId187" ref="G189"/>
   </hyperlinks>
-  <drawing r:id="rId186"/>
+  <drawing r:id="rId188"/>
 </worksheet>
 </file>
--- a/Car_Wash_Advisory_Companies.xlsx
+++ b/Car_Wash_Advisory_Companies.xlsx
@@ -11,11 +11,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="560">
   <si>
     <t>Company Name</t>
   </si>
   <si>
+    <t>Locale ID</t>
+  </si>
+  <si>
     <t>Headquarters</t>
   </si>
   <si>
@@ -37,6 +40,9 @@
     <t>Mister Car Wash</t>
   </si>
   <si>
+    <t>653ad5a6e882f528b3301834</t>
+  </si>
+  <si>
     <t>Arizona</t>
   </si>
   <si>
@@ -64,7 +70,7 @@
     <t>https://www.tidalwaveautospa.com/</t>
   </si>
   <si>
-    <t>Quick Quack Express Car Wash</t>
+    <t>Quick Quack Car Wash</t>
   </si>
   <si>
     <t>California</t>
@@ -1234,15 +1240,6 @@
     <t>https://supercleanmycar.com/</t>
   </si>
   <si>
-    <t>WashX Car Wash</t>
-  </si>
-  <si>
-    <t>Maryland | Delaware</t>
-  </si>
-  <si>
-    <t>https://washx.space/</t>
-  </si>
-  <si>
     <t>Xtreme Auto Wash</t>
   </si>
   <si>
@@ -1486,6 +1483,12 @@
     <t>https://www.speedwashes.com/</t>
   </si>
   <si>
+    <t>TipTop Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.tiptopcarwashes.com/</t>
+  </si>
+  <si>
     <t>Dash Car Wash</t>
   </si>
   <si>
@@ -1528,6 +1531,12 @@
     <t>https://washtopia.com/</t>
   </si>
   <si>
+    <t>The Wave Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.thewavewash.com/</t>
+  </si>
+  <si>
     <t>American Pride Xpress Carwash</t>
   </si>
   <si>
@@ -1678,64 +1687,10 @@
     <t>https://wavesexpresswash.com/</t>
   </si>
   <si>
-    <t>Clean Wheels Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.cleanwheelswash.com/</t>
-  </si>
-  <si>
-    <t>Clean Sweep Car Wash</t>
-  </si>
-  <si>
-    <t>https://cleansweepcarwash.com/</t>
-  </si>
-  <si>
-    <t>Luv-A-Wash</t>
-  </si>
-  <si>
-    <t>https://luvawash.com/</t>
-  </si>
-  <si>
-    <t>Peak Shine Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.thepeakshine.com/</t>
-  </si>
-  <si>
-    <t>Shammy's Auto Wash</t>
-  </si>
-  <si>
-    <t>https://www.shammysautowash.com/</t>
-  </si>
-  <si>
-    <t>Ace Auto Wash</t>
-  </si>
-  <si>
-    <t>https://www.aceautowash.com/</t>
-  </si>
-  <si>
-    <t>In &amp; Out Car Wash</t>
-  </si>
-  <si>
-    <t>https://inoutwash.com/</t>
-  </si>
-  <si>
-    <t>Country Club Auto Spa</t>
-  </si>
-  <si>
-    <t>Las Vegas, NV</t>
-  </si>
-  <si>
-    <t>https://www.countryclubautospa.com/</t>
-  </si>
-  <si>
-    <t>Rocket Shine Car Wash</t>
-  </si>
-  <si>
-    <t>Flroida</t>
-  </si>
-  <si>
-    <t>https://sunandsudscarwashes.com/rocket-shine-car-wash/</t>
+    <t>Fast Trak Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.fasttrakcarwash.com/</t>
   </si>
 </sst>
 </file>
@@ -2031,7 +1986,9 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2053,27 +2010,29 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2">
         <v>1969.0</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>518.0</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -2095,27 +2054,29 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2">
         <v>1999.0</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>308.0</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2137,27 +2098,29 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2">
         <v>2004.0</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>275.0</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2179,27 +2142,29 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2">
         <v>2006.0</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>257.0</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -2221,27 +2186,29 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2">
         <v>2011.0</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>256.0</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -2263,27 +2230,29 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="2">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2">
         <v>2006.0</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>226.0</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -2305,27 +2274,29 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="2">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>213.0</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -2347,27 +2318,29 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="2">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2">
         <v>2004.0</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="2">
         <v>197.0</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -2389,27 +2362,29 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="2">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>154.0</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -2431,27 +2406,29 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2">
         <v>2002.0</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>150.0</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -2473,27 +2450,29 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="2">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2">
         <v>2015.0</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>141.0</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -2515,27 +2494,29 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="2">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="2">
         <v>2018.0</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>127.0</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -2557,27 +2538,29 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="2">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2">
         <v>2020.0</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
         <v>120.0</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -2599,27 +2582,29 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2">
         <v>1993.0</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>112.0</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -2641,27 +2626,29 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="2">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="2">
         <v>2014.0</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>108.0</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -2683,27 +2670,29 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="2">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2">
         <v>2022.0</v>
       </c>
-      <c r="D17" s="2">
+      <c r="E17" s="2">
         <v>104.0</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -2725,27 +2714,29 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="2">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="2">
         <v>1969.0</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="2">
         <v>91.0</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H18" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -2767,27 +2758,29 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" s="2">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="2">
         <v>2010.0</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="2">
         <v>90.0</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H19" s="1"/>
+      <c r="H19" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -2809,27 +2802,29 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="2">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="2">
         <v>2021.0</v>
       </c>
-      <c r="D20" s="2">
+      <c r="E20" s="2">
         <v>83.0</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -2851,27 +2846,29 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2">
         <v>2021.0</v>
       </c>
-      <c r="D21" s="2">
+      <c r="E21" s="2">
         <v>77.0</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G21" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -2893,27 +2890,29 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C22" s="2">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="2">
         <v>1981.0</v>
       </c>
-      <c r="D22" s="2">
+      <c r="E22" s="2">
         <v>71.0</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G22" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2935,27 +2934,29 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="2">
+        <v>9</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="2">
         <v>2015.0</v>
       </c>
-      <c r="D23" s="2">
+      <c r="E23" s="2">
         <v>71.0</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -2977,27 +2978,29 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2">
+        <v>9</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2">
         <v>2016.0</v>
       </c>
-      <c r="D24" s="2">
+      <c r="E24" s="2">
         <v>68.0</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G24" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -3019,27 +3022,29 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="2">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D25" s="2">
+      <c r="E25" s="2">
         <v>64.0</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G25" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="H25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -3061,27 +3066,29 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="2">
+        <v>9</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="2">
         <v>1970.0</v>
       </c>
-      <c r="D26" s="2">
+      <c r="E26" s="2">
         <v>58.0</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -3103,27 +3110,29 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C27" s="2">
+        <v>9</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="2">
         <v>2007.0</v>
       </c>
-      <c r="D27" s="2">
+      <c r="E27" s="2">
         <v>58.0</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H27" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -3145,27 +3154,29 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="2">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="2">
         <v>2015.0</v>
       </c>
-      <c r="D28" s="2">
+      <c r="E28" s="2">
         <v>54.0</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H28" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -3187,27 +3198,29 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="2">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="2">
         <v>1948.0</v>
       </c>
-      <c r="D29" s="2">
+      <c r="E29" s="2">
         <v>50.0</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H29" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -3229,27 +3242,29 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="2">
+        <v>9</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="2">
         <v>2012.0</v>
       </c>
-      <c r="D30" s="2">
+      <c r="E30" s="2">
         <v>50.0</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H30" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -3271,27 +3286,29 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="2">
+        <v>9</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="2">
         <v>1953.0</v>
       </c>
-      <c r="D31" s="2">
+      <c r="E31" s="2">
         <v>49.0</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G31" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -3313,27 +3330,29 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C32" s="2">
+        <v>9</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="2">
         <v>1997.0</v>
       </c>
-      <c r="D32" s="2">
+      <c r="E32" s="2">
         <v>49.0</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F32" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H32" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -3355,27 +3374,29 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" s="2">
+        <v>9</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="2">
         <v>1959.0</v>
       </c>
-      <c r="D33" s="2">
+      <c r="E33" s="2">
         <v>47.0</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H33" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -3397,27 +3418,29 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="2">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="2">
         <v>2009.0</v>
       </c>
-      <c r="D34" s="2">
+      <c r="E34" s="2">
         <v>46.0</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="F34" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G34" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -3439,27 +3462,29 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="2">
+        <v>9</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="2">
         <v>2020.0</v>
       </c>
-      <c r="D35" s="2">
+      <c r="E35" s="2">
         <v>45.0</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G35" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H35" s="1"/>
+      <c r="G35" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -3481,27 +3506,29 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C36" s="2">
+        <v>9</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" s="2">
         <v>1957.0</v>
       </c>
-      <c r="D36" s="2">
+      <c r="E36" s="2">
         <v>45.0</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F36" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H36" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -3523,27 +3550,29 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="2">
+        <v>9</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="2">
         <v>1988.0</v>
       </c>
-      <c r="D37" s="2">
+      <c r="E37" s="2">
         <v>45.0</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="F37" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G37" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="H37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -3565,27 +3594,29 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="2">
+        <v>9</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="2">
         <v>1995.0</v>
       </c>
-      <c r="D38" s="2">
+      <c r="E38" s="2">
         <v>42.0</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G38" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H38" s="1"/>
+      <c r="G38" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -3607,27 +3638,29 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" s="2">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="2">
         <v>2013.0</v>
       </c>
-      <c r="D39" s="2">
+      <c r="E39" s="2">
         <v>42.0</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H39" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -3649,27 +3682,29 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C40" s="2">
+        <v>9</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D40" s="2">
         <v>1976.0</v>
       </c>
-      <c r="D40" s="2">
+      <c r="E40" s="2">
         <v>41.0</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F40" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H40" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -3691,27 +3726,29 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" s="2">
+        <v>9</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="2">
         <v>1948.0</v>
       </c>
-      <c r="D41" s="2">
+      <c r="E41" s="2">
         <v>40.0</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F41" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H41" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>174</v>
+      </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -3733,27 +3770,29 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="2">
+        <v>9</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="2">
         <v>2011.0</v>
       </c>
-      <c r="D42" s="2">
+      <c r="E42" s="2">
         <v>36.0</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F42" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H42" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -3775,27 +3814,29 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="2">
+        <v>9</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" s="2">
         <v>2018.0</v>
       </c>
-      <c r="D43" s="2">
+      <c r="E43" s="2">
         <v>36.0</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F43" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H43" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -3817,27 +3858,29 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C44" s="2">
+        <v>9</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D44" s="2">
         <v>1967.0</v>
       </c>
-      <c r="D44" s="2">
+      <c r="E44" s="2">
         <v>32.0</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F44" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H44" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -3859,27 +3902,29 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C45" s="2">
+        <v>9</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" s="2">
         <v>1986.0</v>
       </c>
-      <c r="D45" s="2">
+      <c r="E45" s="2">
         <v>31.0</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F45" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H45" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -3901,27 +3946,29 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="2">
+        <v>9</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="2">
         <v>2013.0</v>
       </c>
-      <c r="D46" s="2">
+      <c r="E46" s="2">
         <v>30.0</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="F46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="H46" s="1"/>
+        <v>188</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -3943,27 +3990,29 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C47" s="2">
+        <v>9</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D47" s="2">
         <v>2015.0</v>
       </c>
-      <c r="D47" s="2">
+      <c r="E47" s="2">
         <v>30.0</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G47" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H47" s="1"/>
+      <c r="G47" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3985,27 +4034,29 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C48" s="2">
+        <v>9</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="2">
         <v>1970.0</v>
       </c>
-      <c r="D48" s="2">
+      <c r="E48" s="2">
         <v>29.0</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H48" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -4027,27 +4078,29 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C49" s="2">
+        <v>9</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D49" s="2">
         <v>1981.0</v>
       </c>
-      <c r="D49" s="2">
+      <c r="E49" s="2">
         <v>28.0</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G49" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H49" s="1"/>
+      <c r="H49" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -4069,27 +4122,29 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C50" s="2">
+        <v>9</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D50" s="2">
         <v>1965.0</v>
       </c>
-      <c r="D50" s="2">
+      <c r="E50" s="2">
         <v>28.0</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F50" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="H50" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -4111,27 +4166,29 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="2">
+        <v>9</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="2">
         <v>1992.0</v>
       </c>
-      <c r="D51" s="2">
+      <c r="E51" s="2">
         <v>27.0</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H51" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -4153,27 +4210,29 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C52" s="2">
+        <v>9</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D52" s="2">
         <v>2020.0</v>
       </c>
-      <c r="D52" s="2">
+      <c r="E52" s="2">
         <v>26.0</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G52" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H52" s="1"/>
+      <c r="G52" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -4195,27 +4254,29 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" s="2">
+        <v>9</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" s="2">
         <v>2004.0</v>
       </c>
-      <c r="D53" s="2">
+      <c r="E53" s="2">
         <v>26.0</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G53" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="H53" s="1"/>
+      <c r="G53" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -4237,27 +4298,29 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C54" s="2">
+        <v>9</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" s="2">
         <v>2000.0</v>
       </c>
-      <c r="D54" s="2">
+      <c r="E54" s="2">
         <v>25.0</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="G54" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -4279,27 +4342,29 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" s="2">
+        <v>9</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="2">
         <v>2011.0</v>
       </c>
-      <c r="D55" s="2">
+      <c r="E55" s="2">
         <v>25.0</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F55" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="H55" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -4321,27 +4386,29 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="2">
+        <v>9</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" s="2">
         <v>2004.0</v>
       </c>
-      <c r="D56" s="2">
+      <c r="E56" s="2">
         <v>25.0</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="F56" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="H56" s="1"/>
+        <v>224</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -4363,27 +4430,29 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C57" s="2">
+        <v>9</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D57" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D57" s="2">
+      <c r="E57" s="2">
         <v>25.0</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="F57" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G57" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="H57" s="1"/>
+      <c r="G57" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -4405,27 +4474,29 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C58" s="2">
+        <v>9</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="2">
         <v>2013.0</v>
       </c>
-      <c r="D58" s="2">
+      <c r="E58" s="2">
         <v>24.0</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="H58" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -4447,27 +4518,29 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" s="2">
+        <v>9</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" s="2">
         <v>2018.0</v>
       </c>
-      <c r="D59" s="2">
+      <c r="E59" s="2">
         <v>24.0</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H59" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -4489,27 +4562,29 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C60" s="2">
+        <v>9</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="2">
         <v>2021.0</v>
       </c>
-      <c r="D60" s="2">
+      <c r="E60" s="2">
         <v>24.0</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="F60" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G60" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="H60" s="1"/>
+      <c r="G60" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -4531,27 +4606,29 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C61" s="2">
+        <v>9</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" s="2">
         <v>2021.0</v>
       </c>
-      <c r="D61" s="2">
+      <c r="E61" s="2">
         <v>23.0</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="H61" s="1"/>
+        <v>240</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -4573,27 +4650,29 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C62" s="2">
+        <v>9</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" s="2">
         <v>2012.0</v>
       </c>
-      <c r="D62" s="2">
+      <c r="E62" s="2">
         <v>23.0</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H62" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -4615,27 +4694,29 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C63" s="2">
+        <v>9</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D63" s="2">
         <v>1959.0</v>
       </c>
-      <c r="D63" s="2">
+      <c r="E63" s="2">
         <v>23.0</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="F63" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G63" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="H63" s="1"/>
+      <c r="G63" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>249</v>
+      </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -4657,27 +4738,29 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C64" s="2">
+        <v>9</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" s="2">
         <v>1966.0</v>
       </c>
-      <c r="D64" s="2">
+      <c r="E64" s="2">
         <v>23.0</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F64" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="H64" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -4699,27 +4782,29 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C65" s="2">
+        <v>9</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D65" s="2">
         <v>1981.0</v>
       </c>
-      <c r="D65" s="2">
+      <c r="E65" s="2">
         <v>22.0</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="H65" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -4741,27 +4826,29 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C66" s="2">
+        <v>9</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D66" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D66" s="2">
+      <c r="E66" s="2">
         <v>22.0</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H66" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>256</v>
+      </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -4783,27 +4870,29 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="2">
+        <v>9</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D67" s="2">
+      <c r="E67" s="2">
         <v>21.0</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="F67" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G67" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="H67" s="1"/>
+      <c r="G67" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -4825,27 +4914,29 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C68" s="2">
+        <v>9</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D68" s="2">
         <v>2016.0</v>
       </c>
-      <c r="D68" s="2">
+      <c r="E68" s="2">
         <v>21.0</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F68" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H68" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>264</v>
+      </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -4867,27 +4958,29 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C69" s="2">
+        <v>9</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D69" s="2">
         <v>1997.0</v>
       </c>
-      <c r="D69" s="2">
+      <c r="E69" s="2">
         <v>20.0</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F69" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H69" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -4909,27 +5002,29 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C70" s="2">
+        <v>9</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D70" s="2">
         <v>2012.0</v>
       </c>
-      <c r="D70" s="2">
+      <c r="E70" s="2">
         <v>20.0</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F70" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H70" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>270</v>
+      </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -4951,27 +5046,29 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C71" s="2">
+        <v>9</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D71" s="2">
+      <c r="E71" s="2">
         <v>20.0</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="H71" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -4993,27 +5090,29 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" s="2">
+        <v>9</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="2">
         <v>1997.0</v>
       </c>
-      <c r="D72" s="2">
+      <c r="E72" s="2">
         <v>19.0</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="F72" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="H72" s="1"/>
+        <v>275</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -5035,27 +5134,29 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C73" s="2">
+        <v>9</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D73" s="2">
         <v>1960.0</v>
       </c>
-      <c r="D73" s="2">
+      <c r="E73" s="2">
         <v>19.0</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F73" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="H73" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
@@ -5077,27 +5178,29 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C74" s="2">
+        <v>9</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D74" s="2">
         <v>2012.0</v>
       </c>
-      <c r="D74" s="2">
+      <c r="E74" s="2">
         <v>19.0</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F74" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="H74" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
@@ -5119,27 +5222,29 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C75" s="2">
+        <v>9</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D75" s="2">
         <v>1995.0</v>
       </c>
-      <c r="D75" s="2">
+      <c r="E75" s="2">
         <v>19.0</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F75" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="H75" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
@@ -5161,27 +5266,29 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" s="2">
+        <v>9</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D76" s="2">
         <v>2020.0</v>
       </c>
-      <c r="D76" s="2">
+      <c r="E76" s="2">
         <v>18.0</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="F76" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="H76" s="1"/>
+        <v>285</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
@@ -5203,27 +5310,29 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C77" s="2">
+        <v>9</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D77" s="2">
         <v>1951.0</v>
       </c>
-      <c r="D77" s="2">
+      <c r="E77" s="2">
         <v>18.0</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F77" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="H77" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
@@ -5245,27 +5354,29 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C78" s="2">
+        <v>9</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D78" s="2">
         <v>1976.0</v>
       </c>
-      <c r="D78" s="2">
+      <c r="E78" s="2">
         <v>18.0</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F78" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="H78" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>291</v>
+      </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -5287,27 +5398,29 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C79" s="2">
+        <v>9</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="2">
         <v>2018.0</v>
       </c>
-      <c r="D79" s="2">
+      <c r="E79" s="2">
         <v>18.0</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F79" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="H79" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
@@ -5329,27 +5442,29 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C80" s="2">
+        <v>9</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D80" s="2">
         <v>2016.0</v>
       </c>
-      <c r="D80" s="2">
+      <c r="E80" s="2">
         <v>18.0</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="F80" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="H80" s="1"/>
+        <v>296</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -5371,27 +5486,29 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" s="2">
+        <v>9</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="2">
         <v>2021.0</v>
       </c>
-      <c r="D81" s="2">
+      <c r="E81" s="2">
         <v>17.0</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F81" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="H81" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
@@ -5413,27 +5530,29 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C82" s="2">
+        <v>9</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D82" s="2">
+      <c r="E82" s="2">
         <v>17.0</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="H82" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -5455,27 +5574,29 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C83" s="2">
+        <v>9</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" s="2">
         <v>1982.0</v>
       </c>
-      <c r="D83" s="2">
+      <c r="E83" s="2">
         <v>17.0</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F83" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="H83" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
@@ -5497,27 +5618,29 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C84" s="2">
+        <v>9</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" s="2">
         <v>1977.0</v>
       </c>
-      <c r="D84" s="2">
+      <c r="E84" s="2">
         <v>17.0</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F84" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="H84" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
@@ -5539,27 +5662,29 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C85" s="2">
+        <v>9</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D85" s="2">
         <v>2017.0</v>
       </c>
-      <c r="D85" s="2">
+      <c r="E85" s="2">
         <v>17.0</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F85" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="H85" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>308</v>
+      </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
@@ -5581,27 +5706,29 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C86" s="2">
+        <v>9</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="2">
         <v>2015.0</v>
       </c>
-      <c r="D86" s="2">
+      <c r="E86" s="2">
         <v>17.0</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F86" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="H86" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>310</v>
+      </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
@@ -5623,27 +5750,29 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C87" s="2">
+        <v>9</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D87" s="2">
         <v>1995.0</v>
       </c>
-      <c r="D87" s="2">
+      <c r="E87" s="2">
         <v>16.0</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F87" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="H87" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
@@ -5665,27 +5794,29 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C88" s="2">
+        <v>9</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D88" s="2">
         <v>1993.0</v>
       </c>
-      <c r="D88" s="2">
+      <c r="E88" s="2">
         <v>16.0</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F88" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="H88" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>317</v>
+      </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
@@ -5707,27 +5838,29 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C89" s="2">
+        <v>9</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D89" s="2">
         <v>2001.0</v>
       </c>
-      <c r="D89" s="2">
+      <c r="E89" s="2">
         <v>16.0</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F89" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H89" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
@@ -5749,27 +5882,29 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C90" s="2">
+        <v>9</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D90" s="2">
         <v>2013.0</v>
       </c>
-      <c r="D90" s="2">
+      <c r="E90" s="2">
         <v>16.0</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F90" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H90" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
@@ -5791,27 +5926,29 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C91" s="2">
+        <v>9</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D91" s="2">
         <v>1976.0</v>
       </c>
-      <c r="D91" s="2">
+      <c r="E91" s="2">
         <v>16.0</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F91" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H91" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>327</v>
+      </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -5833,27 +5970,29 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C92" s="2">
+        <v>9</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D92" s="2">
         <v>1999.0</v>
       </c>
-      <c r="D92" s="2">
+      <c r="E92" s="2">
         <v>15.0</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F92" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="H92" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
@@ -5875,27 +6014,29 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C93" s="2">
+        <v>9</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D93" s="2">
         <v>2007.0</v>
       </c>
-      <c r="D93" s="2">
+      <c r="E93" s="2">
         <v>15.0</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F93" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="H93" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>333</v>
+      </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
@@ -5917,27 +6058,29 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C94" s="2">
+        <v>9</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D94" s="2">
         <v>2018.0</v>
       </c>
-      <c r="D94" s="2">
+      <c r="E94" s="2">
         <v>15.0</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H94" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>336</v>
+      </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
@@ -5959,27 +6102,29 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C95" s="2">
+        <v>9</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D95" s="2">
         <v>2024.0</v>
       </c>
-      <c r="D95" s="2">
+      <c r="E95" s="2">
         <v>15.0</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="F95" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G95" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="H95" s="1"/>
+      <c r="G95" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
@@ -6001,27 +6146,29 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C96" s="2">
+        <v>9</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D96" s="2">
         <v>2007.0</v>
       </c>
-      <c r="D96" s="2">
+      <c r="E96" s="2">
         <v>14.0</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F96" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="H96" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
@@ -6043,27 +6190,29 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C97" s="2">
+        <v>9</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D97" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D97" s="2">
+      <c r="E97" s="2">
         <v>14.0</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="F97" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G97" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="H97" s="1"/>
+      <c r="G97" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>347</v>
+      </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
@@ -6085,27 +6234,29 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C98" s="2">
+        <v>9</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98" s="2">
         <v>2020.0</v>
       </c>
-      <c r="D98" s="2">
+      <c r="E98" s="2">
         <v>14.0</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F98" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H98" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>350</v>
+      </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
@@ -6127,27 +6278,29 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C99" s="2">
+        <v>9</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D99" s="2">
         <v>1969.0</v>
       </c>
-      <c r="D99" s="2">
+      <c r="E99" s="2">
         <v>14.0</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F99" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H99" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
@@ -6169,27 +6322,29 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C100" s="2">
+        <v>9</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D100" s="2">
         <v>2000.0</v>
       </c>
-      <c r="D100" s="2">
+      <c r="E100" s="2">
         <v>14.0</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F100" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H100" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
@@ -6211,27 +6366,29 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C101" s="2">
+        <v>9</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D101" s="2">
         <v>1987.0</v>
       </c>
-      <c r="D101" s="2">
+      <c r="E101" s="2">
         <v>14.0</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="H101" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
@@ -6253,25 +6410,27 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C102" s="2">
+        <v>9</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D102" s="2">
         <v>2008.0</v>
       </c>
-      <c r="D102" s="2">
+      <c r="E102" s="2">
         <v>14.0</v>
       </c>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="H102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
@@ -6293,27 +6452,29 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C103" s="2">
+        <v>9</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D103" s="2">
         <v>1994.0</v>
       </c>
-      <c r="D103" s="2">
+      <c r="E103" s="2">
         <v>14.0</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F103" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="H103" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
@@ -6335,27 +6496,29 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C104" s="2">
+        <v>9</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D104" s="2">
         <v>1997.0</v>
       </c>
-      <c r="D104" s="2">
+      <c r="E104" s="2">
         <v>13.0</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="F104" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="G104" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="H104" s="1"/>
+      <c r="G104" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>369</v>
+      </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
@@ -6377,27 +6540,29 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="C105" s="2">
+        <v>9</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D105" s="2">
         <v>1981.0</v>
       </c>
-      <c r="D105" s="2">
+      <c r="E105" s="2">
         <v>13.0</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F105" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="H105" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
@@ -6419,25 +6584,27 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C106" s="2">
+        <v>9</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D106" s="2">
         <v>2013.0</v>
       </c>
-      <c r="D106" s="2">
+      <c r="E106" s="2">
         <v>13.0</v>
       </c>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="H106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>377</v>
+      </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
@@ -6459,27 +6626,29 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C107" s="2">
+        <v>9</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D107" s="2">
         <v>2015.0</v>
       </c>
-      <c r="D107" s="2">
+      <c r="E107" s="2">
         <v>13.0</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F107" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="H107" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>379</v>
+      </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
@@ -6501,27 +6670,29 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C108" s="2">
+        <v>9</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="2">
         <v>1980.0</v>
       </c>
-      <c r="D108" s="2">
+      <c r="E108" s="2">
         <v>13.0</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F108" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="H108" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>381</v>
+      </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
@@ -6543,27 +6714,29 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C109" s="2">
+        <v>9</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D109" s="2">
         <v>1983.0</v>
       </c>
-      <c r="D109" s="2">
+      <c r="E109" s="2">
         <v>13.0</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F109" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="H109" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>383</v>
+      </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
@@ -6585,27 +6758,29 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C110" s="2">
+        <v>9</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D110" s="2">
         <v>2020.0</v>
       </c>
-      <c r="D110" s="2">
+      <c r="E110" s="2">
         <v>13.0</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F110" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="H110" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>385</v>
+      </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
@@ -6627,27 +6802,29 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C111" s="2">
+        <v>9</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" s="2">
         <v>2021.0</v>
       </c>
-      <c r="D111" s="2">
+      <c r="E111" s="2">
         <v>13.0</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="F111" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="G111" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="H111" s="1"/>
+      <c r="G111" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>389</v>
+      </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
@@ -6669,27 +6846,29 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="2">
+        <v>9</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D112" s="2">
         <v>2019.0</v>
       </c>
-      <c r="D112" s="2">
+      <c r="E112" s="2">
         <v>13.0</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="F112" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="G112" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="H112" s="1"/>
+      <c r="G112" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>393</v>
+      </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
@@ -6711,27 +6890,29 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C113" s="2">
+        <v>9</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D113" s="2">
         <v>2010.0</v>
       </c>
-      <c r="D113" s="2">
+      <c r="E113" s="2">
         <v>13.0</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F113" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="H113" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>396</v>
+      </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
@@ -6753,27 +6934,29 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C114" s="2">
+        <v>9</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D114" s="2">
         <v>2017.0</v>
       </c>
-      <c r="D114" s="2">
+      <c r="E114" s="2">
         <v>12.0</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F114" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="H114" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>398</v>
+      </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
@@ -6795,27 +6978,29 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C115" s="2">
+        <v>9</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D115" s="2">
         <v>2023.0</v>
       </c>
-      <c r="D115" s="2">
+      <c r="E115" s="2">
         <v>12.0</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F115" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="H115" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>401</v>
+      </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
@@ -6837,27 +7022,29 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C116" s="2">
+        <v>9</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D116" s="2">
         <v>2017.0</v>
       </c>
-      <c r="D116" s="2">
+      <c r="E116" s="2">
         <v>12.0</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F116" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="H116" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>403</v>
+      </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
@@ -6879,27 +7066,29 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C117" s="2">
+        <v>9</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D117" s="2">
         <v>2013.0</v>
       </c>
-      <c r="D117" s="2">
+      <c r="E117" s="2">
         <v>12.0</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F117" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="H117" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>406</v>
+      </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
       <c r="K117" s="1"/>
@@ -6921,27 +7110,29 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C118" s="2">
+        <v>9</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D118" s="2">
         <v>1990.0</v>
       </c>
-      <c r="D118" s="2">
+      <c r="E118" s="2">
         <v>12.0</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F118" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G118" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="H118" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>408</v>
+      </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
@@ -6963,25 +7154,25 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C119" s="2">
-        <v>2023.0</v>
+        <v>9</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="D119" s="2">
+        <v>2006.0</v>
+      </c>
+      <c r="E119" s="2">
         <v>12.0</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F119" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>409</v>
+        <v>31</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -7008,22 +7199,26 @@
         <v>410</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C120" s="2">
-        <v>2006.0</v>
+        <v>9</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D120" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>29</v>
+        <v>1964.0</v>
+      </c>
+      <c r="E120" s="2">
+        <v>11.0</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="G120" s="1"/>
-      <c r="H120" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>411</v>
+      </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
@@ -7045,27 +7240,29 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C121" s="2">
-        <v>1964.0</v>
+        <v>9</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D121" s="2">
+        <v>1993.0</v>
+      </c>
+      <c r="E121" s="2">
         <v>11.0</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F121" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G121" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="H121" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>413</v>
+      </c>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
@@ -7087,27 +7284,29 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C122" s="2">
-        <v>1993.0</v>
+        <v>9</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="D122" s="2">
+        <v>1958.0</v>
+      </c>
+      <c r="E122" s="2">
         <v>11.0</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F122" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="H122" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>416</v>
+      </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
@@ -7129,27 +7328,29 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C123" s="2">
-        <v>1958.0</v>
+        <v>9</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D123" s="2">
+        <v>1950.0</v>
+      </c>
+      <c r="E123" s="2">
         <v>11.0</v>
       </c>
-      <c r="E123" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F123" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="H123" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>418</v>
+      </c>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
@@ -7171,27 +7372,29 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C124" s="2">
-        <v>1950.0</v>
+        <v>9</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>420</v>
       </c>
       <c r="D124" s="2">
+        <v>1947.0</v>
+      </c>
+      <c r="E124" s="2">
         <v>11.0</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F124" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="H124" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>421</v>
+      </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
@@ -7213,27 +7416,29 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C125" s="2">
-        <v>1947.0</v>
+        <v>9</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="D125" s="2">
+        <v>2007.0</v>
+      </c>
+      <c r="E125" s="2">
         <v>11.0</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F125" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="G125" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="H125" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>424</v>
+      </c>
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1"/>
@@ -7255,27 +7460,29 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C126" s="2">
-        <v>2007.0</v>
+        <v>9</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D126" s="2">
+        <v>2011.0</v>
+      </c>
+      <c r="E126" s="2">
         <v>11.0</v>
       </c>
-      <c r="E126" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F126" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="H126" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>427</v>
+      </c>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
@@ -7297,27 +7504,27 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C127" s="2">
-        <v>2011.0</v>
-      </c>
-      <c r="D127" s="2">
+        <v>9</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D127" s="1"/>
+      <c r="E127" s="2">
         <v>11.0</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F127" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="H127" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>430</v>
+      </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
@@ -7339,25 +7546,29 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C128" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="D128" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>29</v>
+        <v>2022.0</v>
+      </c>
+      <c r="E128" s="2">
+        <v>10.0</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="H128" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>432</v>
+      </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
@@ -7379,27 +7590,29 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" s="2">
-        <v>2022.0</v>
+        <v>9</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D129" s="2">
+        <v>2016.0</v>
+      </c>
+      <c r="E129" s="2">
         <v>10.0</v>
       </c>
-      <c r="E129" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F129" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="H129" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>435</v>
+      </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
@@ -7421,27 +7634,29 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C130" s="2">
-        <v>2016.0</v>
+        <v>9</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D130" s="2">
+        <v>2018.0</v>
+      </c>
+      <c r="E130" s="2">
         <v>10.0</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F130" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="H130" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>438</v>
+      </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
@@ -7463,27 +7678,29 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C131" s="2">
-        <v>2018.0</v>
+        <v>9</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D131" s="2">
+        <v>2019.0</v>
+      </c>
+      <c r="E131" s="2">
         <v>10.0</v>
       </c>
-      <c r="E131" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F131" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="G131" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="H131" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>440</v>
+      </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
       <c r="K131" s="1"/>
@@ -7505,27 +7722,29 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C132" s="2">
-        <v>2019.0</v>
+        <v>9</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D132" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="E132" s="2">
         <v>10.0</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F132" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G132" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="H132" s="1"/>
+        <v>442</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>444</v>
+      </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
@@ -7547,27 +7766,29 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C133" s="2">
-        <v>2022.0</v>
+        <v>9</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="D133" s="2">
+        <v>2018.0</v>
+      </c>
+      <c r="E133" s="2">
         <v>10.0</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="F133" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="H133" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>447</v>
+      </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
       <c r="K133" s="1"/>
@@ -7589,27 +7810,29 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C134" s="2">
-        <v>2018.0</v>
+        <v>9</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="D134" s="2">
+        <v>2015.0</v>
+      </c>
+      <c r="E134" s="2">
         <v>10.0</v>
       </c>
-      <c r="E134" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F134" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="H134" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>450</v>
+      </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
       <c r="K134" s="1"/>
@@ -7631,27 +7854,29 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C135" s="2">
-        <v>2015.0</v>
+        <v>9</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D135" s="2">
+        <v>2005.0</v>
+      </c>
+      <c r="E135" s="2">
         <v>10.0</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F135" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="G135" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="H135" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>452</v>
+      </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
@@ -7673,27 +7898,29 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C136" s="2">
-        <v>2005.0</v>
+        <v>9</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="D136" s="2">
+        <v>1999.0</v>
+      </c>
+      <c r="E136" s="2">
         <v>10.0</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F136" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="H136" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>455</v>
+      </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
       <c r="K136" s="1"/>
@@ -7715,27 +7942,29 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C137" s="2">
-        <v>1999.0</v>
+        <v>9</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D137" s="2">
+        <v>2019.0</v>
+      </c>
+      <c r="E137" s="2">
         <v>10.0</v>
       </c>
-      <c r="E137" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F137" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="G137" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="H137" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>457</v>
+      </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
       <c r="K137" s="1"/>
@@ -7757,27 +7986,29 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C138" s="2">
-        <v>2019.0</v>
+        <v>9</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D138" s="2">
+        <v>2009.0</v>
+      </c>
+      <c r="E138" s="2">
         <v>10.0</v>
       </c>
-      <c r="E138" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F138" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G138" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="H138" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>459</v>
+      </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
       <c r="K138" s="1"/>
@@ -7799,27 +8030,29 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C139" s="2">
-        <v>2009.0</v>
+        <v>9</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="D139" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>29</v>
+        <v>2002.0</v>
+      </c>
+      <c r="E139" s="2">
+        <v>9.0</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G139" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="H139" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>461</v>
+      </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
       <c r="K139" s="1"/>
@@ -7841,27 +8074,29 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C140" s="2">
-        <v>2002.0</v>
+        <v>9</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="D140" s="2">
+        <v>1951.0</v>
+      </c>
+      <c r="E140" s="2">
         <v>9.0</v>
       </c>
-      <c r="E140" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F140" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G140" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="H140" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>463</v>
+      </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
@@ -7883,27 +8118,29 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C141" s="2">
-        <v>1951.0</v>
+        <v>9</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D141" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="E141" s="2">
         <v>9.0</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F141" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="H141" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>465</v>
+      </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
@@ -7925,27 +8162,29 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C142" s="2">
-        <v>2021.0</v>
+        <v>9</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="D142" s="2">
+        <v>1998.0</v>
+      </c>
+      <c r="E142" s="2">
         <v>9.0</v>
       </c>
-      <c r="E142" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F142" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="H142" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>468</v>
+      </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
@@ -7967,27 +8206,29 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C143" s="2">
-        <v>1998.0</v>
+        <v>9</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="D143" s="2">
+        <v>2003.0</v>
+      </c>
+      <c r="E143" s="2">
         <v>9.0</v>
       </c>
-      <c r="E143" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F143" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="G143" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="H143" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>470</v>
+      </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
@@ -8009,27 +8250,29 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C144" s="2">
-        <v>2003.0</v>
+        <v>9</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="D144" s="2">
+        <v>2019.0</v>
+      </c>
+      <c r="E144" s="2">
         <v>9.0</v>
       </c>
-      <c r="E144" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F144" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G144" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="H144" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>472</v>
+      </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
@@ -8051,27 +8294,27 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C145" s="2">
-        <v>2019.0</v>
+        <v>9</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D145" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="E145" s="2">
         <v>9.0</v>
       </c>
-      <c r="E145" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G145" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="H145" s="1"/>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>475</v>
+      </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
@@ -8093,25 +8336,29 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C146" s="2">
+        <v>9</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D146" s="2">
         <v>2021.0</v>
       </c>
-      <c r="D146" s="2">
+      <c r="E146" s="2">
         <v>9.0</v>
       </c>
-      <c r="E146" s="1"/>
       <c r="F146" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="H146" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>478</v>
+      </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
       <c r="K146" s="1"/>
@@ -8133,27 +8380,29 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C147" s="2">
-        <v>2021.0</v>
+        <v>9</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="D147" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>29</v>
+        <v>1998.0</v>
+      </c>
+      <c r="E147" s="2">
+        <v>8.0</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="H147" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>480</v>
+      </c>
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
@@ -8175,27 +8424,29 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C148" s="2">
-        <v>1998.0</v>
+        <v>9</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D148" s="2">
+        <v>2016.0</v>
+      </c>
+      <c r="E148" s="2">
         <v>8.0</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F148" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G148" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="H148" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>483</v>
+      </c>
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
       <c r="K148" s="1"/>
@@ -8217,27 +8468,29 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C149" s="2">
-        <v>2016.0</v>
+        <v>9</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D149" s="2">
+        <v>2004.0</v>
+      </c>
+      <c r="E149" s="2">
         <v>8.0</v>
       </c>
-      <c r="E149" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F149" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="G149" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="H149" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>485</v>
+      </c>
       <c r="I149" s="1"/>
       <c r="J149" s="1"/>
       <c r="K149" s="1"/>
@@ -8259,27 +8512,29 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C150" s="2">
-        <v>2004.0</v>
+        <v>9</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D150" s="2">
+        <v>2017.0</v>
+      </c>
+      <c r="E150" s="2">
         <v>8.0</v>
       </c>
-      <c r="E150" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F150" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G150" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="H150" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>487</v>
+      </c>
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
       <c r="K150" s="1"/>
@@ -8301,27 +8556,29 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C151" s="2">
-        <v>2017.0</v>
+        <v>9</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D151" s="2">
+        <v>2014.0</v>
+      </c>
+      <c r="E151" s="2">
         <v>8.0</v>
       </c>
-      <c r="E151" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F151" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G151" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="H151" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>489</v>
+      </c>
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
@@ -8343,27 +8600,27 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C152" s="2">
-        <v>2014.0</v>
+        <v>9</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="D152" s="2">
+        <v>2024.0</v>
+      </c>
+      <c r="E152" s="2">
         <v>8.0</v>
       </c>
-      <c r="E152" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="H152" s="1"/>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>491</v>
+      </c>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
       <c r="K152" s="1"/>
@@ -8385,20 +8642,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="B153" s="1"/>
-      <c r="C153" s="2">
+        <v>492</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="1"/>
+      <c r="D153" s="2">
         <v>2021.0</v>
       </c>
-      <c r="D153" s="2">
+      <c r="E153" s="2">
         <v>7.0</v>
       </c>
-      <c r="E153" s="1"/>
-      <c r="F153" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="G153" s="1"/>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1" t="s">
+        <v>493</v>
+      </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
@@ -8421,27 +8680,29 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C154" s="2">
+        <v>9</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D154" s="2">
         <v>2023.0</v>
       </c>
-      <c r="D154" s="2">
+      <c r="E154" s="2">
         <v>7.0</v>
       </c>
-      <c r="E154" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F154" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="H154" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>495</v>
+      </c>
       <c r="I154" s="1"/>
       <c r="J154" s="1"/>
       <c r="K154" s="1"/>
@@ -8463,25 +8724,27 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C155" s="2">
+        <v>9</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="D155" s="2">
         <v>2009.0</v>
       </c>
-      <c r="D155" s="2">
+      <c r="E155" s="2">
         <v>7.0</v>
       </c>
-      <c r="E155" s="1"/>
-      <c r="F155" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="G155" s="3" t="s">
+      <c r="F155" s="1"/>
+      <c r="G155" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="H155" s="1"/>
+      <c r="H155" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
       <c r="K155" s="1"/>
@@ -8503,27 +8766,29 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C156" s="2">
+        <v>9</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D156" s="2">
         <v>2010.0</v>
       </c>
-      <c r="D156" s="2">
+      <c r="E156" s="2">
         <v>7.0</v>
       </c>
-      <c r="E156" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="F156" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G156" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="H156" s="1"/>
+      <c r="G156" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
       <c r="K156" s="1"/>
@@ -8545,27 +8810,29 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C157" s="2">
+        <v>9</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D157" s="2">
         <v>2018.0</v>
       </c>
-      <c r="D157" s="2">
+      <c r="E157" s="2">
         <v>7.0</v>
       </c>
-      <c r="E157" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F157" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="H157" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>503</v>
+      </c>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
       <c r="K157" s="1"/>
@@ -8587,27 +8854,29 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C158" s="2">
+        <v>9</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" s="2">
         <v>2016.0</v>
       </c>
-      <c r="D158" s="2">
+      <c r="E158" s="2">
         <v>7.0</v>
       </c>
-      <c r="E158" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F158" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="H158" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>505</v>
+      </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
       <c r="K158" s="1"/>
@@ -8629,27 +8898,27 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C159" s="2">
-        <v>1981.0</v>
+        <v>9</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="D159" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="H159" s="1"/>
+        <v>2005.0</v>
+      </c>
+      <c r="E159" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
@@ -8671,25 +8940,29 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C160" s="2">
-        <v>1964.0</v>
+        <v>9</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D160" s="2">
+        <v>1981.0</v>
+      </c>
+      <c r="E160" s="2">
         <v>6.0</v>
       </c>
-      <c r="E160" s="1"/>
       <c r="F160" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G160" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="H160" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>509</v>
+      </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
       <c r="K160" s="1"/>
@@ -8711,27 +8984,27 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C161" s="2">
-        <v>2009.0</v>
+        <v>9</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="D161" s="2">
+        <v>1964.0</v>
+      </c>
+      <c r="E161" s="2">
         <v>6.0</v>
       </c>
-      <c r="E161" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="H161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>511</v>
+      </c>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
       <c r="K161" s="1"/>
@@ -8753,27 +9026,29 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C162" s="2">
-        <v>2018.0</v>
+        <v>9</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="D162" s="2">
+        <v>2009.0</v>
+      </c>
+      <c r="E162" s="2">
         <v>6.0</v>
       </c>
-      <c r="E162" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F162" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="H162" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>513</v>
+      </c>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
       <c r="K162" s="1"/>
@@ -8795,27 +9070,29 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C163" s="2">
-        <v>1966.0</v>
+        <v>9</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D163" s="2">
+        <v>2018.0</v>
+      </c>
+      <c r="E163" s="2">
         <v>6.0</v>
       </c>
-      <c r="E163" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F163" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="G163" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H163" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="H163" s="1"/>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
       <c r="K163" s="1"/>
@@ -8840,24 +9117,26 @@
         <v>516</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C164" s="2">
-        <v>2010.0</v>
+        <v>9</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D164" s="2">
+        <v>1966.0</v>
+      </c>
+      <c r="E164" s="2">
         <v>6.0</v>
       </c>
-      <c r="E164" s="1" t="s">
+      <c r="F164" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G164" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="F164" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="G164" s="3" t="s">
+      <c r="H164" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="H164" s="1"/>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
@@ -8882,24 +9161,26 @@
         <v>519</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C165" s="2">
+        <v>9</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D165" s="2">
         <v>2010.0</v>
       </c>
-      <c r="D165" s="2">
+      <c r="E165" s="2">
         <v>6.0</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="G165" s="3" t="s">
+      <c r="G165" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H165" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="H165" s="1"/>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
@@ -8924,24 +9205,26 @@
         <v>522</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C166" s="2">
-        <v>2023.0</v>
+        <v>9</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="D166" s="2">
+        <v>2010.0</v>
+      </c>
+      <c r="E166" s="2">
         <v>6.0</v>
       </c>
-      <c r="E166" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F166" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G166" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G166" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H166" s="1"/>
+      <c r="H166" s="3" t="s">
+        <v>524</v>
+      </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
       <c r="K166" s="1"/>
@@ -8963,27 +9246,29 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C167" s="2">
-        <v>1985.0</v>
+        <v>9</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="D167" s="2">
+        <v>2023.0</v>
+      </c>
+      <c r="E167" s="2">
         <v>6.0</v>
       </c>
-      <c r="E167" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F167" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="H167" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>526</v>
+      </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
@@ -9005,27 +9290,29 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C168" s="2">
-        <v>2018.0</v>
+        <v>9</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="D168" s="2">
+        <v>1985.0</v>
+      </c>
+      <c r="E168" s="2">
         <v>6.0</v>
       </c>
-      <c r="E168" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F168" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G168" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="H168" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>528</v>
+      </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
@@ -9047,27 +9334,29 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C169" s="2">
-        <v>2019.0</v>
+        <v>9</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="D169" s="2">
+        <v>2018.0</v>
+      </c>
+      <c r="E169" s="2">
         <v>6.0</v>
       </c>
-      <c r="E169" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F169" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="H169" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>530</v>
+      </c>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
@@ -9089,27 +9378,29 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C170" s="2">
-        <v>2006.0</v>
+        <v>9</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D170" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>29</v>
+        <v>2019.0</v>
+      </c>
+      <c r="E170" s="2">
+        <v>6.0</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G170" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H170" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="H170" s="1"/>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
       <c r="K170" s="1"/>
@@ -9134,22 +9425,26 @@
         <v>533</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C171" s="2">
-        <v>1981.0</v>
+        <v>9</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>534</v>
       </c>
       <c r="D171" s="2">
+        <v>2006.0</v>
+      </c>
+      <c r="E171" s="2">
         <v>5.0</v>
       </c>
-      <c r="E171" s="1"/>
       <c r="F171" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G171" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G171" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="H171" s="1"/>
+      <c r="H171" s="3" t="s">
+        <v>535</v>
+      </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
       <c r="K171" s="1"/>
@@ -9171,27 +9466,27 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C172" s="2">
-        <v>2012.0</v>
+        <v>9</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="D172" s="2">
+        <v>1981.0</v>
+      </c>
+      <c r="E172" s="2">
         <v>5.0</v>
       </c>
-      <c r="E172" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="H172" s="1"/>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>537</v>
+      </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
       <c r="K172" s="1"/>
@@ -9213,25 +9508,29 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C173" s="2">
-        <v>2016.0</v>
+        <v>9</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D173" s="2">
+        <v>2012.0</v>
+      </c>
+      <c r="E173" s="2">
         <v>5.0</v>
       </c>
-      <c r="E173" s="1"/>
       <c r="F173" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="H173" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>539</v>
+      </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
@@ -9253,27 +9552,27 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C174" s="2">
-        <v>2018.0</v>
+        <v>9</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="D174" s="2">
+        <v>2016.0</v>
+      </c>
+      <c r="E174" s="2">
         <v>5.0</v>
       </c>
-      <c r="E174" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="H174" s="1"/>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>541</v>
+      </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
@@ -9295,27 +9594,29 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C175" s="2">
-        <v>1978.0</v>
+        <v>9</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="D175" s="2">
+        <v>2018.0</v>
+      </c>
+      <c r="E175" s="2">
         <v>5.0</v>
       </c>
-      <c r="E175" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F175" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="G175" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H175" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="H175" s="1"/>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
@@ -9340,22 +9641,26 @@
         <v>544</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C176" s="2">
-        <v>2019.0</v>
+        <v>9</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D176" s="2">
+        <v>1978.0</v>
+      </c>
+      <c r="E176" s="2">
         <v>5.0</v>
       </c>
-      <c r="E176" s="1"/>
       <c r="F176" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G176" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G176" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="H176" s="1"/>
+      <c r="H176" s="3" t="s">
+        <v>546</v>
+      </c>
       <c r="I176" s="1"/>
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
@@ -9377,27 +9682,27 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C177" s="2">
-        <v>2021.0</v>
+        <v>9</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D177" s="2">
+        <v>2019.0</v>
+      </c>
+      <c r="E177" s="2">
         <v>5.0</v>
       </c>
-      <c r="E177" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G177" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="H177" s="1"/>
+      <c r="F177" s="1"/>
+      <c r="G177" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>548</v>
+      </c>
       <c r="I177" s="1"/>
       <c r="J177" s="1"/>
       <c r="K177" s="1"/>
@@ -9419,27 +9724,29 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C178" s="2">
-        <v>2002.0</v>
+        <v>9</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D178" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="E178" s="2">
         <v>5.0</v>
       </c>
-      <c r="E178" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F178" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G178" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="H178" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H178" s="3" t="s">
+        <v>550</v>
+      </c>
       <c r="I178" s="1"/>
       <c r="J178" s="1"/>
       <c r="K178" s="1"/>
@@ -9461,27 +9768,29 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C179" s="2">
-        <v>2022.0</v>
+        <v>9</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="D179" s="2">
+        <v>2002.0</v>
+      </c>
+      <c r="E179" s="2">
         <v>5.0</v>
       </c>
-      <c r="E179" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F179" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="G179" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H179" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="H179" s="1"/>
       <c r="I179" s="1"/>
       <c r="J179" s="1"/>
       <c r="K179" s="1"/>
@@ -9506,24 +9815,26 @@
         <v>553</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C180" s="2">
-        <v>2017.0</v>
+        <v>9</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D180" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="E180" s="2">
         <v>5.0</v>
       </c>
-      <c r="E180" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F180" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G180" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G180" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="H180" s="1"/>
+      <c r="H180" s="3" t="s">
+        <v>555</v>
+      </c>
       <c r="I180" s="1"/>
       <c r="J180" s="1"/>
       <c r="K180" s="1"/>
@@ -9545,25 +9856,29 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C181" s="2">
-        <v>2018.0</v>
+        <v>9</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="D181" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="E181" s="1"/>
+        <v>2017.0</v>
+      </c>
+      <c r="E181" s="2">
+        <v>5.0</v>
+      </c>
       <c r="F181" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G181" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="H181" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>557</v>
+      </c>
       <c r="I181" s="1"/>
       <c r="J181" s="1"/>
       <c r="K181" s="1"/>
@@ -9585,27 +9900,27 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C182" s="2">
-        <v>1993.0</v>
+        <v>9</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D182" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="H182" s="1"/>
+        <v>2009.0</v>
+      </c>
+      <c r="E182" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>559</v>
+      </c>
       <c r="I182" s="1"/>
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
@@ -9626,25 +9941,13 @@
       <c r="Z182" s="1"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C183" s="2">
-        <v>2009.0</v>
-      </c>
-      <c r="D183" s="2">
-        <v>3.0</v>
-      </c>
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
       <c r="E183" s="1"/>
-      <c r="F183" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G183" s="3" t="s">
-        <v>560</v>
-      </c>
+      <c r="F183" s="1"/>
+      <c r="G183" s="1"/>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
       <c r="J183" s="1"/>
@@ -9666,25 +9969,13 @@
       <c r="Z183" s="1"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C184" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="D184" s="2">
-        <v>3.0</v>
-      </c>
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
       <c r="E184" s="1"/>
-      <c r="F184" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G184" s="3" t="s">
-        <v>562</v>
-      </c>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1"/>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
       <c r="J184" s="1"/>
@@ -9706,25 +9997,13 @@
       <c r="Z184" s="1"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C185" s="2">
-        <v>2006.0</v>
-      </c>
-      <c r="D185" s="2">
-        <v>3.0</v>
-      </c>
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
       <c r="E185" s="1"/>
-      <c r="F185" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>564</v>
-      </c>
+      <c r="F185" s="1"/>
+      <c r="G185" s="1"/>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
       <c r="J185" s="1"/>
@@ -9746,27 +10025,13 @@
       <c r="Z185" s="1"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C186" s="2">
-        <v>2018.0</v>
-      </c>
-      <c r="D186" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>566</v>
-      </c>
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="1"/>
+      <c r="F186" s="1"/>
+      <c r="G186" s="1"/>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
       <c r="J186" s="1"/>
@@ -9788,25 +10053,13 @@
       <c r="Z186" s="1"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C187" s="2">
-        <v>2005.0</v>
-      </c>
-      <c r="D187" s="2">
-        <v>2.0</v>
-      </c>
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
       <c r="E187" s="1"/>
-      <c r="F187" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>568</v>
-      </c>
+      <c r="F187" s="1"/>
+      <c r="G187" s="1"/>
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
       <c r="J187" s="1"/>
@@ -9828,25 +10081,13 @@
       <c r="Z187" s="1"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="C188" s="2">
-        <v>2003.0</v>
-      </c>
-      <c r="D188" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
       <c r="E188" s="1"/>
-      <c r="F188" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>571</v>
-      </c>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1"/>
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
@@ -9868,23 +10109,13 @@
       <c r="Z188" s="1"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>573</v>
-      </c>
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
       <c r="C189" s="1"/>
-      <c r="D189" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="D189" s="1"/>
       <c r="E189" s="1"/>
-      <c r="F189" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G189" s="3" t="s">
-        <v>574</v>
-      </c>
+      <c r="F189" s="1"/>
+      <c r="G189" s="1"/>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
@@ -32615,194 +32846,187 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="G2"/>
-    <hyperlink r:id="rId2" ref="G3"/>
-    <hyperlink r:id="rId3" ref="G4"/>
-    <hyperlink r:id="rId4" ref="G5"/>
-    <hyperlink r:id="rId5" ref="G6"/>
-    <hyperlink r:id="rId6" ref="G7"/>
-    <hyperlink r:id="rId7" ref="G8"/>
-    <hyperlink r:id="rId8" ref="G9"/>
-    <hyperlink r:id="rId9" ref="G10"/>
-    <hyperlink r:id="rId10" ref="G11"/>
-    <hyperlink r:id="rId11" ref="G12"/>
-    <hyperlink r:id="rId12" ref="G13"/>
-    <hyperlink r:id="rId13" ref="G14"/>
-    <hyperlink r:id="rId14" ref="G15"/>
-    <hyperlink r:id="rId15" ref="G16"/>
-    <hyperlink r:id="rId16" ref="G17"/>
-    <hyperlink r:id="rId17" ref="G18"/>
-    <hyperlink r:id="rId18" ref="G19"/>
-    <hyperlink r:id="rId19" ref="G20"/>
-    <hyperlink r:id="rId20" ref="G21"/>
-    <hyperlink r:id="rId21" ref="G22"/>
-    <hyperlink r:id="rId22" ref="G23"/>
-    <hyperlink r:id="rId23" ref="G24"/>
-    <hyperlink r:id="rId24" ref="G25"/>
-    <hyperlink r:id="rId25" ref="G26"/>
-    <hyperlink r:id="rId26" ref="G27"/>
-    <hyperlink r:id="rId27" ref="G28"/>
-    <hyperlink r:id="rId28" ref="G29"/>
-    <hyperlink r:id="rId29" ref="G30"/>
-    <hyperlink r:id="rId30" ref="G31"/>
-    <hyperlink r:id="rId31" ref="G32"/>
-    <hyperlink r:id="rId32" ref="G33"/>
-    <hyperlink r:id="rId33" ref="G34"/>
-    <hyperlink r:id="rId34" ref="G35"/>
-    <hyperlink r:id="rId35" ref="G36"/>
-    <hyperlink r:id="rId36" ref="G37"/>
-    <hyperlink r:id="rId37" ref="G38"/>
-    <hyperlink r:id="rId38" ref="G39"/>
-    <hyperlink r:id="rId39" ref="G40"/>
-    <hyperlink r:id="rId40" ref="G41"/>
-    <hyperlink r:id="rId41" ref="G42"/>
-    <hyperlink r:id="rId42" ref="G43"/>
-    <hyperlink r:id="rId43" ref="G44"/>
-    <hyperlink r:id="rId44" ref="G45"/>
-    <hyperlink r:id="rId45" ref="G46"/>
-    <hyperlink r:id="rId46" ref="E47"/>
-    <hyperlink r:id="rId47" ref="G47"/>
-    <hyperlink r:id="rId48" ref="G48"/>
-    <hyperlink r:id="rId49" ref="G49"/>
-    <hyperlink r:id="rId50" ref="G50"/>
-    <hyperlink r:id="rId51" ref="G51"/>
-    <hyperlink r:id="rId52" ref="G52"/>
-    <hyperlink r:id="rId53" ref="G53"/>
-    <hyperlink r:id="rId54" ref="G54"/>
-    <hyperlink r:id="rId55" ref="G55"/>
-    <hyperlink r:id="rId56" ref="G56"/>
-    <hyperlink r:id="rId57" ref="G57"/>
-    <hyperlink r:id="rId58" ref="G58"/>
-    <hyperlink r:id="rId59" ref="G59"/>
-    <hyperlink r:id="rId60" ref="G60"/>
-    <hyperlink r:id="rId61" ref="G61"/>
-    <hyperlink r:id="rId62" ref="G62"/>
-    <hyperlink r:id="rId63" ref="G63"/>
-    <hyperlink r:id="rId64" ref="G64"/>
-    <hyperlink r:id="rId65" ref="G65"/>
-    <hyperlink r:id="rId66" ref="G66"/>
-    <hyperlink r:id="rId67" ref="G67"/>
-    <hyperlink r:id="rId68" ref="G68"/>
-    <hyperlink r:id="rId69" ref="G69"/>
-    <hyperlink r:id="rId70" ref="G70"/>
-    <hyperlink r:id="rId71" ref="G71"/>
-    <hyperlink r:id="rId72" ref="G72"/>
-    <hyperlink r:id="rId73" ref="G73"/>
-    <hyperlink r:id="rId74" ref="G74"/>
-    <hyperlink r:id="rId75" ref="G75"/>
-    <hyperlink r:id="rId76" ref="G76"/>
-    <hyperlink r:id="rId77" ref="G77"/>
-    <hyperlink r:id="rId78" ref="G78"/>
-    <hyperlink r:id="rId79" ref="G79"/>
-    <hyperlink r:id="rId80" ref="G80"/>
-    <hyperlink r:id="rId81" ref="G81"/>
-    <hyperlink r:id="rId82" ref="G82"/>
-    <hyperlink r:id="rId83" ref="G83"/>
-    <hyperlink r:id="rId84" ref="G84"/>
-    <hyperlink r:id="rId85" ref="G85"/>
-    <hyperlink r:id="rId86" ref="G86"/>
-    <hyperlink r:id="rId87" ref="G87"/>
-    <hyperlink r:id="rId88" ref="G88"/>
-    <hyperlink r:id="rId89" ref="G89"/>
-    <hyperlink r:id="rId90" ref="G90"/>
-    <hyperlink r:id="rId91" ref="G91"/>
-    <hyperlink r:id="rId92" ref="G92"/>
-    <hyperlink r:id="rId93" ref="G93"/>
-    <hyperlink r:id="rId94" ref="G94"/>
-    <hyperlink r:id="rId95" ref="G95"/>
-    <hyperlink r:id="rId96" ref="G96"/>
-    <hyperlink r:id="rId97" ref="G97"/>
-    <hyperlink r:id="rId98" ref="G98"/>
-    <hyperlink r:id="rId99" ref="G99"/>
-    <hyperlink r:id="rId100" ref="G100"/>
-    <hyperlink r:id="rId101" ref="G101"/>
-    <hyperlink r:id="rId102" ref="G102"/>
-    <hyperlink r:id="rId103" ref="G103"/>
-    <hyperlink r:id="rId104" ref="G104"/>
-    <hyperlink r:id="rId105" ref="G105"/>
-    <hyperlink r:id="rId106" ref="G106"/>
-    <hyperlink r:id="rId107" ref="G107"/>
-    <hyperlink r:id="rId108" ref="G108"/>
-    <hyperlink r:id="rId109" ref="G109"/>
-    <hyperlink r:id="rId110" ref="G110"/>
-    <hyperlink r:id="rId111" ref="G111"/>
-    <hyperlink r:id="rId112" ref="G112"/>
-    <hyperlink r:id="rId113" ref="G113"/>
-    <hyperlink r:id="rId114" ref="G114"/>
-    <hyperlink r:id="rId115" ref="G115"/>
-    <hyperlink r:id="rId116" ref="G116"/>
-    <hyperlink r:id="rId117" ref="G117"/>
-    <hyperlink r:id="rId118" ref="G118"/>
-    <hyperlink r:id="rId119" ref="G119"/>
-    <hyperlink r:id="rId120" ref="G121"/>
-    <hyperlink r:id="rId121" ref="G122"/>
-    <hyperlink r:id="rId122" ref="G123"/>
-    <hyperlink r:id="rId123" ref="G124"/>
-    <hyperlink r:id="rId124" ref="G125"/>
-    <hyperlink r:id="rId125" ref="G126"/>
-    <hyperlink r:id="rId126" ref="G127"/>
-    <hyperlink r:id="rId127" ref="G128"/>
-    <hyperlink r:id="rId128" ref="G129"/>
-    <hyperlink r:id="rId129" ref="G130"/>
-    <hyperlink r:id="rId130" ref="G131"/>
-    <hyperlink r:id="rId131" ref="G132"/>
-    <hyperlink r:id="rId132" ref="G133"/>
-    <hyperlink r:id="rId133" ref="G134"/>
-    <hyperlink r:id="rId134" ref="G135"/>
-    <hyperlink r:id="rId135" ref="G136"/>
-    <hyperlink r:id="rId136" ref="G137"/>
-    <hyperlink r:id="rId137" ref="G138"/>
-    <hyperlink r:id="rId138" ref="G139"/>
-    <hyperlink r:id="rId139" ref="G140"/>
-    <hyperlink r:id="rId140" ref="G141"/>
-    <hyperlink r:id="rId141" ref="G142"/>
-    <hyperlink r:id="rId142" ref="G143"/>
-    <hyperlink r:id="rId143" ref="G144"/>
-    <hyperlink r:id="rId144" ref="G145"/>
-    <hyperlink r:id="rId145" ref="G146"/>
-    <hyperlink r:id="rId146" ref="G147"/>
-    <hyperlink r:id="rId147" ref="G148"/>
-    <hyperlink r:id="rId148" ref="G149"/>
-    <hyperlink r:id="rId149" ref="G150"/>
-    <hyperlink r:id="rId150" ref="G151"/>
-    <hyperlink r:id="rId151" ref="G152"/>
-    <hyperlink r:id="rId152" ref="G154"/>
-    <hyperlink r:id="rId153" ref="G155"/>
-    <hyperlink r:id="rId154" ref="G156"/>
-    <hyperlink r:id="rId155" ref="G157"/>
-    <hyperlink r:id="rId156" ref="G158"/>
-    <hyperlink r:id="rId157" ref="G159"/>
-    <hyperlink r:id="rId158" ref="G160"/>
-    <hyperlink r:id="rId159" ref="G161"/>
-    <hyperlink r:id="rId160" ref="G162"/>
-    <hyperlink r:id="rId161" ref="G163"/>
-    <hyperlink r:id="rId162" ref="G164"/>
-    <hyperlink r:id="rId163" ref="G165"/>
-    <hyperlink r:id="rId164" ref="G166"/>
-    <hyperlink r:id="rId165" ref="G167"/>
-    <hyperlink r:id="rId166" ref="G168"/>
-    <hyperlink r:id="rId167" ref="G169"/>
-    <hyperlink r:id="rId168" ref="G170"/>
-    <hyperlink r:id="rId169" ref="G171"/>
-    <hyperlink r:id="rId170" ref="G172"/>
-    <hyperlink r:id="rId171" ref="G173"/>
-    <hyperlink r:id="rId172" ref="G174"/>
-    <hyperlink r:id="rId173" ref="G175"/>
-    <hyperlink r:id="rId174" ref="G176"/>
-    <hyperlink r:id="rId175" ref="G177"/>
-    <hyperlink r:id="rId176" ref="G178"/>
-    <hyperlink r:id="rId177" ref="G179"/>
-    <hyperlink r:id="rId178" ref="G180"/>
-    <hyperlink r:id="rId179" ref="G181"/>
-    <hyperlink r:id="rId180" ref="G182"/>
-    <hyperlink r:id="rId181" ref="G183"/>
-    <hyperlink r:id="rId182" ref="G184"/>
-    <hyperlink r:id="rId183" ref="G185"/>
-    <hyperlink r:id="rId184" ref="G186"/>
-    <hyperlink r:id="rId185" ref="G187"/>
-    <hyperlink r:id="rId186" ref="G188"/>
-    <hyperlink r:id="rId187" ref="G189"/>
+    <hyperlink r:id="rId1" ref="H2"/>
+    <hyperlink r:id="rId2" ref="H3"/>
+    <hyperlink r:id="rId3" ref="H4"/>
+    <hyperlink r:id="rId4" ref="H5"/>
+    <hyperlink r:id="rId5" ref="H6"/>
+    <hyperlink r:id="rId6" ref="H7"/>
+    <hyperlink r:id="rId7" ref="H8"/>
+    <hyperlink r:id="rId8" ref="H9"/>
+    <hyperlink r:id="rId9" ref="H10"/>
+    <hyperlink r:id="rId10" ref="H11"/>
+    <hyperlink r:id="rId11" ref="H12"/>
+    <hyperlink r:id="rId12" ref="H13"/>
+    <hyperlink r:id="rId13" ref="H14"/>
+    <hyperlink r:id="rId14" ref="H15"/>
+    <hyperlink r:id="rId15" ref="H16"/>
+    <hyperlink r:id="rId16" ref="H17"/>
+    <hyperlink r:id="rId17" ref="H18"/>
+    <hyperlink r:id="rId18" ref="H19"/>
+    <hyperlink r:id="rId19" ref="H20"/>
+    <hyperlink r:id="rId20" ref="H21"/>
+    <hyperlink r:id="rId21" ref="H22"/>
+    <hyperlink r:id="rId22" ref="H23"/>
+    <hyperlink r:id="rId23" ref="H24"/>
+    <hyperlink r:id="rId24" ref="H25"/>
+    <hyperlink r:id="rId25" ref="H26"/>
+    <hyperlink r:id="rId26" ref="H27"/>
+    <hyperlink r:id="rId27" ref="H28"/>
+    <hyperlink r:id="rId28" ref="H29"/>
+    <hyperlink r:id="rId29" ref="H30"/>
+    <hyperlink r:id="rId30" ref="H31"/>
+    <hyperlink r:id="rId31" ref="H32"/>
+    <hyperlink r:id="rId32" ref="H33"/>
+    <hyperlink r:id="rId33" ref="H34"/>
+    <hyperlink r:id="rId34" ref="H35"/>
+    <hyperlink r:id="rId35" ref="H36"/>
+    <hyperlink r:id="rId36" ref="H37"/>
+    <hyperlink r:id="rId37" ref="H38"/>
+    <hyperlink r:id="rId38" ref="H39"/>
+    <hyperlink r:id="rId39" ref="H40"/>
+    <hyperlink r:id="rId40" ref="H41"/>
+    <hyperlink r:id="rId41" ref="H42"/>
+    <hyperlink r:id="rId42" ref="H43"/>
+    <hyperlink r:id="rId43" ref="H44"/>
+    <hyperlink r:id="rId44" ref="H45"/>
+    <hyperlink r:id="rId45" ref="H46"/>
+    <hyperlink r:id="rId46" ref="F47"/>
+    <hyperlink r:id="rId47" ref="H47"/>
+    <hyperlink r:id="rId48" ref="H48"/>
+    <hyperlink r:id="rId49" ref="H49"/>
+    <hyperlink r:id="rId50" ref="H50"/>
+    <hyperlink r:id="rId51" ref="H51"/>
+    <hyperlink r:id="rId52" ref="H52"/>
+    <hyperlink r:id="rId53" ref="H53"/>
+    <hyperlink r:id="rId54" ref="H54"/>
+    <hyperlink r:id="rId55" ref="H55"/>
+    <hyperlink r:id="rId56" ref="H56"/>
+    <hyperlink r:id="rId57" ref="H57"/>
+    <hyperlink r:id="rId58" ref="H58"/>
+    <hyperlink r:id="rId59" ref="H59"/>
+    <hyperlink r:id="rId60" ref="H60"/>
+    <hyperlink r:id="rId61" ref="H61"/>
+    <hyperlink r:id="rId62" ref="H62"/>
+    <hyperlink r:id="rId63" ref="H63"/>
+    <hyperlink r:id="rId64" ref="H64"/>
+    <hyperlink r:id="rId65" ref="H65"/>
+    <hyperlink r:id="rId66" ref="H66"/>
+    <hyperlink r:id="rId67" ref="H67"/>
+    <hyperlink r:id="rId68" ref="H68"/>
+    <hyperlink r:id="rId69" ref="H69"/>
+    <hyperlink r:id="rId70" ref="H70"/>
+    <hyperlink r:id="rId71" ref="H71"/>
+    <hyperlink r:id="rId72" ref="H72"/>
+    <hyperlink r:id="rId73" ref="H73"/>
+    <hyperlink r:id="rId74" ref="H74"/>
+    <hyperlink r:id="rId75" ref="H75"/>
+    <hyperlink r:id="rId76" ref="H76"/>
+    <hyperlink r:id="rId77" ref="H77"/>
+    <hyperlink r:id="rId78" ref="H78"/>
+    <hyperlink r:id="rId79" ref="H79"/>
+    <hyperlink r:id="rId80" ref="H80"/>
+    <hyperlink r:id="rId81" ref="H81"/>
+    <hyperlink r:id="rId82" ref="H82"/>
+    <hyperlink r:id="rId83" ref="H83"/>
+    <hyperlink r:id="rId84" ref="H84"/>
+    <hyperlink r:id="rId85" ref="H85"/>
+    <hyperlink r:id="rId86" ref="H86"/>
+    <hyperlink r:id="rId87" ref="H87"/>
+    <hyperlink r:id="rId88" ref="H88"/>
+    <hyperlink r:id="rId89" ref="H89"/>
+    <hyperlink r:id="rId90" ref="H90"/>
+    <hyperlink r:id="rId91" ref="H91"/>
+    <hyperlink r:id="rId92" ref="H92"/>
+    <hyperlink r:id="rId93" ref="H93"/>
+    <hyperlink r:id="rId94" ref="H94"/>
+    <hyperlink r:id="rId95" ref="H95"/>
+    <hyperlink r:id="rId96" ref="H96"/>
+    <hyperlink r:id="rId97" ref="H97"/>
+    <hyperlink r:id="rId98" ref="H98"/>
+    <hyperlink r:id="rId99" ref="H99"/>
+    <hyperlink r:id="rId100" ref="H100"/>
+    <hyperlink r:id="rId101" ref="H101"/>
+    <hyperlink r:id="rId102" ref="H102"/>
+    <hyperlink r:id="rId103" ref="H103"/>
+    <hyperlink r:id="rId104" ref="H104"/>
+    <hyperlink r:id="rId105" ref="H105"/>
+    <hyperlink r:id="rId106" ref="H106"/>
+    <hyperlink r:id="rId107" ref="H107"/>
+    <hyperlink r:id="rId108" ref="H108"/>
+    <hyperlink r:id="rId109" ref="H109"/>
+    <hyperlink r:id="rId110" ref="H110"/>
+    <hyperlink r:id="rId111" ref="H111"/>
+    <hyperlink r:id="rId112" ref="H112"/>
+    <hyperlink r:id="rId113" ref="H113"/>
+    <hyperlink r:id="rId114" ref="H114"/>
+    <hyperlink r:id="rId115" ref="H115"/>
+    <hyperlink r:id="rId116" ref="H116"/>
+    <hyperlink r:id="rId117" ref="H117"/>
+    <hyperlink r:id="rId118" ref="H118"/>
+    <hyperlink r:id="rId119" ref="H120"/>
+    <hyperlink r:id="rId120" ref="H121"/>
+    <hyperlink r:id="rId121" ref="H122"/>
+    <hyperlink r:id="rId122" ref="H123"/>
+    <hyperlink r:id="rId123" ref="H124"/>
+    <hyperlink r:id="rId124" ref="H125"/>
+    <hyperlink r:id="rId125" ref="H126"/>
+    <hyperlink r:id="rId126" ref="H127"/>
+    <hyperlink r:id="rId127" ref="H128"/>
+    <hyperlink r:id="rId128" ref="H129"/>
+    <hyperlink r:id="rId129" ref="H130"/>
+    <hyperlink r:id="rId130" ref="H131"/>
+    <hyperlink r:id="rId131" ref="H132"/>
+    <hyperlink r:id="rId132" ref="H133"/>
+    <hyperlink r:id="rId133" ref="H134"/>
+    <hyperlink r:id="rId134" ref="H135"/>
+    <hyperlink r:id="rId135" ref="H136"/>
+    <hyperlink r:id="rId136" ref="H137"/>
+    <hyperlink r:id="rId137" ref="H138"/>
+    <hyperlink r:id="rId138" ref="H139"/>
+    <hyperlink r:id="rId139" ref="H140"/>
+    <hyperlink r:id="rId140" ref="H141"/>
+    <hyperlink r:id="rId141" ref="H142"/>
+    <hyperlink r:id="rId142" ref="H143"/>
+    <hyperlink r:id="rId143" ref="H144"/>
+    <hyperlink r:id="rId144" ref="H145"/>
+    <hyperlink r:id="rId145" ref="H146"/>
+    <hyperlink r:id="rId146" ref="H147"/>
+    <hyperlink r:id="rId147" ref="H148"/>
+    <hyperlink r:id="rId148" ref="H149"/>
+    <hyperlink r:id="rId149" ref="H150"/>
+    <hyperlink r:id="rId150" ref="H151"/>
+    <hyperlink r:id="rId151" ref="H152"/>
+    <hyperlink r:id="rId152" ref="H154"/>
+    <hyperlink r:id="rId153" ref="H155"/>
+    <hyperlink r:id="rId154" ref="H156"/>
+    <hyperlink r:id="rId155" ref="H157"/>
+    <hyperlink r:id="rId156" ref="H158"/>
+    <hyperlink r:id="rId157" ref="H159"/>
+    <hyperlink r:id="rId158" ref="H160"/>
+    <hyperlink r:id="rId159" ref="H161"/>
+    <hyperlink r:id="rId160" ref="H162"/>
+    <hyperlink r:id="rId161" ref="H163"/>
+    <hyperlink r:id="rId162" ref="H164"/>
+    <hyperlink r:id="rId163" ref="H165"/>
+    <hyperlink r:id="rId164" ref="H166"/>
+    <hyperlink r:id="rId165" ref="H167"/>
+    <hyperlink r:id="rId166" ref="H168"/>
+    <hyperlink r:id="rId167" ref="H169"/>
+    <hyperlink r:id="rId168" ref="H170"/>
+    <hyperlink r:id="rId169" ref="H171"/>
+    <hyperlink r:id="rId170" ref="H172"/>
+    <hyperlink r:id="rId171" ref="H173"/>
+    <hyperlink r:id="rId172" ref="H174"/>
+    <hyperlink r:id="rId173" ref="H175"/>
+    <hyperlink r:id="rId174" ref="H176"/>
+    <hyperlink r:id="rId175" ref="H177"/>
+    <hyperlink r:id="rId176" ref="H178"/>
+    <hyperlink r:id="rId177" ref="H179"/>
+    <hyperlink r:id="rId178" ref="H180"/>
+    <hyperlink r:id="rId179" ref="H181"/>
+    <hyperlink r:id="rId180" ref="H182"/>
   </hyperlinks>
-  <drawing r:id="rId188"/>
+  <drawing r:id="rId181"/>
 </worksheet>
 </file>
--- a/Car_Wash_Advisory_Companies.xlsx
+++ b/Car_Wash_Advisory_Companies.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="562">
   <si>
     <t>Company Name</t>
   </si>
@@ -37,12 +37,27 @@
     <t>Website</t>
   </si>
   <si>
+    <t>Whistle Express Car Wash</t>
+  </si>
+  <si>
+    <t>653ad5a6e882f528b3301834</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>Oaktree Capital Management LP</t>
+  </si>
+  <si>
+    <t>North Carolina | South Carolina | Georgia | Florida | Virginia | Tennessee | Kentucky | Ohio | Indiana | Illinois | Michigan | Texas | Alabama | Arkansas | Mississippi | Louisiana | Oklahoma | Kansas | Colorado | Utah | Missouri | Arizona | Nevada</t>
+  </si>
+  <si>
+    <t>https://whistleexpresscarwash.com/</t>
+  </si>
+  <si>
     <t>Mister Car Wash</t>
   </si>
   <si>
-    <t>653ad5a6e882f528b3301834</t>
-  </si>
-  <si>
     <t>Arizona</t>
   </si>
   <si>
@@ -115,21 +130,6 @@
     <t>https://tommys-express.com/</t>
   </si>
   <si>
-    <t>Take 5 Car Wash</t>
-  </si>
-  <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
-    <t>Roark Capital Group</t>
-  </si>
-  <si>
-    <t>Alabama | Arkansas | Colorado | Florida | Georgia | Indiana | Kentucky | Louisiana | Mississippi | North Carolina | Ohio | Oklahoma | South Carolina | Tennessee | Texas | West Virginia</t>
-  </si>
-  <si>
-    <t>https://www.take5carwash.com/</t>
-  </si>
-  <si>
     <t>Spotless Brands</t>
   </si>
   <si>
@@ -160,6 +160,18 @@
     <t>https://www.zipscarwash.com/</t>
   </si>
   <si>
+    <t>Super Star Car Wash</t>
+  </si>
+  <si>
+    <t>TSG Consumer Partners</t>
+  </si>
+  <si>
+    <t>Arizona | California | Colorado | Texas</t>
+  </si>
+  <si>
+    <t>https://www.superstarcarwashaz.com/</t>
+  </si>
+  <si>
     <t>GO Car Wash</t>
   </si>
   <si>
@@ -202,6 +214,21 @@
     <t>https://www.whitewatercw.com/</t>
   </si>
   <si>
+    <t>ModWash</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>Hutton</t>
+  </si>
+  <si>
+    <t>Alabama | Florida | Georgia | Maryland | New Jersey | North Carolina | Ohio | Pennsylvania | South Carolina | Tennessee | Virginia | Delaware</t>
+  </si>
+  <si>
+    <t>https://www.modwash.com/</t>
+  </si>
+  <si>
     <t>Express Wash Concepts</t>
   </si>
   <si>
@@ -214,45 +241,6 @@
     <t>https://www.expresswashconcepts.com/</t>
   </si>
   <si>
-    <t>ModWash</t>
-  </si>
-  <si>
-    <t>Tennessee</t>
-  </si>
-  <si>
-    <t>Hutton</t>
-  </si>
-  <si>
-    <t>Alabama | Florida | Georgia | Maryland | New Jersey | North Carolina | Ohio | Pennsylvania | South Carolina | Tennessee | Virginia | Delaware</t>
-  </si>
-  <si>
-    <t>https://www.modwash.com/</t>
-  </si>
-  <si>
-    <t>Super Star Car Wash</t>
-  </si>
-  <si>
-    <t>TSG Consumer Partners</t>
-  </si>
-  <si>
-    <t>Arizona | California | Colorado | Texas</t>
-  </si>
-  <si>
-    <t>https://www.superstarcarwashaz.com/</t>
-  </si>
-  <si>
-    <t>Whistle Express Car Wash</t>
-  </si>
-  <si>
-    <t>Oaktree Capital Management LP</t>
-  </si>
-  <si>
-    <t>Alabama | Florida | Georgia | Indiana | Kentucky | North Carolina | Ohio | South Carolina | Tennessee | Virginia</t>
-  </si>
-  <si>
-    <t>https://whistleexpresscarwash.com/</t>
-  </si>
-  <si>
     <t>Summit Wash Holdings</t>
   </si>
   <si>
@@ -727,7 +715,7 @@
     <t>Arizona | Nevada</t>
   </si>
   <si>
-    <t>https://ultracleanexpress.com/</t>
+    <t>https://dashcarwash.com/</t>
   </si>
   <si>
     <t>Carnation Auto Spa</t>
@@ -1204,6 +1192,15 @@
     <t>https://www.whitehorseautowash.com/</t>
   </si>
   <si>
+    <t>Dream Clean Car Wash</t>
+  </si>
+  <si>
+    <t>Cross Timbers Capital Group</t>
+  </si>
+  <si>
+    <t>https://www.dreamcleancw.com/</t>
+  </si>
+  <si>
     <t>Fast Splash Car Wash</t>
   </si>
   <si>
@@ -1489,18 +1486,18 @@
     <t>https://www.tiptopcarwashes.com/</t>
   </si>
   <si>
+    <t>Ocean Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://oceancarwashtx.com/</t>
+  </si>
+  <si>
     <t>Dash Car Wash</t>
   </si>
   <si>
     <t>Arizona | Texas | Nevada</t>
   </si>
   <si>
-    <t>Dream Clean Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.dreamcleancw.com/</t>
-  </si>
-  <si>
     <t>Greenhill Car Wash</t>
   </si>
   <si>
@@ -1531,7 +1528,7 @@
     <t>https://washtopia.com/</t>
   </si>
   <si>
-    <t>The Wave Car Wash</t>
+    <t>The Wave Car Wash (WA)</t>
   </si>
   <si>
     <t>https://www.thewavewash.com/</t>
@@ -1547,6 +1544,15 @@
   </si>
   <si>
     <t>https://www.beboscarwash.com/</t>
+  </si>
+  <si>
+    <t>Blue Tide Car Wash</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>https://bluetidecarwash.com/</t>
   </si>
   <si>
     <t>Canton Car Wash</t>
@@ -2019,10 +2025,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="2">
-        <v>1969.0</v>
+        <v>2014.0</v>
       </c>
       <c r="E2" s="2">
-        <v>518.0</v>
+        <v>530.0</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
@@ -2063,10 +2069,10 @@
         <v>15</v>
       </c>
       <c r="D3" s="2">
-        <v>1999.0</v>
+        <v>1969.0</v>
       </c>
       <c r="E3" s="2">
-        <v>308.0</v>
+        <v>518.0</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
@@ -2107,10 +2113,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="2">
-        <v>2004.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E4" s="2">
-        <v>275.0</v>
+        <v>308.0</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>21</v>
@@ -2151,10 +2157,10 @@
         <v>25</v>
       </c>
       <c r="D5" s="2">
-        <v>2006.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E5" s="2">
-        <v>257.0</v>
+        <v>275.0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>26</v>
@@ -2195,10 +2201,10 @@
         <v>30</v>
       </c>
       <c r="D6" s="2">
-        <v>2011.0</v>
+        <v>2006.0</v>
       </c>
       <c r="E6" s="2">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>31</v>
@@ -2239,10 +2245,10 @@
         <v>35</v>
       </c>
       <c r="D7" s="2">
-        <v>2006.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E7" s="2">
-        <v>226.0</v>
+        <v>256.0</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>36</v>
@@ -2368,22 +2374,22 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1993.0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>192.0</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>154.0</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -2406,19 +2412,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D11" s="2">
-        <v>2002.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E11" s="2">
-        <v>150.0</v>
+        <v>154.0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>55</v>
@@ -2456,22 +2462,22 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2002.0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>150.0</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="2">
-        <v>2015.0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>141.0</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -2494,22 +2500,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2015.0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>141.0</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2018.0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>127.0</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>65</v>
@@ -2550,7 +2556,7 @@
         <v>2020.0</v>
       </c>
       <c r="E14" s="2">
-        <v>120.0</v>
+        <v>130.0</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>69</v>
@@ -2588,16 +2594,16 @@
         <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="D15" s="2">
-        <v>1993.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E15" s="2">
-        <v>112.0</v>
+        <v>127.0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>74</v>
@@ -2632,22 +2638,22 @@
         <v>9</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D16" s="2">
-        <v>2014.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E16" s="2">
-        <v>108.0</v>
+        <v>104.0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2670,28 +2676,28 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2">
-        <v>2022.0</v>
+        <v>1969.0</v>
       </c>
       <c r="E17" s="2">
-        <v>104.0</v>
+        <v>91.0</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -2714,25 +2720,25 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="D18" s="2">
-        <v>1969.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E18" s="2">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>87</v>
@@ -2764,22 +2770,22 @@
         <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2">
-        <v>2010.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E19" s="2">
-        <v>90.0</v>
+        <v>83.0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>89</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -2802,22 +2808,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="D20" s="2">
         <v>2021.0</v>
       </c>
       <c r="E20" s="2">
-        <v>83.0</v>
+        <v>77.0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>93</v>
@@ -2852,22 +2858,22 @@
         <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D21" s="2">
-        <v>2021.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E21" s="2">
-        <v>77.0</v>
+        <v>71.0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -2890,28 +2896,28 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D22" s="2">
-        <v>1981.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E22" s="2">
         <v>71.0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -2934,19 +2940,19 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D23" s="2">
-        <v>2015.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E23" s="2">
-        <v>71.0</v>
+        <v>68.0</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>106</v>
@@ -2984,13 +2990,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2">
-        <v>2016.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E24" s="2">
-        <v>68.0</v>
+        <v>64.0</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>110</v>
@@ -3028,22 +3034,22 @@
         <v>9</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="D25" s="2">
-        <v>2019.0</v>
+        <v>1970.0</v>
       </c>
       <c r="E25" s="2">
-        <v>64.0</v>
+        <v>58.0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -3066,22 +3072,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D26" s="2">
-        <v>1970.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E26" s="2">
         <v>58.0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>120</v>
@@ -3116,22 +3122,22 @@
         <v>9</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2015.0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>54.0</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="2">
-        <v>2007.0</v>
-      </c>
-      <c r="E27" s="2">
-        <v>58.0</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -3154,22 +3160,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="D28" s="2">
-        <v>2015.0</v>
+        <v>1948.0</v>
       </c>
       <c r="E28" s="2">
-        <v>54.0</v>
+        <v>50.0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>127</v>
@@ -3204,22 +3210,22 @@
         <v>9</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2">
-        <v>1948.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E29" s="2">
         <v>50.0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -3242,7 +3248,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>9</v>
@@ -3251,13 +3257,13 @@
         <v>35</v>
       </c>
       <c r="D30" s="2">
-        <v>2012.0</v>
+        <v>1953.0</v>
       </c>
       <c r="E30" s="2">
-        <v>50.0</v>
+        <v>49.0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>134</v>
@@ -3292,22 +3298,22 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="D31" s="2">
-        <v>1953.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E31" s="2">
         <v>49.0</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -3330,25 +3336,25 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D32" s="2">
-        <v>1997.0</v>
+        <v>1959.0</v>
       </c>
       <c r="E32" s="2">
-        <v>49.0</v>
+        <v>47.0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>141</v>
@@ -3380,16 +3386,16 @@
         <v>9</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2009.0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>46.0</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="D33" s="2">
-        <v>1959.0</v>
-      </c>
-      <c r="E33" s="2">
-        <v>47.0</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>144</v>
@@ -3424,13 +3430,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2">
-        <v>2009.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E34" s="2">
-        <v>46.0</v>
+        <v>45.0</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>147</v>
@@ -3468,22 +3474,22 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D35" s="2">
-        <v>2020.0</v>
+        <v>1957.0</v>
       </c>
       <c r="E35" s="2">
         <v>45.0</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="H35" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -3506,22 +3512,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="D36" s="2">
-        <v>1957.0</v>
+        <v>1988.0</v>
       </c>
       <c r="E36" s="2">
         <v>45.0</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>155</v>
@@ -3556,13 +3562,13 @@
         <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="D37" s="2">
-        <v>1988.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E37" s="2">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>158</v>
@@ -3600,22 +3606,22 @@
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D38" s="2">
-        <v>1995.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E38" s="2">
         <v>42.0</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -3638,22 +3644,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="D39" s="2">
-        <v>2013.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E39" s="2">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>166</v>
@@ -3688,22 +3694,22 @@
         <v>9</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1948.0</v>
+      </c>
+      <c r="E40" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D40" s="2">
-        <v>1976.0</v>
-      </c>
-      <c r="E40" s="2">
-        <v>41.0</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -3726,28 +3732,28 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D41" s="2">
-        <v>1948.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E41" s="2">
-        <v>40.0</v>
+        <v>36.0</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G41" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -3770,28 +3776,28 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D42" s="2">
-        <v>2011.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E42" s="2">
         <v>36.0</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G42" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -3814,22 +3820,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="D43" s="2">
-        <v>2018.0</v>
+        <v>1967.0</v>
       </c>
       <c r="E43" s="2">
-        <v>36.0</v>
+        <v>32.0</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>179</v>
@@ -3864,22 +3870,22 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1986.0</v>
+      </c>
+      <c r="E44" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="D44" s="2">
-        <v>1967.0</v>
-      </c>
-      <c r="E44" s="2">
-        <v>32.0</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -3902,28 +3908,28 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D45" s="2">
-        <v>1986.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E45" s="2">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -3946,28 +3952,28 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>40</v>
+        <v>187</v>
       </c>
       <c r="D46" s="2">
-        <v>2013.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E46" s="2">
         <v>30.0</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="3" t="s">
         <v>188</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>40</v>
+        <v>189</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -3990,28 +3996,28 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="D47" s="2">
-        <v>2015.0</v>
+        <v>1970.0</v>
       </c>
       <c r="E47" s="2">
-        <v>30.0</v>
-      </c>
-      <c r="F47" s="3" t="s">
+        <v>29.0</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -4034,25 +4040,25 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="D48" s="2">
-        <v>1970.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E48" s="2">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>197</v>
@@ -4084,22 +4090,22 @@
         <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="D49" s="2">
-        <v>1981.0</v>
+        <v>1965.0</v>
       </c>
       <c r="E49" s="2">
         <v>28.0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>200</v>
+        <v>36</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -4122,28 +4128,28 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>182</v>
+        <v>15</v>
       </c>
       <c r="D50" s="2">
-        <v>1965.0</v>
+        <v>1992.0</v>
       </c>
       <c r="E50" s="2">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -4166,28 +4172,28 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="D51" s="2">
-        <v>1992.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E51" s="2">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>31</v>
+        <v>205</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -4210,16 +4216,16 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>208</v>
+        <v>63</v>
       </c>
       <c r="D52" s="2">
-        <v>2020.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E52" s="2">
         <v>26.0</v>
@@ -4260,22 +4266,22 @@
         <v>9</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>59</v>
+        <v>213</v>
       </c>
       <c r="D53" s="2">
-        <v>2004.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E53" s="2">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -4298,28 +4304,28 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>217</v>
+        <v>25</v>
       </c>
       <c r="D54" s="2">
-        <v>2000.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E54" s="2">
         <v>25.0</v>
       </c>
       <c r="F54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H54" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -4342,28 +4348,28 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D55" s="2">
-        <v>2011.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E55" s="2">
         <v>25.0</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>31</v>
+        <v>220</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4386,25 +4392,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="D56" s="2">
-        <v>2004.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E56" s="2">
         <v>25.0</v>
       </c>
       <c r="F56" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>225</v>
@@ -4436,22 +4442,22 @@
         <v>9</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c r="D57" s="2">
-        <v>2019.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E57" s="2">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="F57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -4474,28 +4480,28 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D58" s="2">
-        <v>2013.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E58" s="2">
         <v>24.0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -4518,22 +4524,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="D59" s="2">
-        <v>2018.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E59" s="2">
         <v>24.0</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>31</v>
+        <v>232</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>233</v>
@@ -4568,22 +4574,22 @@
         <v>9</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="D60" s="2">
         <v>2021.0</v>
       </c>
       <c r="E60" s="2">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H60" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -4606,28 +4612,28 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D61" s="2">
-        <v>2021.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E61" s="2">
         <v>23.0</v>
       </c>
       <c r="F61" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -4650,28 +4656,28 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>59</v>
+        <v>242</v>
       </c>
       <c r="D62" s="2">
-        <v>2012.0</v>
+        <v>1959.0</v>
       </c>
       <c r="E62" s="2">
         <v>23.0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>31</v>
+        <v>243</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -4694,28 +4700,28 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>246</v>
+        <v>114</v>
       </c>
       <c r="D63" s="2">
-        <v>1959.0</v>
+        <v>1966.0</v>
       </c>
       <c r="E63" s="2">
         <v>23.0</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="H63" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -4738,28 +4744,28 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="D64" s="2">
-        <v>1966.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E64" s="2">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>251</v>
+        <v>45</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -4782,28 +4788,28 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="D65" s="2">
-        <v>1981.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E65" s="2">
         <v>22.0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -4826,25 +4832,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="D66" s="2">
         <v>2019.0</v>
       </c>
       <c r="E66" s="2">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>31</v>
+        <v>254</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>89</v>
+        <v>255</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>256</v>
@@ -4876,16 +4882,16 @@
         <v>9</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>15</v>
+        <v>258</v>
       </c>
       <c r="D67" s="2">
-        <v>2019.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E67" s="2">
         <v>21.0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>258</v>
+        <v>36</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>259</v>
@@ -4920,22 +4926,22 @@
         <v>9</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D68" s="2">
+        <v>1997.0</v>
+      </c>
+      <c r="E68" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D68" s="2">
-        <v>2016.0</v>
-      </c>
-      <c r="E68" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G68" s="1" t="s">
+      <c r="H68" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
@@ -4958,28 +4964,28 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="D69" s="2">
-        <v>1997.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E69" s="2">
         <v>20.0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G69" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
@@ -5002,28 +5008,28 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="D70" s="2">
-        <v>2012.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E70" s="2">
         <v>20.0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G70" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
@@ -5046,28 +5052,28 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="D71" s="2">
-        <v>2019.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E71" s="2">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>31</v>
+        <v>271</v>
       </c>
       <c r="G71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -5090,28 +5096,28 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D72" s="2">
-        <v>1997.0</v>
+        <v>1960.0</v>
       </c>
       <c r="E72" s="2">
         <v>19.0</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>275</v>
+        <v>36</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -5134,28 +5140,28 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>40</v>
+        <v>258</v>
       </c>
       <c r="D73" s="2">
-        <v>1960.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E73" s="2">
         <v>19.0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -5178,28 +5184,28 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>262</v>
+        <v>101</v>
       </c>
       <c r="D74" s="2">
-        <v>2012.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E74" s="2">
         <v>19.0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>280</v>
+        <v>101</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -5222,28 +5228,28 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D75" s="2">
-        <v>1995.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E75" s="2">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>31</v>
+        <v>281</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -5266,28 +5272,28 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="D76" s="2">
-        <v>2020.0</v>
+        <v>1951.0</v>
       </c>
       <c r="E76" s="2">
         <v>18.0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>285</v>
+        <v>36</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -5310,28 +5316,28 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="D77" s="2">
-        <v>1951.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E77" s="2">
         <v>18.0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>155</v>
+        <v>286</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -5354,28 +5360,28 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D78" s="2">
-        <v>1976.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E78" s="2">
         <v>18.0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G78" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -5398,28 +5404,28 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="D79" s="2">
-        <v>2018.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E79" s="2">
         <v>18.0</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>31</v>
+        <v>292</v>
       </c>
       <c r="G79" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -5442,28 +5448,28 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="D80" s="2">
-        <v>2016.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E80" s="2">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="F80" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -5486,28 +5492,28 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D81" s="2">
-        <v>2021.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E81" s="2">
         <v>17.0</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>299</v>
+        <v>25</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -5530,28 +5536,28 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D82" s="2">
-        <v>2019.0</v>
+        <v>1982.0</v>
       </c>
       <c r="E82" s="2">
         <v>17.0</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -5574,28 +5580,28 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D83" s="2">
-        <v>1982.0</v>
+        <v>1977.0</v>
       </c>
       <c r="E83" s="2">
         <v>17.0</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -5618,28 +5624,28 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="D84" s="2">
-        <v>1977.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E84" s="2">
         <v>17.0</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -5662,28 +5668,28 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="D85" s="2">
-        <v>2017.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E85" s="2">
         <v>17.0</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -5706,28 +5712,28 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="D86" s="2">
-        <v>2015.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E86" s="2">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -5750,22 +5756,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>118</v>
+        <v>311</v>
       </c>
       <c r="D87" s="2">
-        <v>1995.0</v>
+        <v>1993.0</v>
       </c>
       <c r="E87" s="2">
         <v>16.0</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>312</v>
@@ -5803,13 +5809,13 @@
         <v>315</v>
       </c>
       <c r="D88" s="2">
-        <v>1993.0</v>
+        <v>2001.0</v>
       </c>
       <c r="E88" s="2">
         <v>16.0</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>316</v>
@@ -5844,22 +5850,22 @@
         <v>9</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>319</v>
+        <v>73</v>
       </c>
       <c r="D89" s="2">
-        <v>2001.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E89" s="2">
         <v>16.0</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>320</v>
+        <v>73</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -5882,25 +5888,25 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>64</v>
+        <v>321</v>
       </c>
       <c r="D90" s="2">
-        <v>2013.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E90" s="2">
         <v>16.0</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>64</v>
+        <v>322</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>323</v>
@@ -5932,22 +5938,22 @@
         <v>9</v>
       </c>
       <c r="C91" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D91" s="2">
+        <v>1999.0</v>
+      </c>
+      <c r="E91" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D91" s="2">
-        <v>1976.0</v>
-      </c>
-      <c r="E91" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G91" s="1" t="s">
+      <c r="H91" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
@@ -5970,28 +5976,28 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="D92" s="2">
-        <v>1999.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E92" s="2">
         <v>15.0</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G92" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H92" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -6014,28 +6020,28 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="D93" s="2">
-        <v>2007.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E93" s="2">
         <v>15.0</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G93" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>333</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -6058,22 +6064,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="D94" s="2">
-        <v>2018.0</v>
+        <v>2024.0</v>
       </c>
       <c r="E94" s="2">
         <v>15.0</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>31</v>
+        <v>334</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>335</v>
@@ -6108,22 +6114,22 @@
         <v>9</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="D95" s="2">
-        <v>2024.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E95" s="2">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="H95" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -6146,22 +6152,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D96" s="2">
-        <v>2007.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E96" s="2">
         <v>14.0</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>31</v>
+        <v>341</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>342</v>
@@ -6196,22 +6202,22 @@
         <v>9</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="D97" s="2">
-        <v>2019.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E97" s="2">
         <v>14.0</v>
       </c>
       <c r="F97" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G97" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="H97" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>347</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -6234,22 +6240,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>35</v>
+        <v>348</v>
       </c>
       <c r="D98" s="2">
-        <v>2020.0</v>
+        <v>1969.0</v>
       </c>
       <c r="E98" s="2">
         <v>14.0</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>349</v>
@@ -6284,22 +6290,22 @@
         <v>9</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>352</v>
+        <v>311</v>
       </c>
       <c r="D99" s="2">
-        <v>1969.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E99" s="2">
         <v>14.0</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>353</v>
+        <v>311</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -6322,28 +6328,28 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>315</v>
+        <v>119</v>
       </c>
       <c r="D100" s="2">
-        <v>2000.0</v>
+        <v>1987.0</v>
       </c>
       <c r="E100" s="2">
         <v>14.0</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -6366,28 +6372,26 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>123</v>
+        <v>357</v>
       </c>
       <c r="D101" s="2">
-        <v>1987.0</v>
+        <v>2008.0</v>
       </c>
       <c r="E101" s="2">
         <v>14.0</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -6410,26 +6414,28 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>361</v>
+        <v>321</v>
       </c>
       <c r="D102" s="2">
-        <v>2008.0</v>
+        <v>1994.0</v>
       </c>
       <c r="E102" s="2">
         <v>14.0</v>
       </c>
-      <c r="F102" s="1"/>
+      <c r="F102" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G102" s="1" t="s">
-        <v>59</v>
+        <v>360</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -6452,22 +6458,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>325</v>
+        <v>63</v>
       </c>
       <c r="D103" s="2">
-        <v>1994.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E103" s="2">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>31</v>
+        <v>363</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>364</v>
@@ -6502,16 +6508,16 @@
         <v>9</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>59</v>
+        <v>367</v>
       </c>
       <c r="D104" s="2">
-        <v>1997.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E104" s="2">
         <v>13.0</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>367</v>
+        <v>36</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>368</v>
@@ -6549,14 +6555,12 @@
         <v>371</v>
       </c>
       <c r="D105" s="2">
-        <v>1981.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E105" s="2">
         <v>13.0</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="F105" s="1"/>
       <c r="G105" s="1" t="s">
         <v>372</v>
       </c>
@@ -6590,20 +6594,22 @@
         <v>9</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>375</v>
+        <v>63</v>
       </c>
       <c r="D106" s="2">
-        <v>2013.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E106" s="2">
         <v>13.0</v>
       </c>
-      <c r="F106" s="1"/>
+      <c r="F106" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G106" s="1" t="s">
-        <v>376</v>
+        <v>63</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -6626,28 +6632,28 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="D107" s="2">
-        <v>2015.0</v>
+        <v>1980.0</v>
       </c>
       <c r="E107" s="2">
         <v>13.0</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -6670,28 +6676,28 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D108" s="2">
-        <v>1980.0</v>
+        <v>1983.0</v>
       </c>
       <c r="E108" s="2">
         <v>13.0</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -6714,28 +6720,28 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>59</v>
+        <v>321</v>
       </c>
       <c r="D109" s="2">
-        <v>1983.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E109" s="2">
         <v>13.0</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>59</v>
+        <v>321</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6758,25 +6764,25 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="D110" s="2">
-        <v>2020.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E110" s="2">
         <v>13.0</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>31</v>
+        <v>383</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>385</v>
@@ -6808,10 +6814,10 @@
         <v>9</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D111" s="2">
-        <v>2021.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E111" s="2">
         <v>13.0</v>
@@ -6852,22 +6858,22 @@
         <v>9</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>40</v>
+        <v>195</v>
       </c>
       <c r="D112" s="2">
-        <v>2019.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E112" s="2">
         <v>13.0</v>
       </c>
       <c r="F112" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G112" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="G112" s="1" t="s">
+      <c r="H112" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6890,28 +6896,28 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>199</v>
+        <v>40</v>
       </c>
       <c r="D113" s="2">
-        <v>2010.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E113" s="2">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>31</v>
+        <v>394</v>
       </c>
       <c r="G113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H113" s="3" t="s">
         <v>395</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6934,13 +6940,13 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D114" s="2">
         <v>2017.0</v>
@@ -6949,13 +6955,13 @@
         <v>12.0</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -6978,13 +6984,13 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D115" s="2">
         <v>2023.0</v>
@@ -6993,13 +6999,13 @@
         <v>12.0</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G115" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="H115" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -7022,13 +7028,13 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D116" s="2">
         <v>2017.0</v>
@@ -7037,13 +7043,13 @@
         <v>12.0</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -7066,13 +7072,13 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D117" s="2">
         <v>2013.0</v>
@@ -7081,13 +7087,13 @@
         <v>12.0</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G117" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H117" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>406</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -7110,13 +7116,13 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D118" s="2">
         <v>1990.0</v>
@@ -7125,13 +7131,13 @@
         <v>12.0</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
@@ -7154,13 +7160,13 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D119" s="2">
         <v>2006.0</v>
@@ -7169,10 +7175,10 @@
         <v>12.0</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -7196,13 +7202,13 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D120" s="2">
         <v>1964.0</v>
@@ -7211,13 +7217,13 @@
         <v>11.0</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
@@ -7240,13 +7246,13 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D121" s="2">
         <v>1993.0</v>
@@ -7255,13 +7261,13 @@
         <v>11.0</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
@@ -7284,13 +7290,13 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D122" s="2">
         <v>1958.0</v>
@@ -7299,13 +7305,13 @@
         <v>11.0</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G122" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H122" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
@@ -7328,13 +7334,13 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D123" s="2">
         <v>1950.0</v>
@@ -7343,13 +7349,13 @@
         <v>11.0</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
@@ -7372,13 +7378,13 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D124" s="2">
         <v>1947.0</v>
@@ -7387,13 +7393,13 @@
         <v>11.0</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G124" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>421</v>
       </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
@@ -7416,13 +7422,13 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D125" s="2">
         <v>2007.0</v>
@@ -7431,13 +7437,13 @@
         <v>11.0</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G125" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H125" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>424</v>
       </c>
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
@@ -7460,13 +7466,13 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D126" s="2">
         <v>2011.0</v>
@@ -7475,13 +7481,13 @@
         <v>11.0</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G126" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
@@ -7504,26 +7510,26 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="2">
         <v>11.0</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G127" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H127" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>430</v>
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
@@ -7546,13 +7552,13 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D128" s="2">
         <v>2022.0</v>
@@ -7561,13 +7567,13 @@
         <v>10.0</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
@@ -7590,13 +7596,13 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D129" s="2">
         <v>2016.0</v>
@@ -7605,13 +7611,13 @@
         <v>10.0</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G129" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="H129" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="H129" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
@@ -7634,13 +7640,13 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D130" s="2">
         <v>2018.0</v>
@@ -7649,13 +7655,13 @@
         <v>10.0</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G130" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H130" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -7678,7 +7684,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>9</v>
@@ -7693,13 +7699,13 @@
         <v>10.0</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -7722,13 +7728,13 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D132" s="2">
         <v>2022.0</v>
@@ -7737,13 +7743,13 @@
         <v>10.0</v>
       </c>
       <c r="F132" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G132" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="G132" s="1" t="s">
+      <c r="H132" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="H132" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -7766,7 +7772,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>9</v>
@@ -7781,13 +7787,13 @@
         <v>10.0</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G133" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="H133" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="H133" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -7810,13 +7816,13 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D134" s="2">
         <v>2015.0</v>
@@ -7825,13 +7831,13 @@
         <v>10.0</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G134" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H134" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>450</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -7854,13 +7860,13 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D135" s="2">
         <v>2005.0</v>
@@ -7869,13 +7875,13 @@
         <v>10.0</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -7898,13 +7904,13 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D136" s="2">
         <v>1999.0</v>
@@ -7913,13 +7919,13 @@
         <v>10.0</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G136" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -7942,13 +7948,13 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D137" s="2">
         <v>2019.0</v>
@@ -7957,13 +7963,13 @@
         <v>10.0</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -7986,13 +7992,13 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D138" s="2">
         <v>2009.0</v>
@@ -8001,13 +8007,13 @@
         <v>10.0</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -8030,13 +8036,13 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D139" s="2">
         <v>2002.0</v>
@@ -8045,13 +8051,13 @@
         <v>9.0</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -8074,13 +8080,13 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D140" s="2">
         <v>1951.0</v>
@@ -8089,13 +8095,13 @@
         <v>9.0</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -8118,7 +8124,7 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>9</v>
@@ -8133,13 +8139,13 @@
         <v>9.0</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
@@ -8162,13 +8168,13 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D142" s="2">
         <v>1998.0</v>
@@ -8177,13 +8183,13 @@
         <v>9.0</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G142" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="H142" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="H142" s="3" t="s">
-        <v>468</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -8206,13 +8212,13 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D143" s="2">
         <v>2003.0</v>
@@ -8221,13 +8227,13 @@
         <v>9.0</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -8250,13 +8256,13 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D144" s="2">
         <v>2019.0</v>
@@ -8265,13 +8271,13 @@
         <v>9.0</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -8294,13 +8300,13 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D145" s="2">
         <v>2021.0</v>
@@ -8310,10 +8316,10 @@
       </c>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="H145" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="H145" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -8336,13 +8342,13 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D146" s="2">
         <v>2021.0</v>
@@ -8351,13 +8357,13 @@
         <v>9.0</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G146" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="H146" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="H146" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -8380,13 +8386,13 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D147" s="2">
         <v>1998.0</v>
@@ -8395,13 +8401,13 @@
         <v>8.0</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
@@ -8424,7 +8430,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>9</v>
@@ -8439,13 +8445,13 @@
         <v>8.0</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G148" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="H148" s="3" t="s">
         <v>482</v>
-      </c>
-      <c r="H148" s="3" t="s">
-        <v>483</v>
       </c>
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
@@ -8468,13 +8474,13 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D149" s="2">
         <v>2004.0</v>
@@ -8483,13 +8489,13 @@
         <v>8.0</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I149" s="1"/>
       <c r="J149" s="1"/>
@@ -8512,13 +8518,13 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D150" s="2">
         <v>2017.0</v>
@@ -8527,13 +8533,13 @@
         <v>8.0</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
@@ -8556,13 +8562,13 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D151" s="2">
         <v>2014.0</v>
@@ -8571,13 +8577,13 @@
         <v>8.0</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
@@ -8600,13 +8606,13 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D152" s="2">
         <v>2024.0</v>
@@ -8616,10 +8622,10 @@
       </c>
       <c r="F152" s="1"/>
       <c r="G152" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
@@ -8642,23 +8648,27 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C153" s="1"/>
+      <c r="C153" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="D153" s="2">
-        <v>2021.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E153" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="H153" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>492</v>
+      </c>
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
       <c r="K153" s="1"/>
@@ -8680,29 +8690,23 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="C154" s="1"/>
       <c r="D154" s="2">
-        <v>2023.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E154" s="2">
         <v>7.0</v>
       </c>
-      <c r="F154" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="F154" s="1"/>
       <c r="G154" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H154" s="3" t="s">
-        <v>495</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="H154" s="1"/>
       <c r="I154" s="1"/>
       <c r="J154" s="1"/>
       <c r="K154" s="1"/>
@@ -8724,13 +8728,13 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D155" s="2">
         <v>2009.0</v>
@@ -8740,10 +8744,10 @@
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H155" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="H155" s="3" t="s">
-        <v>498</v>
       </c>
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
@@ -8766,13 +8770,13 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D156" s="2">
         <v>2010.0</v>
@@ -8781,13 +8785,13 @@
         <v>7.0</v>
       </c>
       <c r="F156" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H156" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H156" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
@@ -8810,13 +8814,13 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D157" s="2">
         <v>2018.0</v>
@@ -8825,13 +8829,13 @@
         <v>7.0</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
@@ -8854,7 +8858,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>9</v>
@@ -8869,13 +8873,13 @@
         <v>7.0</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
@@ -8898,13 +8902,13 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D159" s="2">
         <v>2005.0</v>
@@ -8914,10 +8918,10 @@
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -8940,13 +8944,13 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D160" s="2">
         <v>1981.0</v>
@@ -8955,13 +8959,13 @@
         <v>6.0</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -8984,13 +8988,13 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D161" s="2">
         <v>1964.0</v>
@@ -9000,10 +9004,10 @@
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
@@ -9026,25 +9030,23 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D162" s="2">
-        <v>2009.0</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="D162" s="1"/>
       <c r="E162" s="2">
         <v>6.0</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>123</v>
+        <v>512</v>
       </c>
       <c r="H162" s="3" t="s">
         <v>513</v>
@@ -9076,19 +9078,19 @@
         <v>9</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="D163" s="2">
-        <v>2018.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E163" s="2">
         <v>6.0</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="H163" s="3" t="s">
         <v>515</v>
@@ -9120,22 +9122,22 @@
         <v>9</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D164" s="2">
-        <v>1966.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E164" s="2">
         <v>6.0</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H164" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="H164" s="3" t="s">
-        <v>518</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -9158,28 +9160,28 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>420</v>
+        <v>96</v>
       </c>
       <c r="D165" s="2">
-        <v>2010.0</v>
+        <v>1966.0</v>
       </c>
       <c r="E165" s="2">
         <v>6.0</v>
       </c>
       <c r="F165" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H165" s="3" t="s">
         <v>520</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="H165" s="3" t="s">
-        <v>521</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -9202,13 +9204,13 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>89</v>
+        <v>419</v>
       </c>
       <c r="D166" s="2">
         <v>2010.0</v>
@@ -9217,13 +9219,13 @@
         <v>6.0</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>31</v>
+        <v>522</v>
       </c>
       <c r="G166" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H166" s="3" t="s">
         <v>523</v>
-      </c>
-      <c r="H166" s="3" t="s">
-        <v>524</v>
       </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
@@ -9246,25 +9248,25 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D167" s="2">
-        <v>2023.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E167" s="2">
         <v>6.0</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>68</v>
+        <v>525</v>
       </c>
       <c r="H167" s="3" t="s">
         <v>526</v>
@@ -9296,19 +9298,19 @@
         <v>9</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="D168" s="2">
-        <v>1985.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E168" s="2">
         <v>6.0</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="H168" s="3" t="s">
         <v>528</v>
@@ -9340,19 +9342,19 @@
         <v>9</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="D169" s="2">
-        <v>2018.0</v>
+        <v>1985.0</v>
       </c>
       <c r="E169" s="2">
         <v>6.0</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="H169" s="3" t="s">
         <v>530</v>
@@ -9384,19 +9386,19 @@
         <v>9</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="D170" s="2">
-        <v>2019.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E170" s="2">
         <v>6.0</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="H170" s="3" t="s">
         <v>532</v>
@@ -9428,22 +9430,22 @@
         <v>9</v>
       </c>
       <c r="C171" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D171" s="2">
+        <v>2019.0</v>
+      </c>
+      <c r="E171" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H171" s="3" t="s">
         <v>534</v>
-      </c>
-      <c r="D171" s="2">
-        <v>2006.0</v>
-      </c>
-      <c r="E171" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="H171" s="3" t="s">
-        <v>535</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -9466,23 +9468,25 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>182</v>
+        <v>536</v>
       </c>
       <c r="D172" s="2">
-        <v>1981.0</v>
+        <v>2006.0</v>
       </c>
       <c r="E172" s="2">
         <v>5.0</v>
       </c>
-      <c r="F172" s="1"/>
+      <c r="F172" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G172" s="1" t="s">
-        <v>182</v>
+        <v>536</v>
       </c>
       <c r="H172" s="3" t="s">
         <v>537</v>
@@ -9514,19 +9518,17 @@
         <v>9</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="D173" s="2">
-        <v>2012.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E173" s="2">
         <v>5.0</v>
       </c>
-      <c r="F173" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="F173" s="1"/>
       <c r="G173" s="1" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="H173" s="3" t="s">
         <v>539</v>
@@ -9558,17 +9560,19 @@
         <v>9</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D174" s="2">
-        <v>2016.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E174" s="2">
         <v>5.0</v>
       </c>
-      <c r="F174" s="1"/>
+      <c r="F174" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G174" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H174" s="3" t="s">
         <v>541</v>
@@ -9600,19 +9604,17 @@
         <v>9</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>208</v>
+        <v>68</v>
       </c>
       <c r="D175" s="2">
-        <v>2018.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E175" s="2">
         <v>5.0</v>
       </c>
-      <c r="F175" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="F175" s="1"/>
       <c r="G175" s="1" t="s">
-        <v>208</v>
+        <v>68</v>
       </c>
       <c r="H175" s="3" t="s">
         <v>543</v>
@@ -9644,22 +9646,22 @@
         <v>9</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>50</v>
+        <v>204</v>
       </c>
       <c r="D176" s="2">
-        <v>1978.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E176" s="2">
         <v>5.0</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G176" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H176" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="H176" s="3" t="s">
-        <v>546</v>
       </c>
       <c r="I176" s="1"/>
       <c r="J176" s="1"/>
@@ -9682,23 +9684,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D177" s="2">
-        <v>2019.0</v>
+        <v>1978.0</v>
       </c>
       <c r="E177" s="2">
         <v>5.0</v>
       </c>
-      <c r="F177" s="1"/>
+      <c r="F177" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G177" s="1" t="s">
-        <v>59</v>
+        <v>547</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>548</v>
@@ -9730,19 +9734,17 @@
         <v>9</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D178" s="2">
-        <v>2021.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E178" s="2">
         <v>5.0</v>
       </c>
-      <c r="F178" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="F178" s="1"/>
       <c r="G178" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="H178" s="3" t="s">
         <v>550</v>
@@ -9774,19 +9776,19 @@
         <v>9</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D179" s="2">
-        <v>2002.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E179" s="2">
         <v>5.0</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>552</v>
@@ -9818,22 +9820,22 @@
         <v>9</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="D180" s="2">
-        <v>2022.0</v>
+        <v>2002.0</v>
       </c>
       <c r="E180" s="2">
         <v>5.0</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G180" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H180" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="H180" s="3" t="s">
-        <v>555</v>
       </c>
       <c r="I180" s="1"/>
       <c r="J180" s="1"/>
@@ -9856,25 +9858,25 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="D181" s="2">
-        <v>2017.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E181" s="2">
         <v>5.0</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>191</v>
+        <v>556</v>
       </c>
       <c r="H181" s="3" t="s">
         <v>557</v>
@@ -9906,17 +9908,19 @@
         <v>9</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="D182" s="2">
-        <v>2009.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E182" s="2">
         <v>5.0</v>
       </c>
-      <c r="F182" s="1"/>
+      <c r="F182" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G182" s="1" t="s">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>559</v>
@@ -9941,14 +9945,28 @@
       <c r="Z182" s="1"/>
     </row>
     <row r="183">
-      <c r="A183" s="1"/>
-      <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
-      <c r="E183" s="1"/>
+      <c r="A183" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D183" s="2">
+        <v>2009.0</v>
+      </c>
+      <c r="E183" s="2">
+        <v>5.0</v>
+      </c>
       <c r="F183" s="1"/>
-      <c r="G183" s="1"/>
-      <c r="H183" s="1"/>
+      <c r="G183" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>561</v>
+      </c>
       <c r="I183" s="1"/>
       <c r="J183" s="1"/>
       <c r="K183" s="1"/>
@@ -32890,8 +32908,8 @@
     <hyperlink r:id="rId42" ref="H43"/>
     <hyperlink r:id="rId43" ref="H44"/>
     <hyperlink r:id="rId44" ref="H45"/>
-    <hyperlink r:id="rId45" ref="H46"/>
-    <hyperlink r:id="rId46" ref="F47"/>
+    <hyperlink r:id="rId45" ref="F46"/>
+    <hyperlink r:id="rId46" ref="H46"/>
     <hyperlink r:id="rId47" ref="H47"/>
     <hyperlink r:id="rId48" ref="H48"/>
     <hyperlink r:id="rId49" ref="H49"/>
@@ -32997,7 +33015,7 @@
     <hyperlink r:id="rId149" ref="H150"/>
     <hyperlink r:id="rId150" ref="H151"/>
     <hyperlink r:id="rId151" ref="H152"/>
-    <hyperlink r:id="rId152" ref="H154"/>
+    <hyperlink r:id="rId152" ref="H153"/>
     <hyperlink r:id="rId153" ref="H155"/>
     <hyperlink r:id="rId154" ref="H156"/>
     <hyperlink r:id="rId155" ref="H157"/>
@@ -33026,7 +33044,8 @@
     <hyperlink r:id="rId178" ref="H180"/>
     <hyperlink r:id="rId179" ref="H181"/>
     <hyperlink r:id="rId180" ref="H182"/>
+    <hyperlink r:id="rId181" ref="H183"/>
   </hyperlinks>
-  <drawing r:id="rId181"/>
+  <drawing r:id="rId182"/>
 </worksheet>
 </file>
--- a/Car_Wash_Advisory_Companies.xlsx
+++ b/Car_Wash_Advisory_Companies.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="577">
   <si>
     <t>Company Name</t>
   </si>
@@ -70,6 +70,21 @@
     <t>https://mistercarwash.com/</t>
   </si>
   <si>
+    <t>Quick Quack Car Wash</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>Texas | Colorado | Utah | Arizona | California | Hawaii | Nevada | Oklahoma | Washington</t>
+  </si>
+  <si>
+    <t>https://www.dontdrivedirty.com/</t>
+  </si>
+  <si>
     <t>Tidal Wave Auto Spa</t>
   </si>
   <si>
@@ -85,21 +100,6 @@
     <t>https://www.tidalwaveautospa.com/</t>
   </si>
   <si>
-    <t>Quick Quack Car Wash</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>KKR</t>
-  </si>
-  <si>
-    <t>Texas | Colorado | Utah | Arizona | California</t>
-  </si>
-  <si>
-    <t>https://www.dontdrivedirty.com/</t>
-  </si>
-  <si>
     <t>Club Car Wash</t>
   </si>
   <si>
@@ -187,6 +187,21 @@
     <t>https://gocarwash.com/</t>
   </si>
   <si>
+    <t>WhiteWater Express Car Wash</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Freeman Spogil &amp; Co.</t>
+  </si>
+  <si>
+    <t>Texas | Oklahoma | Louisiana | Kentucky | Ohio | Michigan | South Carolina | Georgia</t>
+  </si>
+  <si>
+    <t>https://www.whitewatercw.com/</t>
+  </si>
+  <si>
     <t>Mammoth Holdings LLC</t>
   </si>
   <si>
@@ -199,19 +214,16 @@
     <t>https://mammothholdings.com/</t>
   </si>
   <si>
-    <t>WhiteWater Express Car Wash</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>Freeman Spogil &amp; Co.</t>
-  </si>
-  <si>
-    <t>Texas | Oklahoma | Louisiana | Kentucky | Ohio | Michigan | South Carolina</t>
-  </si>
-  <si>
-    <t>https://www.whitewatercw.com/</t>
+    <t>Express Wash Concepts</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Ohio | Virginia | Pennsylvania | North Carolina | Indiana | Michigan</t>
+  </si>
+  <si>
+    <t>https://www.expresswashconcepts.com/</t>
   </si>
   <si>
     <t>ModWash</t>
@@ -229,18 +241,6 @@
     <t>https://www.modwash.com/</t>
   </si>
   <si>
-    <t>Express Wash Concepts</t>
-  </si>
-  <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Ohio | Virginia | Pennsylvania | North Carolina | Indiana | Michigan</t>
-  </si>
-  <si>
-    <t>https://www.expresswashconcepts.com/</t>
-  </si>
-  <si>
     <t>Summit Wash Holdings</t>
   </si>
   <si>
@@ -256,6 +256,18 @@
     <t>https://summitwashholdings.com</t>
   </si>
   <si>
+    <t>El Car Wash</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Warburg Pincus</t>
+  </si>
+  <si>
+    <t>https://elcarwash.com/</t>
+  </si>
+  <si>
     <t>Autobell Car Wash</t>
   </si>
   <si>
@@ -265,18 +277,6 @@
     <t>https://www.autobell.com/</t>
   </si>
   <si>
-    <t>El Car Wash</t>
-  </si>
-  <si>
-    <t>Florida</t>
-  </si>
-  <si>
-    <t>Warburg Pincus</t>
-  </si>
-  <si>
-    <t>https://elcarwash.com/</t>
-  </si>
-  <si>
     <t>ClearWater Express Wash</t>
   </si>
   <si>
@@ -388,6 +388,15 @@
     <t>https://champxpress.com/</t>
   </si>
   <si>
+    <t>Brown Bear Car Wash</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>https://www.brownbear.com/</t>
+  </si>
+  <si>
     <t>Crew Carwash</t>
   </si>
   <si>
@@ -463,15 +472,6 @@
     <t>https://www.bigdanscarwash.com/</t>
   </si>
   <si>
-    <t>Brown Bear Car Wash</t>
-  </si>
-  <si>
-    <t>Washington</t>
-  </si>
-  <si>
-    <t>https://www.brownbear.com/</t>
-  </si>
-  <si>
     <t>Mr. Clean Car Wash</t>
   </si>
   <si>
@@ -622,6 +622,12 @@
     <t>https://quicknclean.net/</t>
   </si>
   <si>
+    <t>Soapy Joe’s Car Wash</t>
+  </si>
+  <si>
+    <t>https://soapyjoescarwash.com/</t>
+  </si>
+  <si>
     <t>Thoroughbred Express Auto Wash</t>
   </si>
   <si>
@@ -664,12 +670,6 @@
     <t>https://rocketcarwash.com/</t>
   </si>
   <si>
-    <t>Soapy Joe’s Car Wash</t>
-  </si>
-  <si>
-    <t>https://soapyjoescarwash.com/</t>
-  </si>
-  <si>
     <t>Wash Masters Car Wash</t>
   </si>
   <si>
@@ -691,6 +691,12 @@
     <t>https://washvillecarwash.com/</t>
   </si>
   <si>
+    <t>Dash Car Wash</t>
+  </si>
+  <si>
+    <t>Arizona | Nevada</t>
+  </si>
+  <si>
     <t>Fast 5 Xpress Car Wash</t>
   </si>
   <si>
@@ -706,18 +712,6 @@
     <t>https://www.glidexwash.com/</t>
   </si>
   <si>
-    <t>Ultra Clean Express</t>
-  </si>
-  <si>
-    <t>Lindsay Goldberg</t>
-  </si>
-  <si>
-    <t>Arizona | Nevada</t>
-  </si>
-  <si>
-    <t>https://dashcarwash.com/</t>
-  </si>
-  <si>
     <t>Carnation Auto Spa</t>
   </si>
   <si>
@@ -928,6 +922,12 @@
     <t>https://gateexpresscarwash.com/</t>
   </si>
   <si>
+    <t>Raindrop Car Wash</t>
+  </si>
+  <si>
+    <t>https://raindropcarwash.com/</t>
+  </si>
+  <si>
     <t>Zax Auto Wash</t>
   </si>
   <si>
@@ -1216,12 +1216,6 @@
     <t>https://hang10carwash.com/</t>
   </si>
   <si>
-    <t>Raindrop Car Wash</t>
-  </si>
-  <si>
-    <t>https://raindropcarwash.com/</t>
-  </si>
-  <si>
     <t>RocketFast Car Wash</t>
   </si>
   <si>
@@ -1303,6 +1297,36 @@
     <t>https://timeitxpresswash.com/</t>
   </si>
   <si>
+    <t>Classy Chassis</t>
+  </si>
+  <si>
+    <t>https://classychassis.com/</t>
+  </si>
+  <si>
+    <t>Genie Car Wash</t>
+  </si>
+  <si>
+    <t>California | Arizona</t>
+  </si>
+  <si>
+    <t>https://www.geniecarwash.com/</t>
+  </si>
+  <si>
+    <t>Halo Car Wash</t>
+  </si>
+  <si>
+    <t>Ontario</t>
+  </si>
+  <si>
+    <t>https://halowash.com/</t>
+  </si>
+  <si>
+    <t>Valet Car Wash</t>
+  </si>
+  <si>
+    <t>https://washmycar.ca/</t>
+  </si>
+  <si>
     <t>Blue Penguin Car Wash</t>
   </si>
   <si>
@@ -1390,6 +1414,12 @@
     <t>https://washguystx.com/</t>
   </si>
   <si>
+    <t>Sparkle Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://sparklestatus.com/</t>
+  </si>
+  <si>
     <t>Auto Spa Car Wash (WA)</t>
   </si>
   <si>
@@ -1492,12 +1522,6 @@
     <t>https://oceancarwashtx.com/</t>
   </si>
   <si>
-    <t>Dash Car Wash</t>
-  </si>
-  <si>
-    <t>Arizona | Texas | Nevada</t>
-  </si>
-  <si>
     <t>Greenhill Car Wash</t>
   </si>
   <si>
@@ -1555,12 +1579,6 @@
     <t>https://bluetidecarwash.com/</t>
   </si>
   <si>
-    <t>Canton Car Wash</t>
-  </si>
-  <si>
-    <t>https://cantoncarwash.com/</t>
-  </si>
-  <si>
     <t>Endless Clean Car Wash</t>
   </si>
   <si>
@@ -1618,6 +1636,21 @@
     <t>https://supershinexpress.com/</t>
   </si>
   <si>
+    <t>Mint Smartwash</t>
+  </si>
+  <si>
+    <t>Alberta</t>
+  </si>
+  <si>
+    <t>https://mintsmartwash.com/</t>
+  </si>
+  <si>
+    <t>Great White Car Wash</t>
+  </si>
+  <si>
+    <t>https://greatwhitewash.com/</t>
+  </si>
+  <si>
     <t>5 Minute Express Car Wash</t>
   </si>
   <si>
@@ -1697,6 +1730,18 @@
   </si>
   <si>
     <t>https://www.fasttrakcarwash.com/</t>
+  </si>
+  <si>
+    <t>Mint Express</t>
+  </si>
+  <si>
+    <t>https://www.mintexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>Bubbles Car Washes and Detail Centres</t>
+  </si>
+  <si>
+    <t>https://bubbles.ca/</t>
   </si>
 </sst>
 </file>
@@ -2113,10 +2158,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="2">
-        <v>1999.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E4" s="2">
-        <v>308.0</v>
+        <v>350.0</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>21</v>
@@ -2157,10 +2202,10 @@
         <v>25</v>
       </c>
       <c r="D5" s="2">
-        <v>2004.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E5" s="2">
-        <v>275.0</v>
+        <v>308.0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>26</v>
@@ -2462,22 +2507,22 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2">
-        <v>2002.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E12" s="2">
-        <v>150.0</v>
+        <v>154.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -2500,19 +2545,19 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2">
-        <v>2015.0</v>
+        <v>2002.0</v>
       </c>
       <c r="E13" s="2">
-        <v>141.0</v>
+        <v>150.0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>64</v>
@@ -2553,19 +2598,19 @@
         <v>68</v>
       </c>
       <c r="D14" s="2">
-        <v>2020.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E14" s="2">
-        <v>130.0</v>
+        <v>141.0</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -2588,22 +2633,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2020.0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>130.0</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2018.0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>127.0</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>74</v>
@@ -2682,22 +2727,22 @@
         <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="D17" s="2">
-        <v>1969.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E17" s="2">
-        <v>91.0</v>
+        <v>100.0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>82</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -2720,25 +2765,25 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2">
-        <v>2010.0</v>
+        <v>1969.0</v>
       </c>
       <c r="E18" s="2">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>87</v>
@@ -2770,7 +2815,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D19" s="2">
         <v>2021.0</v>
@@ -2864,7 +2909,7 @@
         <v>1981.0</v>
       </c>
       <c r="E21" s="2">
-        <v>71.0</v>
+        <v>77.0</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>97</v>
@@ -2990,7 +3035,7 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D24" s="2">
         <v>2019.0</v>
@@ -3122,7 +3167,7 @@
         <v>9</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2">
         <v>2015.0</v>
@@ -3169,19 +3214,19 @@
         <v>126</v>
       </c>
       <c r="D28" s="2">
-        <v>1948.0</v>
+        <v>1957.0</v>
       </c>
       <c r="E28" s="2">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -3204,16 +3249,16 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="D29" s="2">
-        <v>2012.0</v>
+        <v>1948.0</v>
       </c>
       <c r="E29" s="2">
         <v>50.0</v>
@@ -3254,22 +3299,22 @@
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2">
-        <v>1953.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E30" s="2">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="F30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -3292,28 +3337,28 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2">
-        <v>1997.0</v>
+        <v>1953.0</v>
       </c>
       <c r="E31" s="2">
         <v>49.0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -3336,28 +3381,28 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="D32" s="2">
-        <v>1959.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E32" s="2">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -3380,28 +3425,28 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>15</v>
+        <v>142</v>
       </c>
       <c r="D33" s="2">
-        <v>2009.0</v>
+        <v>1959.0</v>
       </c>
       <c r="E33" s="2">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="F33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -3424,28 +3469,28 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D34" s="2">
-        <v>2020.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E34" s="2">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -3468,22 +3513,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="D35" s="2">
-        <v>1957.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E35" s="2">
         <v>45.0</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>151</v>
@@ -3518,7 +3563,7 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D36" s="2">
         <v>1988.0</v>
@@ -3562,7 +3607,7 @@
         <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D37" s="2">
         <v>1995.0</v>
@@ -3606,7 +3651,7 @@
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D38" s="2">
         <v>2013.0</v>
@@ -3694,7 +3739,7 @@
         <v>9</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D40" s="2">
         <v>1948.0</v>
@@ -3738,7 +3783,7 @@
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D41" s="2">
         <v>2011.0</v>
@@ -3782,7 +3827,7 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D42" s="2">
         <v>2018.0</v>
@@ -3870,7 +3915,7 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2">
         <v>1986.0</v>
@@ -3882,7 +3927,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>182</v>
@@ -4178,22 +4223,22 @@
         <v>9</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2011.0</v>
+      </c>
+      <c r="E51" s="2">
+        <v>27.0</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="D51" s="2">
-        <v>2020.0</v>
-      </c>
-      <c r="E51" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -4216,28 +4261,28 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>63</v>
+        <v>206</v>
       </c>
       <c r="D52" s="2">
-        <v>2004.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E52" s="2">
         <v>26.0</v>
       </c>
       <c r="F52" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -4260,28 +4305,28 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2004.0</v>
+      </c>
+      <c r="E53" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="D53" s="2">
-        <v>2000.0</v>
-      </c>
-      <c r="E53" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -4304,25 +4349,25 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>25</v>
+        <v>215</v>
       </c>
       <c r="D54" s="2">
-        <v>2011.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E54" s="2">
         <v>25.0</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>36</v>
+        <v>216</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>25</v>
+        <v>217</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>218</v>
@@ -4354,7 +4399,7 @@
         <v>9</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D55" s="2">
         <v>2004.0</v>
@@ -4366,7 +4411,7 @@
         <v>220</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>221</v>
@@ -4441,24 +4486,18 @@
       <c r="B57" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="C57" s="1"/>
       <c r="D57" s="2">
-        <v>2013.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E57" s="2">
         <v>24.0</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F57" s="1"/>
       <c r="G57" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H57" s="3" t="s">
         <v>227</v>
       </c>
+      <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -4486,10 +4525,10 @@
         <v>9</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D58" s="2">
-        <v>2018.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E58" s="2">
         <v>24.0</v>
@@ -4498,10 +4537,10 @@
         <v>36</v>
       </c>
       <c r="G58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -4524,28 +4563,28 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="D59" s="2">
-        <v>2021.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E59" s="2">
         <v>24.0</v>
       </c>
       <c r="F59" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -4568,13 +4607,13 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D60" s="2">
         <v>2021.0</v>
@@ -4583,13 +4622,13 @@
         <v>23.0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -4612,13 +4651,13 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D61" s="2">
         <v>2012.0</v>
@@ -4630,10 +4669,10 @@
         <v>36</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -4656,13 +4695,13 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D62" s="2">
         <v>1959.0</v>
@@ -4671,13 +4710,13 @@
         <v>23.0</v>
       </c>
       <c r="F62" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>245</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -4700,7 +4739,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
@@ -4718,10 +4757,10 @@
         <v>36</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -4744,7 +4783,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>9</v>
@@ -4765,7 +4804,7 @@
         <v>45</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -4788,13 +4827,13 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D65" s="2">
         <v>2019.0</v>
@@ -4806,10 +4845,10 @@
         <v>36</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -4832,13 +4871,13 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D66" s="2">
         <v>2019.0</v>
@@ -4847,13 +4886,13 @@
         <v>21.0</v>
       </c>
       <c r="F66" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H66" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -4876,13 +4915,13 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D67" s="2">
         <v>2016.0</v>
@@ -4894,10 +4933,10 @@
         <v>36</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
@@ -4920,13 +4959,13 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D68" s="2">
         <v>1997.0</v>
@@ -4938,10 +4977,10 @@
         <v>36</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
@@ -4964,7 +5003,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>9</v>
@@ -4982,10 +5021,10 @@
         <v>36</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
@@ -5008,13 +5047,13 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D70" s="2">
         <v>2019.0</v>
@@ -5026,10 +5065,10 @@
         <v>36</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
@@ -5052,7 +5091,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>9</v>
@@ -5067,13 +5106,13 @@
         <v>19.0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -5096,7 +5135,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>9</v>
@@ -5117,7 +5156,7 @@
         <v>40</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -5140,13 +5179,13 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D73" s="2">
         <v>2012.0</v>
@@ -5158,10 +5197,10 @@
         <v>36</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -5184,7 +5223,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>9</v>
@@ -5205,7 +5244,7 @@
         <v>101</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -5228,13 +5267,13 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D75" s="2">
         <v>2020.0</v>
@@ -5243,13 +5282,13 @@
         <v>18.0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -5272,13 +5311,13 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="D76" s="2">
         <v>1951.0</v>
@@ -5290,10 +5329,10 @@
         <v>36</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -5316,7 +5355,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>9</v>
@@ -5334,10 +5373,10 @@
         <v>36</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -5360,13 +5399,13 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D78" s="2">
         <v>2018.0</v>
@@ -5378,10 +5417,10 @@
         <v>36</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -5404,13 +5443,13 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D79" s="2">
         <v>2016.0</v>
@@ -5419,13 +5458,13 @@
         <v>18.0</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -5448,13 +5487,13 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D80" s="2">
         <v>2021.0</v>
@@ -5466,10 +5505,10 @@
         <v>36</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -5492,13 +5531,13 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D81" s="2">
         <v>2019.0</v>
@@ -5510,10 +5549,10 @@
         <v>36</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -5536,7 +5575,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>9</v>
@@ -5557,7 +5596,7 @@
         <v>40</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -5580,7 +5619,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
@@ -5601,7 +5640,7 @@
         <v>35</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -5624,13 +5663,13 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D84" s="2">
         <v>2017.0</v>
@@ -5642,10 +5681,10 @@
         <v>36</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -5668,16 +5707,16 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="D85" s="2">
-        <v>2015.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E85" s="2">
         <v>17.0</v>
@@ -5686,10 +5725,10 @@
         <v>36</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -5712,28 +5751,28 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="D86" s="2">
-        <v>1995.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E86" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>308</v>
+        <v>35</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -5756,16 +5795,16 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>311</v>
+        <v>114</v>
       </c>
       <c r="D87" s="2">
-        <v>1993.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E87" s="2">
         <v>16.0</v>
@@ -5774,10 +5813,10 @@
         <v>36</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -5800,16 +5839,16 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D88" s="2">
-        <v>2001.0</v>
+        <v>1993.0</v>
       </c>
       <c r="E88" s="2">
         <v>16.0</v>
@@ -5818,10 +5857,10 @@
         <v>36</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -5844,16 +5883,16 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>73</v>
+        <v>315</v>
       </c>
       <c r="D89" s="2">
-        <v>2013.0</v>
+        <v>2001.0</v>
       </c>
       <c r="E89" s="2">
         <v>16.0</v>
@@ -5862,10 +5901,10 @@
         <v>36</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -5888,16 +5927,16 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>321</v>
+        <v>68</v>
       </c>
       <c r="D90" s="2">
-        <v>1976.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E90" s="2">
         <v>16.0</v>
@@ -5906,10 +5945,10 @@
         <v>36</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>322</v>
+        <v>68</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -5932,28 +5971,28 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>63</v>
+        <v>321</v>
       </c>
       <c r="D91" s="2">
-        <v>1999.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E91" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
@@ -5976,16 +6015,16 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="D92" s="2">
-        <v>2007.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E92" s="2">
         <v>15.0</v>
@@ -5994,10 +6033,10 @@
         <v>36</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -6020,16 +6059,16 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="D93" s="2">
-        <v>2018.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E93" s="2">
         <v>15.0</v>
@@ -6038,10 +6077,10 @@
         <v>36</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -6064,28 +6103,28 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="D94" s="2">
-        <v>2024.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E94" s="2">
         <v>15.0</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>334</v>
+        <v>36</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
@@ -6108,28 +6147,28 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="D95" s="2">
-        <v>2007.0</v>
+        <v>2024.0</v>
       </c>
       <c r="E95" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>36</v>
+        <v>334</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -6152,28 +6191,28 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D96" s="2">
-        <v>2019.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E96" s="2">
         <v>14.0</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>341</v>
+        <v>36</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -6196,28 +6235,28 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="D97" s="2">
-        <v>2020.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E97" s="2">
         <v>14.0</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>36</v>
+        <v>341</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -6240,16 +6279,16 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>348</v>
+        <v>10</v>
       </c>
       <c r="D98" s="2">
-        <v>1969.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E98" s="2">
         <v>14.0</v>
@@ -6258,10 +6297,10 @@
         <v>36</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -6284,16 +6323,16 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="D99" s="2">
-        <v>2000.0</v>
+        <v>1969.0</v>
       </c>
       <c r="E99" s="2">
         <v>14.0</v>
@@ -6302,10 +6341,10 @@
         <v>36</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -6328,16 +6367,16 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>119</v>
+        <v>311</v>
       </c>
       <c r="D100" s="2">
-        <v>1987.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E100" s="2">
         <v>14.0</v>
@@ -6346,10 +6385,10 @@
         <v>36</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -6372,26 +6411,28 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>357</v>
+        <v>119</v>
       </c>
       <c r="D101" s="2">
-        <v>2008.0</v>
+        <v>1987.0</v>
       </c>
       <c r="E101" s="2">
         <v>14.0</v>
       </c>
-      <c r="F101" s="1"/>
+      <c r="F101" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G101" s="1" t="s">
-        <v>63</v>
+        <v>354</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -6414,28 +6455,26 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="D102" s="2">
-        <v>1994.0</v>
+        <v>2008.0</v>
       </c>
       <c r="E102" s="2">
         <v>14.0</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F102" s="1"/>
       <c r="G102" s="1" t="s">
-        <v>360</v>
+        <v>59</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -6458,28 +6497,28 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>63</v>
+        <v>321</v>
       </c>
       <c r="D103" s="2">
-        <v>1997.0</v>
+        <v>1994.0</v>
       </c>
       <c r="E103" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>363</v>
+        <v>36</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -6502,28 +6541,28 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>367</v>
+        <v>59</v>
       </c>
       <c r="D104" s="2">
-        <v>1981.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E104" s="2">
         <v>13.0</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>36</v>
+        <v>363</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -6546,26 +6585,28 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D105" s="2">
-        <v>2013.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E105" s="2">
         <v>13.0</v>
       </c>
-      <c r="F105" s="1"/>
+      <c r="F105" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G105" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -6588,28 +6629,26 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>63</v>
+        <v>371</v>
       </c>
       <c r="D106" s="2">
-        <v>2015.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E106" s="2">
         <v>13.0</v>
       </c>
-      <c r="F106" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>63</v>
+        <v>372</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -6632,16 +6671,16 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D107" s="2">
-        <v>1980.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E107" s="2">
         <v>13.0</v>
@@ -6650,10 +6689,10 @@
         <v>36</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -6676,16 +6715,16 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="D108" s="2">
-        <v>1983.0</v>
+        <v>1980.0</v>
       </c>
       <c r="E108" s="2">
         <v>13.0</v>
@@ -6694,10 +6733,10 @@
         <v>36</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -6720,16 +6759,16 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>321</v>
+        <v>59</v>
       </c>
       <c r="D109" s="2">
-        <v>2020.0</v>
+        <v>1983.0</v>
       </c>
       <c r="E109" s="2">
         <v>13.0</v>
@@ -6738,10 +6777,10 @@
         <v>36</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>321</v>
+        <v>59</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6764,28 +6803,28 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>20</v>
+        <v>321</v>
       </c>
       <c r="D110" s="2">
-        <v>2021.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E110" s="2">
         <v>13.0</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>383</v>
+        <v>36</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>384</v>
+        <v>321</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -6808,28 +6847,28 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D111" s="2">
-        <v>2019.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E111" s="2">
         <v>13.0</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -6852,28 +6891,28 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>195</v>
+        <v>40</v>
       </c>
       <c r="D112" s="2">
-        <v>2010.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E112" s="2">
         <v>13.0</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>36</v>
+        <v>387</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6896,28 +6935,28 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>40</v>
+        <v>195</v>
       </c>
       <c r="D113" s="2">
-        <v>2023.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E113" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>394</v>
+        <v>36</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>40</v>
+        <v>391</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6940,28 +6979,28 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D114" s="2">
-        <v>2017.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E114" s="2">
         <v>12.0</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>36</v>
+        <v>394</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -6984,16 +7023,16 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="D115" s="2">
-        <v>2023.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E115" s="2">
         <v>12.0</v>
@@ -7002,10 +7041,10 @@
         <v>36</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>399</v>
+        <v>35</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -7028,16 +7067,16 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D116" s="2">
-        <v>2017.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E116" s="2">
         <v>12.0</v>
@@ -7046,10 +7085,10 @@
         <v>36</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>165</v>
+        <v>399</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -7072,7 +7111,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>9</v>
@@ -7090,10 +7129,10 @@
         <v>36</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -7116,13 +7155,13 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D118" s="2">
         <v>1990.0</v>
@@ -7134,10 +7173,10 @@
         <v>36</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
@@ -7160,7 +7199,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>9</v>
@@ -7202,13 +7241,13 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D120" s="2">
         <v>1964.0</v>
@@ -7220,10 +7259,10 @@
         <v>36</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
@@ -7246,13 +7285,13 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D121" s="2">
         <v>1993.0</v>
@@ -7264,10 +7303,10 @@
         <v>36</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
@@ -7290,7 +7329,7 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>9</v>
@@ -7308,10 +7347,10 @@
         <v>36</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
@@ -7334,13 +7373,13 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D123" s="2">
         <v>1950.0</v>
@@ -7352,10 +7391,10 @@
         <v>36</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
@@ -7378,13 +7417,13 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D124" s="2">
         <v>1947.0</v>
@@ -7396,10 +7435,10 @@
         <v>36</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
@@ -7422,7 +7461,7 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>9</v>
@@ -7440,10 +7479,10 @@
         <v>36</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
@@ -7466,13 +7505,13 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D126" s="2">
         <v>2011.0</v>
@@ -7484,10 +7523,10 @@
         <v>36</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
@@ -7510,7 +7549,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>9</v>
@@ -7526,10 +7565,10 @@
         <v>36</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
@@ -7552,28 +7591,26 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="D128" s="2">
-        <v>2022.0</v>
+        <v>1985.0</v>
       </c>
       <c r="E128" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>11.0</v>
+      </c>
+      <c r="F128" s="1"/>
       <c r="G128" s="1" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
@@ -7596,28 +7633,26 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D129" s="2">
-        <v>2016.0</v>
+        <v>1982.0</v>
       </c>
       <c r="E129" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>11.0</v>
+      </c>
+      <c r="F129" s="1"/>
       <c r="G129" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
@@ -7640,28 +7675,24 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>96</v>
+        <v>434</v>
       </c>
       <c r="D130" s="2">
-        <v>2018.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E130" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>436</v>
-      </c>
+        <v>11.0</v>
+      </c>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
       <c r="H130" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -7684,28 +7715,24 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>40</v>
+        <v>434</v>
       </c>
       <c r="D131" s="2">
-        <v>2019.0</v>
+        <v>1991.0</v>
       </c>
       <c r="E131" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>40</v>
-      </c>
+        <v>11.0</v>
+      </c>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
       <c r="H131" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -7728,13 +7755,13 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D132" s="2">
         <v>2022.0</v>
@@ -7743,13 +7770,13 @@
         <v>10.0</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>441</v>
+        <v>36</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>442</v>
+        <v>155</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -7772,16 +7799,16 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D133" s="2">
-        <v>2018.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E133" s="2">
         <v>10.0</v>
@@ -7790,10 +7817,10 @@
         <v>36</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -7816,16 +7843,16 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>187</v>
+        <v>96</v>
       </c>
       <c r="D134" s="2">
-        <v>2015.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E134" s="2">
         <v>10.0</v>
@@ -7834,10 +7861,10 @@
         <v>36</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -7860,16 +7887,16 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D135" s="2">
-        <v>2005.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E135" s="2">
         <v>10.0</v>
@@ -7878,10 +7905,10 @@
         <v>36</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -7904,28 +7931,28 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="D136" s="2">
-        <v>1999.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E136" s="2">
         <v>10.0</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>36</v>
+        <v>449</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -7948,16 +7975,16 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D137" s="2">
-        <v>2019.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E137" s="2">
         <v>10.0</v>
@@ -7966,10 +7993,10 @@
         <v>36</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>63</v>
+        <v>453</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -7992,16 +8019,16 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="D138" s="2">
-        <v>2009.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E138" s="2">
         <v>10.0</v>
@@ -8010,10 +8037,10 @@
         <v>36</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>63</v>
+        <v>456</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -8036,28 +8063,28 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="D139" s="2">
-        <v>2002.0</v>
+        <v>2005.0</v>
       </c>
       <c r="E139" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -8080,25 +8107,25 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>311</v>
+        <v>206</v>
       </c>
       <c r="D140" s="2">
-        <v>1951.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E140" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>311</v>
+        <v>461</v>
       </c>
       <c r="H140" s="3" t="s">
         <v>462</v>
@@ -8130,19 +8157,19 @@
         <v>9</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D141" s="2">
-        <v>2021.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E141" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>464</v>
@@ -8174,22 +8201,22 @@
         <v>9</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="D142" s="2">
-        <v>1998.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E142" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G142" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H142" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="H142" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -8212,28 +8239,26 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>213</v>
+        <v>40</v>
       </c>
       <c r="D143" s="2">
-        <v>2003.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E143" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F143" s="1"/>
       <c r="G143" s="1" t="s">
-        <v>213</v>
+        <v>40</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -8256,16 +8281,16 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="D144" s="2">
-        <v>2019.0</v>
+        <v>2002.0</v>
       </c>
       <c r="E144" s="2">
         <v>9.0</v>
@@ -8274,10 +8299,10 @@
         <v>36</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -8300,26 +8325,28 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>10</v>
+        <v>311</v>
       </c>
       <c r="D145" s="2">
-        <v>2021.0</v>
+        <v>1951.0</v>
       </c>
       <c r="E145" s="2">
         <v>9.0</v>
       </c>
-      <c r="F145" s="1"/>
+      <c r="F145" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G145" s="1" t="s">
-        <v>473</v>
+        <v>311</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -8342,13 +8369,13 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D146" s="2">
         <v>2021.0</v>
@@ -8360,10 +8387,10 @@
         <v>36</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>476</v>
+        <v>40</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -8386,28 +8413,28 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>311</v>
+        <v>142</v>
       </c>
       <c r="D147" s="2">
         <v>1998.0</v>
       </c>
       <c r="E147" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>311</v>
+        <v>476</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
@@ -8430,28 +8457,28 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>40</v>
+        <v>215</v>
       </c>
       <c r="D148" s="2">
-        <v>2016.0</v>
+        <v>2003.0</v>
       </c>
       <c r="E148" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>481</v>
+        <v>215</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
@@ -8474,28 +8501,28 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="D149" s="2">
-        <v>2004.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E149" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I149" s="1"/>
       <c r="J149" s="1"/>
@@ -8518,28 +8545,26 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="D150" s="2">
-        <v>2017.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E150" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>9.0</v>
+      </c>
+      <c r="F150" s="1"/>
       <c r="G150" s="1" t="s">
-        <v>63</v>
+        <v>483</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
@@ -8562,28 +8587,28 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D151" s="2">
-        <v>2014.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E151" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>25</v>
+        <v>486</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
@@ -8606,26 +8631,28 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>126</v>
+        <v>311</v>
       </c>
       <c r="D152" s="2">
-        <v>2024.0</v>
+        <v>1998.0</v>
       </c>
       <c r="E152" s="2">
         <v>8.0</v>
       </c>
-      <c r="F152" s="1"/>
+      <c r="F152" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G152" s="1" t="s">
-        <v>126</v>
+        <v>311</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
@@ -8648,23 +8675,25 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D153" s="2">
-        <v>2011.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E153" s="2">
         <v>8.0</v>
       </c>
-      <c r="F153" s="1"/>
+      <c r="F153" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G153" s="1" t="s">
-        <v>63</v>
+        <v>491</v>
       </c>
       <c r="H153" s="3" t="s">
         <v>492</v>
@@ -8695,18 +8724,24 @@
       <c r="B154" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C154" s="1"/>
+      <c r="C154" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="D154" s="2">
-        <v>2021.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E154" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F154" s="1"/>
+        <v>8.0</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G154" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="H154" s="1"/>
       <c r="I154" s="1"/>
       <c r="J154" s="1"/>
       <c r="K154" s="1"/>
@@ -8734,20 +8769,22 @@
         <v>9</v>
       </c>
       <c r="C155" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D155" s="2">
+        <v>2017.0</v>
+      </c>
+      <c r="E155" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H155" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="D155" s="2">
-        <v>2009.0</v>
-      </c>
-      <c r="E155" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F155" s="1"/>
-      <c r="G155" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="H155" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
@@ -8770,28 +8807,28 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D156" s="2">
-        <v>2010.0</v>
+        <v>2014.0</v>
       </c>
       <c r="E156" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>499</v>
+        <v>36</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
@@ -8814,28 +8851,26 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>348</v>
+        <v>129</v>
       </c>
       <c r="D157" s="2">
-        <v>2018.0</v>
+        <v>2024.0</v>
       </c>
       <c r="E157" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F157" s="1"/>
       <c r="G157" s="1" t="s">
-        <v>348</v>
+        <v>129</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
@@ -8858,28 +8893,26 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D158" s="2">
-        <v>2016.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E158" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F158" s="1"/>
       <c r="G158" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
@@ -8902,26 +8935,26 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>151</v>
+        <v>504</v>
       </c>
       <c r="D159" s="2">
-        <v>2005.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E159" s="2">
         <v>7.0</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
-        <v>151</v>
+        <v>504</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -8944,25 +8977,25 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D160" s="2">
-        <v>1981.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E160" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>36</v>
+        <v>507</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H160" s="3" t="s">
         <v>508</v>
@@ -8994,17 +9027,19 @@
         <v>9</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>165</v>
+        <v>348</v>
       </c>
       <c r="D161" s="2">
-        <v>1964.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E161" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="F161" s="1"/>
+        <v>7.0</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G161" s="1" t="s">
-        <v>165</v>
+        <v>348</v>
       </c>
       <c r="H161" s="3" t="s">
         <v>510</v>
@@ -9036,20 +9071,22 @@
         <v>9</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="D162" s="1"/>
+        <v>72</v>
+      </c>
+      <c r="D162" s="2">
+        <v>2016.0</v>
+      </c>
       <c r="E162" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G162" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H162" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="H162" s="3" t="s">
-        <v>513</v>
       </c>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
@@ -9072,28 +9109,26 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D163" s="2">
-        <v>2009.0</v>
+        <v>2005.0</v>
       </c>
       <c r="E163" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F163" s="1"/>
       <c r="G163" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -9116,16 +9151,16 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="D164" s="2">
-        <v>2018.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E164" s="2">
         <v>6.0</v>
@@ -9134,10 +9169,10 @@
         <v>36</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -9160,28 +9195,26 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="D165" s="2">
-        <v>1966.0</v>
+        <v>1964.0</v>
       </c>
       <c r="E165" s="2">
         <v>6.0</v>
       </c>
-      <c r="F165" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F165" s="1"/>
       <c r="G165" s="1" t="s">
-        <v>519</v>
+        <v>165</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -9204,28 +9237,26 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="D166" s="2">
-        <v>2010.0</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="D166" s="1"/>
       <c r="E166" s="2">
         <v>6.0</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>522</v>
+        <v>36</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>419</v>
+        <v>520</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
@@ -9248,16 +9279,16 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="D167" s="2">
-        <v>2010.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E167" s="2">
         <v>6.0</v>
@@ -9266,10 +9297,10 @@
         <v>36</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>525</v>
+        <v>59</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
@@ -9292,16 +9323,16 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="D168" s="2">
-        <v>2023.0</v>
+        <v>1966.0</v>
       </c>
       <c r="E168" s="2">
         <v>6.0</v>
@@ -9310,10 +9341,10 @@
         <v>36</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>68</v>
+        <v>525</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
@@ -9336,28 +9367,28 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>151</v>
+        <v>417</v>
       </c>
       <c r="D169" s="2">
-        <v>1985.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E169" s="2">
         <v>6.0</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>36</v>
+        <v>528</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>151</v>
+        <v>417</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
@@ -9380,16 +9411,16 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D170" s="2">
-        <v>2018.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E170" s="2">
         <v>6.0</v>
@@ -9398,7 +9429,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>85</v>
+        <v>531</v>
       </c>
       <c r="H170" s="3" t="s">
         <v>532</v>
@@ -9430,10 +9461,10 @@
         <v>9</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D171" s="2">
-        <v>2019.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E171" s="2">
         <v>6.0</v>
@@ -9442,7 +9473,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H171" s="3" t="s">
         <v>534</v>
@@ -9474,22 +9505,22 @@
         <v>9</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>536</v>
+        <v>126</v>
       </c>
       <c r="D172" s="2">
-        <v>2006.0</v>
+        <v>1985.0</v>
       </c>
       <c r="E172" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G172" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H172" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="H172" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
@@ -9512,26 +9543,28 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="D173" s="2">
-        <v>1981.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E173" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F173" s="1"/>
+        <v>6.0</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G173" s="1" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
@@ -9554,28 +9587,28 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D174" s="2">
-        <v>2012.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E174" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
@@ -9598,23 +9631,23 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>68</v>
+        <v>542</v>
       </c>
       <c r="D175" s="2">
-        <v>2016.0</v>
+        <v>2014.0</v>
       </c>
       <c r="E175" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F175" s="1"/>
       <c r="G175" s="1" t="s">
-        <v>68</v>
+        <v>315</v>
       </c>
       <c r="H175" s="3" t="s">
         <v>543</v>
@@ -9646,20 +9679,16 @@
         <v>9</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>204</v>
+        <v>542</v>
       </c>
       <c r="D176" s="2">
-        <v>2018.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E176" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>204</v>
-      </c>
+        <v>6.0</v>
+      </c>
+      <c r="F176" s="1"/>
+      <c r="G176" s="1"/>
       <c r="H176" s="3" t="s">
         <v>545</v>
       </c>
@@ -9690,10 +9719,10 @@
         <v>9</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>54</v>
+        <v>547</v>
       </c>
       <c r="D177" s="2">
-        <v>1978.0</v>
+        <v>2006.0</v>
       </c>
       <c r="E177" s="2">
         <v>5.0</v>
@@ -9734,17 +9763,17 @@
         <v>9</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="D178" s="2">
-        <v>2019.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E178" s="2">
         <v>5.0</v>
       </c>
       <c r="F178" s="1"/>
       <c r="G178" s="1" t="s">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="H178" s="3" t="s">
         <v>550</v>
@@ -9776,10 +9805,10 @@
         <v>9</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D179" s="2">
-        <v>2021.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E179" s="2">
         <v>5.0</v>
@@ -9788,7 +9817,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>552</v>
@@ -9820,19 +9849,17 @@
         <v>9</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D180" s="2">
-        <v>2002.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E180" s="2">
         <v>5.0</v>
       </c>
-      <c r="F180" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F180" s="1"/>
       <c r="G180" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>554</v>
@@ -9864,10 +9891,10 @@
         <v>9</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>96</v>
+        <v>206</v>
       </c>
       <c r="D181" s="2">
-        <v>2022.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E181" s="2">
         <v>5.0</v>
@@ -9876,10 +9903,10 @@
         <v>36</v>
       </c>
       <c r="G181" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H181" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="H181" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="I181" s="1"/>
       <c r="J181" s="1"/>
@@ -9902,16 +9929,16 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="D182" s="2">
-        <v>2017.0</v>
+        <v>1978.0</v>
       </c>
       <c r="E182" s="2">
         <v>5.0</v>
@@ -9920,7 +9947,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>187</v>
+        <v>558</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>559</v>
@@ -9952,17 +9979,17 @@
         <v>9</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D183" s="2">
-        <v>2009.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E183" s="2">
         <v>5.0</v>
       </c>
       <c r="F183" s="1"/>
       <c r="G183" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>561</v>
@@ -9987,14 +10014,30 @@
       <c r="Z183" s="1"/>
     </row>
     <row r="184">
-      <c r="A184" s="1"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
-      <c r="E184" s="1"/>
-      <c r="F184" s="1"/>
-      <c r="G184" s="1"/>
-      <c r="H184" s="1"/>
+      <c r="A184" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D184" s="2">
+        <v>2021.0</v>
+      </c>
+      <c r="E184" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>563</v>
+      </c>
       <c r="I184" s="1"/>
       <c r="J184" s="1"/>
       <c r="K184" s="1"/>
@@ -10015,14 +10058,30 @@
       <c r="Z184" s="1"/>
     </row>
     <row r="185">
-      <c r="A185" s="1"/>
-      <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
-      <c r="E185" s="1"/>
-      <c r="F185" s="1"/>
-      <c r="G185" s="1"/>
-      <c r="H185" s="1"/>
+      <c r="A185" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" s="2">
+        <v>2002.0</v>
+      </c>
+      <c r="E185" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>565</v>
+      </c>
       <c r="I185" s="1"/>
       <c r="J185" s="1"/>
       <c r="K185" s="1"/>
@@ -10043,14 +10102,30 @@
       <c r="Z185" s="1"/>
     </row>
     <row r="186">
-      <c r="A186" s="1"/>
-      <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
-      <c r="E186" s="1"/>
-      <c r="F186" s="1"/>
-      <c r="G186" s="1"/>
-      <c r="H186" s="1"/>
+      <c r="A186" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D186" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="E186" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="H186" s="3" t="s">
+        <v>568</v>
+      </c>
       <c r="I186" s="1"/>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
@@ -10071,14 +10146,30 @@
       <c r="Z186" s="1"/>
     </row>
     <row r="187">
-      <c r="A187" s="1"/>
-      <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
-      <c r="E187" s="1"/>
-      <c r="F187" s="1"/>
-      <c r="G187" s="1"/>
-      <c r="H187" s="1"/>
+      <c r="A187" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D187" s="2">
+        <v>2017.0</v>
+      </c>
+      <c r="E187" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>570</v>
+      </c>
       <c r="I187" s="1"/>
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
@@ -10099,14 +10190,28 @@
       <c r="Z187" s="1"/>
     </row>
     <row r="188">
-      <c r="A188" s="1"/>
-      <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
-      <c r="E188" s="1"/>
+      <c r="A188" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D188" s="2">
+        <v>2009.0</v>
+      </c>
+      <c r="E188" s="2">
+        <v>5.0</v>
+      </c>
       <c r="F188" s="1"/>
-      <c r="G188" s="1"/>
-      <c r="H188" s="1"/>
+      <c r="G188" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H188" s="3" t="s">
+        <v>572</v>
+      </c>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
       <c r="K188" s="1"/>
@@ -10127,14 +10232,28 @@
       <c r="Z188" s="1"/>
     </row>
     <row r="189">
-      <c r="A189" s="1"/>
-      <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
-      <c r="E189" s="1"/>
+      <c r="A189" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D189" s="2">
+        <v>2018.0</v>
+      </c>
+      <c r="E189" s="2">
+        <v>5.0</v>
+      </c>
       <c r="F189" s="1"/>
-      <c r="G189" s="1"/>
-      <c r="H189" s="1"/>
+      <c r="G189" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>574</v>
+      </c>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
       <c r="K189" s="1"/>
@@ -10155,14 +10274,26 @@
       <c r="Z189" s="1"/>
     </row>
     <row r="190">
-      <c r="A190" s="1"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
-      <c r="E190" s="1"/>
+      <c r="A190" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D190" s="2">
+        <v>1983.0</v>
+      </c>
+      <c r="E190" s="2">
+        <v>5.0</v>
+      </c>
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
-      <c r="H190" s="1"/>
+      <c r="H190" s="3" t="s">
+        <v>576</v>
+      </c>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
@@ -32920,102 +33051,102 @@
     <hyperlink r:id="rId54" ref="H54"/>
     <hyperlink r:id="rId55" ref="H55"/>
     <hyperlink r:id="rId56" ref="H56"/>
-    <hyperlink r:id="rId57" ref="H57"/>
-    <hyperlink r:id="rId58" ref="H58"/>
-    <hyperlink r:id="rId59" ref="H59"/>
-    <hyperlink r:id="rId60" ref="H60"/>
-    <hyperlink r:id="rId61" ref="H61"/>
-    <hyperlink r:id="rId62" ref="H62"/>
-    <hyperlink r:id="rId63" ref="H63"/>
-    <hyperlink r:id="rId64" ref="H64"/>
-    <hyperlink r:id="rId65" ref="H65"/>
-    <hyperlink r:id="rId66" ref="H66"/>
-    <hyperlink r:id="rId67" ref="H67"/>
-    <hyperlink r:id="rId68" ref="H68"/>
-    <hyperlink r:id="rId69" ref="H69"/>
-    <hyperlink r:id="rId70" ref="H70"/>
-    <hyperlink r:id="rId71" ref="H71"/>
-    <hyperlink r:id="rId72" ref="H72"/>
-    <hyperlink r:id="rId73" ref="H73"/>
-    <hyperlink r:id="rId74" ref="H74"/>
-    <hyperlink r:id="rId75" ref="H75"/>
-    <hyperlink r:id="rId76" ref="H76"/>
-    <hyperlink r:id="rId77" ref="H77"/>
-    <hyperlink r:id="rId78" ref="H78"/>
-    <hyperlink r:id="rId79" ref="H79"/>
-    <hyperlink r:id="rId80" ref="H80"/>
-    <hyperlink r:id="rId81" ref="H81"/>
-    <hyperlink r:id="rId82" ref="H82"/>
-    <hyperlink r:id="rId83" ref="H83"/>
-    <hyperlink r:id="rId84" ref="H84"/>
-    <hyperlink r:id="rId85" ref="H85"/>
-    <hyperlink r:id="rId86" ref="H86"/>
-    <hyperlink r:id="rId87" ref="H87"/>
-    <hyperlink r:id="rId88" ref="H88"/>
-    <hyperlink r:id="rId89" ref="H89"/>
-    <hyperlink r:id="rId90" ref="H90"/>
-    <hyperlink r:id="rId91" ref="H91"/>
-    <hyperlink r:id="rId92" ref="H92"/>
-    <hyperlink r:id="rId93" ref="H93"/>
-    <hyperlink r:id="rId94" ref="H94"/>
-    <hyperlink r:id="rId95" ref="H95"/>
-    <hyperlink r:id="rId96" ref="H96"/>
-    <hyperlink r:id="rId97" ref="H97"/>
-    <hyperlink r:id="rId98" ref="H98"/>
-    <hyperlink r:id="rId99" ref="H99"/>
-    <hyperlink r:id="rId100" ref="H100"/>
-    <hyperlink r:id="rId101" ref="H101"/>
-    <hyperlink r:id="rId102" ref="H102"/>
-    <hyperlink r:id="rId103" ref="H103"/>
-    <hyperlink r:id="rId104" ref="H104"/>
-    <hyperlink r:id="rId105" ref="H105"/>
-    <hyperlink r:id="rId106" ref="H106"/>
-    <hyperlink r:id="rId107" ref="H107"/>
-    <hyperlink r:id="rId108" ref="H108"/>
-    <hyperlink r:id="rId109" ref="H109"/>
-    <hyperlink r:id="rId110" ref="H110"/>
-    <hyperlink r:id="rId111" ref="H111"/>
-    <hyperlink r:id="rId112" ref="H112"/>
-    <hyperlink r:id="rId113" ref="H113"/>
-    <hyperlink r:id="rId114" ref="H114"/>
-    <hyperlink r:id="rId115" ref="H115"/>
-    <hyperlink r:id="rId116" ref="H116"/>
-    <hyperlink r:id="rId117" ref="H117"/>
-    <hyperlink r:id="rId118" ref="H118"/>
-    <hyperlink r:id="rId119" ref="H120"/>
-    <hyperlink r:id="rId120" ref="H121"/>
-    <hyperlink r:id="rId121" ref="H122"/>
-    <hyperlink r:id="rId122" ref="H123"/>
-    <hyperlink r:id="rId123" ref="H124"/>
-    <hyperlink r:id="rId124" ref="H125"/>
-    <hyperlink r:id="rId125" ref="H126"/>
-    <hyperlink r:id="rId126" ref="H127"/>
-    <hyperlink r:id="rId127" ref="H128"/>
-    <hyperlink r:id="rId128" ref="H129"/>
-    <hyperlink r:id="rId129" ref="H130"/>
-    <hyperlink r:id="rId130" ref="H131"/>
-    <hyperlink r:id="rId131" ref="H132"/>
-    <hyperlink r:id="rId132" ref="H133"/>
-    <hyperlink r:id="rId133" ref="H134"/>
-    <hyperlink r:id="rId134" ref="H135"/>
-    <hyperlink r:id="rId135" ref="H136"/>
-    <hyperlink r:id="rId136" ref="H137"/>
-    <hyperlink r:id="rId137" ref="H138"/>
-    <hyperlink r:id="rId138" ref="H139"/>
-    <hyperlink r:id="rId139" ref="H140"/>
-    <hyperlink r:id="rId140" ref="H141"/>
-    <hyperlink r:id="rId141" ref="H142"/>
-    <hyperlink r:id="rId142" ref="H143"/>
-    <hyperlink r:id="rId143" ref="H144"/>
-    <hyperlink r:id="rId144" ref="H145"/>
-    <hyperlink r:id="rId145" ref="H146"/>
-    <hyperlink r:id="rId146" ref="H147"/>
-    <hyperlink r:id="rId147" ref="H148"/>
-    <hyperlink r:id="rId148" ref="H149"/>
-    <hyperlink r:id="rId149" ref="H150"/>
-    <hyperlink r:id="rId150" ref="H151"/>
-    <hyperlink r:id="rId151" ref="H152"/>
-    <hyperlink r:id="rId152" ref="H153"/>
+    <hyperlink r:id="rId57" ref="H58"/>
+    <hyperlink r:id="rId58" ref="H59"/>
+    <hyperlink r:id="rId59" ref="H60"/>
+    <hyperlink r:id="rId60" ref="H61"/>
+    <hyperlink r:id="rId61" ref="H62"/>
+    <hyperlink r:id="rId62" ref="H63"/>
+    <hyperlink r:id="rId63" ref="H64"/>
+    <hyperlink r:id="rId64" ref="H65"/>
+    <hyperlink r:id="rId65" ref="H66"/>
+    <hyperlink r:id="rId66" ref="H67"/>
+    <hyperlink r:id="rId67" ref="H68"/>
+    <hyperlink r:id="rId68" ref="H69"/>
+    <hyperlink r:id="rId69" ref="H70"/>
+    <hyperlink r:id="rId70" ref="H71"/>
+    <hyperlink r:id="rId71" ref="H72"/>
+    <hyperlink r:id="rId72" ref="H73"/>
+    <hyperlink r:id="rId73" ref="H74"/>
+    <hyperlink r:id="rId74" ref="H75"/>
+    <hyperlink r:id="rId75" ref="H76"/>
+    <hyperlink r:id="rId76" ref="H77"/>
+    <hyperlink r:id="rId77" ref="H78"/>
+    <hyperlink r:id="rId78" ref="H79"/>
+    <hyperlink r:id="rId79" ref="H80"/>
+    <hyperlink r:id="rId80" ref="H81"/>
+    <hyperlink r:id="rId81" ref="H82"/>
+    <hyperlink r:id="rId82" ref="H83"/>
+    <hyperlink r:id="rId83" ref="H84"/>
+    <hyperlink r:id="rId84" ref="H85"/>
+    <hyperlink r:id="rId85" ref="H86"/>
+    <hyperlink r:id="rId86" ref="H87"/>
+    <hyperlink r:id="rId87" ref="H88"/>
+    <hyperlink r:id="rId88" ref="H89"/>
+    <hyperlink r:id="rId89" ref="H90"/>
+    <hyperlink r:id="rId90" ref="H91"/>
+    <hyperlink r:id="rId91" ref="H92"/>
+    <hyperlink r:id="rId92" ref="H93"/>
+    <hyperlink r:id="rId93" ref="H94"/>
+    <hyperlink r:id="rId94" ref="H95"/>
+    <hyperlink r:id="rId95" ref="H96"/>
+    <hyperlink r:id="rId96" ref="H97"/>
+    <hyperlink r:id="rId97" ref="H98"/>
+    <hyperlink r:id="rId98" ref="H99"/>
+    <hyperlink r:id="rId99" ref="H100"/>
+    <hyperlink r:id="rId100" ref="H101"/>
+    <hyperlink r:id="rId101" ref="H102"/>
+    <hyperlink r:id="rId102" ref="H103"/>
+    <hyperlink r:id="rId103" ref="H104"/>
+    <hyperlink r:id="rId104" ref="H105"/>
+    <hyperlink r:id="rId105" ref="H106"/>
+    <hyperlink r:id="rId106" ref="H107"/>
+    <hyperlink r:id="rId107" ref="H108"/>
+    <hyperlink r:id="rId108" ref="H109"/>
+    <hyperlink r:id="rId109" ref="H110"/>
+    <hyperlink r:id="rId110" ref="H111"/>
+    <hyperlink r:id="rId111" ref="H112"/>
+    <hyperlink r:id="rId112" ref="H113"/>
+    <hyperlink r:id="rId113" ref="H114"/>
+    <hyperlink r:id="rId114" ref="H115"/>
+    <hyperlink r:id="rId115" ref="H116"/>
+    <hyperlink r:id="rId116" ref="H117"/>
+    <hyperlink r:id="rId117" ref="H118"/>
+    <hyperlink r:id="rId118" ref="H120"/>
+    <hyperlink r:id="rId119" ref="H121"/>
+    <hyperlink r:id="rId120" ref="H122"/>
+    <hyperlink r:id="rId121" ref="H123"/>
+    <hyperlink r:id="rId122" ref="H124"/>
+    <hyperlink r:id="rId123" ref="H125"/>
+    <hyperlink r:id="rId124" ref="H126"/>
+    <hyperlink r:id="rId125" ref="H127"/>
+    <hyperlink r:id="rId126" ref="H128"/>
+    <hyperlink r:id="rId127" ref="H129"/>
+    <hyperlink r:id="rId128" ref="H130"/>
+    <hyperlink r:id="rId129" ref="H131"/>
+    <hyperlink r:id="rId130" ref="H132"/>
+    <hyperlink r:id="rId131" ref="H133"/>
+    <hyperlink r:id="rId132" ref="H134"/>
+    <hyperlink r:id="rId133" ref="H135"/>
+    <hyperlink r:id="rId134" ref="H136"/>
+    <hyperlink r:id="rId135" ref="H137"/>
+    <hyperlink r:id="rId136" ref="H138"/>
+    <hyperlink r:id="rId137" ref="H139"/>
+    <hyperlink r:id="rId138" ref="H140"/>
+    <hyperlink r:id="rId139" ref="H141"/>
+    <hyperlink r:id="rId140" ref="H142"/>
+    <hyperlink r:id="rId141" ref="H143"/>
+    <hyperlink r:id="rId142" ref="H144"/>
+    <hyperlink r:id="rId143" ref="H145"/>
+    <hyperlink r:id="rId144" ref="H146"/>
+    <hyperlink r:id="rId145" ref="H147"/>
+    <hyperlink r:id="rId146" ref="H148"/>
+    <hyperlink r:id="rId147" ref="H149"/>
+    <hyperlink r:id="rId148" ref="H150"/>
+    <hyperlink r:id="rId149" ref="H151"/>
+    <hyperlink r:id="rId150" ref="H152"/>
+    <hyperlink r:id="rId151" ref="H153"/>
+    <hyperlink r:id="rId152" ref="H154"/>
     <hyperlink r:id="rId153" ref="H155"/>
     <hyperlink r:id="rId154" ref="H156"/>
     <hyperlink r:id="rId155" ref="H157"/>
@@ -33045,7 +33176,14 @@
     <hyperlink r:id="rId179" ref="H181"/>
     <hyperlink r:id="rId180" ref="H182"/>
     <hyperlink r:id="rId181" ref="H183"/>
+    <hyperlink r:id="rId182" ref="H184"/>
+    <hyperlink r:id="rId183" ref="H185"/>
+    <hyperlink r:id="rId184" ref="H186"/>
+    <hyperlink r:id="rId185" ref="H187"/>
+    <hyperlink r:id="rId186" ref="H188"/>
+    <hyperlink r:id="rId187" ref="H189"/>
+    <hyperlink r:id="rId188" ref="H190"/>
   </hyperlinks>
-  <drawing r:id="rId182"/>
+  <drawing r:id="rId189"/>
 </worksheet>
 </file>
--- a/Car_Wash_Advisory_Companies.xlsx
+++ b/Car_Wash_Advisory_Companies.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="577">
   <si>
     <t>Company Name</t>
   </si>
@@ -130,6 +130,18 @@
     <t>https://tommys-express.com/</t>
   </si>
   <si>
+    <t>Mammoth Holdings LLC</t>
+  </si>
+  <si>
+    <t>Red Dog Equity and CCMP Growth Advisors</t>
+  </si>
+  <si>
+    <t>Georgia | Alabama | Kentucky | Illinois | Utah | South Carolina | Mississippi | Louisiana | Tennessee | North Dakota | Iowa | Florida | Minnesota | Missouri | South Dakota | Texas | West Virginia</t>
+  </si>
+  <si>
+    <t>https://mammothholdings.com/</t>
+  </si>
+  <si>
     <t>Spotless Brands</t>
   </si>
   <si>
@@ -202,25 +214,13 @@
     <t>https://www.whitewatercw.com/</t>
   </si>
   <si>
-    <t>Mammoth Holdings LLC</t>
-  </si>
-  <si>
-    <t>Red Dog Equity and CCMP Growth Advisors</t>
-  </si>
-  <si>
-    <t>Georgia | Alabama | Kentucky | Illinois | Utah | South Carolina | Mississippi | Louisiana | Tennessee | North Dakota | Iowa | Florida | Minnesota | Missouri | South Dakota | Texas | West Virginia</t>
-  </si>
-  <si>
-    <t>https://mammothholdings.com/</t>
-  </si>
-  <si>
     <t>Express Wash Concepts</t>
   </si>
   <si>
     <t>Ohio</t>
   </si>
   <si>
-    <t>Ohio | Virginia | Pennsylvania | North Carolina | Indiana | Michigan</t>
+    <t>Ohio | Virginia | Pennsylvania | Michigan</t>
   </si>
   <si>
     <t>https://www.expresswashconcepts.com/</t>
@@ -241,6 +241,18 @@
     <t>https://www.modwash.com/</t>
   </si>
   <si>
+    <t>El Car Wash</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Warburg Pincus</t>
+  </si>
+  <si>
+    <t>https://elcarwash.com/</t>
+  </si>
+  <si>
     <t>Summit Wash Holdings</t>
   </si>
   <si>
@@ -256,18 +268,6 @@
     <t>https://summitwashholdings.com</t>
   </si>
   <si>
-    <t>El Car Wash</t>
-  </si>
-  <si>
-    <t>Florida</t>
-  </si>
-  <si>
-    <t>Warburg Pincus</t>
-  </si>
-  <si>
-    <t>https://elcarwash.com/</t>
-  </si>
-  <si>
     <t>Autobell Car Wash</t>
   </si>
   <si>
@@ -277,6 +277,30 @@
     <t>https://www.autobell.com/</t>
   </si>
   <si>
+    <t>LUV Car Wash</t>
+  </si>
+  <si>
+    <t>Susquehanna Private Capital</t>
+  </si>
+  <si>
+    <t>Florida | Georgia | California | Nevada | Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://luvcarwash.com/</t>
+  </si>
+  <si>
+    <t>Caliber Car Wash</t>
+  </si>
+  <si>
+    <t>Percheron Capital</t>
+  </si>
+  <si>
+    <t>Alabama | Florida | Georgia | North Carolina | South Carolina | Texas</t>
+  </si>
+  <si>
+    <t>https://calibercarwash.com/</t>
+  </si>
+  <si>
     <t>ClearWater Express Wash</t>
   </si>
   <si>
@@ -286,16 +310,19 @@
     <t>https://www.clearwaterexpresswash.com</t>
   </si>
   <si>
-    <t>LUV Car Wash</t>
-  </si>
-  <si>
-    <t>Susquehanna Private Capital</t>
-  </si>
-  <si>
-    <t>Florida | Georgia | California | Nevada | Pennsylvania</t>
-  </si>
-  <si>
-    <t>https://luvcarwash.com/</t>
+    <t>Tsunami Express</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Point72 Ventures</t>
+  </si>
+  <si>
+    <t>Arkansas | Indiana | Illinois | Kansas | Michigan | Missouri | Minnesota | Ohio | Wisconsin</t>
+  </si>
+  <si>
+    <t>https://www.tsunamiexpress.com/</t>
   </si>
   <si>
     <t>Splash Car Wash</t>
@@ -313,21 +340,6 @@
     <t>https://splashcarwashes.com/</t>
   </si>
   <si>
-    <t>Tsunami Express</t>
-  </si>
-  <si>
-    <t>Oregon</t>
-  </si>
-  <si>
-    <t>Point72 Ventures</t>
-  </si>
-  <si>
-    <t>Arkansas | Indiana | Illinois | Kansas | Michigan | Missouri | Minnesota | Ohio | Wisconsin</t>
-  </si>
-  <si>
-    <t>https://www.tsunamiexpress.com/</t>
-  </si>
-  <si>
     <t>True Blue Car Wash</t>
   </si>
   <si>
@@ -340,16 +352,28 @@
     <t>https://truebluecw.com/</t>
   </si>
   <si>
-    <t>Caliber Car Wash</t>
-  </si>
-  <si>
-    <t>Percheron Capital</t>
-  </si>
-  <si>
-    <t>Alabama | Florida | Georgia | North Carolina | South Carolina | Texas</t>
-  </si>
-  <si>
-    <t>https://calibercarwash.com/</t>
+    <t>Splash in ECO Car Wash</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>Maryland | Delaware | Virginia</t>
+  </si>
+  <si>
+    <t>https://www.splashin.com/</t>
+  </si>
+  <si>
+    <t>Jax Kar Wash</t>
+  </si>
+  <si>
+    <t>TRP Capital Partners</t>
+  </si>
+  <si>
+    <t>Michigan | Indiana</t>
+  </si>
+  <si>
+    <t>https://www.jaxkarwash.com</t>
   </si>
   <si>
     <t>Golden Nozzle Car Wash</t>
@@ -367,18 +391,6 @@
     <t>https://goldennozzlecarwash.com/</t>
   </si>
   <si>
-    <t>Splash in ECO Car Wash</t>
-  </si>
-  <si>
-    <t>Maryland</t>
-  </si>
-  <si>
-    <t>Maryland | Delaware | Virginia</t>
-  </si>
-  <si>
-    <t>https://www.splashin.com/</t>
-  </si>
-  <si>
     <t>Champion Xpress Carwash</t>
   </si>
   <si>
@@ -388,6 +400,39 @@
     <t>https://champxpress.com/</t>
   </si>
   <si>
+    <t>Big Dan's Car Wash</t>
+  </si>
+  <si>
+    <t>Shadday Family Office</t>
+  </si>
+  <si>
+    <t>Alabama | Florida | Georgia | South Carolina</t>
+  </si>
+  <si>
+    <t>https://www.bigdanscarwash.com/</t>
+  </si>
+  <si>
+    <t>Crew Carwash</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Indiana | Minnesota</t>
+  </si>
+  <si>
+    <t>https://crewcarwash.com/</t>
+  </si>
+  <si>
+    <t>Auto Wash Car Wash</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>https://www.autowashcarwash.com/</t>
+  </si>
+  <si>
     <t>Brown Bear Car Wash</t>
   </si>
   <si>
@@ -397,18 +442,6 @@
     <t>https://www.brownbear.com/</t>
   </si>
   <si>
-    <t>Crew Carwash</t>
-  </si>
-  <si>
-    <t>Indiana</t>
-  </si>
-  <si>
-    <t>Indiana | Minnesota</t>
-  </si>
-  <si>
-    <t>https://crewcarwash.com/</t>
-  </si>
-  <si>
     <t>Sam's Xpress Car Wash</t>
   </si>
   <si>
@@ -418,16 +451,16 @@
     <t>https://samsxpresscarwash.com/</t>
   </si>
   <si>
-    <t>Jax Kar Wash</t>
-  </si>
-  <si>
-    <t>TRP Capital Partners</t>
-  </si>
-  <si>
-    <t>Michigan | Indiana</t>
-  </si>
-  <si>
-    <t>https://www.jaxkarwash.com</t>
+    <t>Mr. Clean Car Wash</t>
+  </si>
+  <si>
+    <t>Corporate Backed or Acquired</t>
+  </si>
+  <si>
+    <t>Georgia | Florida</t>
+  </si>
+  <si>
+    <t>https://www.mrcleancarwash.com/</t>
   </si>
   <si>
     <t>Prestige Car Wash</t>
@@ -436,6 +469,15 @@
     <t>https://www.prestigewash.com/</t>
   </si>
   <si>
+    <t>Wash N' Roll</t>
+  </si>
+  <si>
+    <t>Tennessee | Alabama | Indiana | Georgia</t>
+  </si>
+  <si>
+    <t>https://www.mywashnroll.com/</t>
+  </si>
+  <si>
     <t>Terrible Herbst</t>
   </si>
   <si>
@@ -460,28 +502,13 @@
     <t>https://racewaycarwash.com/</t>
   </si>
   <si>
-    <t>Big Dan's Car Wash</t>
-  </si>
-  <si>
-    <t>Shadday Family Office</t>
-  </si>
-  <si>
-    <t>Alabama | Florida | Georgia | South Carolina</t>
-  </si>
-  <si>
-    <t>https://www.bigdanscarwash.com/</t>
-  </si>
-  <si>
-    <t>Mr. Clean Car Wash</t>
-  </si>
-  <si>
-    <t>Corporate Backed or Acquired</t>
-  </si>
-  <si>
-    <t>Georgia | Florida</t>
-  </si>
-  <si>
-    <t>https://www.mrcleancarwash.com/</t>
+    <t>Mike's Car Wash</t>
+  </si>
+  <si>
+    <t>Kentucky | Ohio | Indiana</t>
+  </si>
+  <si>
+    <t>https://www.mikescarwash.com/</t>
   </si>
   <si>
     <t>Sparkling Image Car Wash</t>
@@ -496,15 +523,6 @@
     <t>https://www.sparklingimage.com/</t>
   </si>
   <si>
-    <t>Wash N' Roll</t>
-  </si>
-  <si>
-    <t>Tennessee | Alabama | Indiana | Georgia</t>
-  </si>
-  <si>
-    <t>https://www.mywashnroll.com/</t>
-  </si>
-  <si>
     <t>Rich's Car Wash</t>
   </si>
   <si>
@@ -517,15 +535,6 @@
     <t>https://www.richscarwash.com/</t>
   </si>
   <si>
-    <t>Mike's Car Wash</t>
-  </si>
-  <si>
-    <t>Kentucky | Ohio | Indiana</t>
-  </si>
-  <si>
-    <t>https://www.mikescarwash.com/</t>
-  </si>
-  <si>
     <t>Surf Thru Express Car Wash</t>
   </si>
   <si>
@@ -544,174 +553,252 @@
     <t>https://watershedcarwash.com/</t>
   </si>
   <si>
+    <t>Gas N Wash</t>
+  </si>
+  <si>
+    <t>Bow River Capital</t>
+  </si>
+  <si>
+    <t>https://www.gasnwash.net/</t>
+  </si>
+  <si>
+    <t>Mighty Wash</t>
+  </si>
+  <si>
+    <t>Texas | New Mexico</t>
+  </si>
+  <si>
+    <t>https://mymightywash.com/</t>
+  </si>
+  <si>
     <t>Delta Sonic</t>
   </si>
   <si>
-    <t>New York</t>
-  </si>
-  <si>
     <t>New York | Illinois | Pennsylvania</t>
   </si>
   <si>
     <t>https://www.deltasoniccarwash.com/</t>
   </si>
   <si>
+    <t>Tagg-N-Go</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>Utah | Nevada | Idaho</t>
+  </si>
+  <si>
+    <t>https://taggngo.com/</t>
+  </si>
+  <si>
+    <t>Glide XPRESS Car Wash</t>
+  </si>
+  <si>
+    <t>Tennessee | Missouri | Arkansas | Mississippi</t>
+  </si>
+  <si>
+    <t>https://www.glidexwash.com/</t>
+  </si>
+  <si>
+    <t>Washville Car Wash</t>
+  </si>
+  <si>
+    <t>Garnett Reynolds Holdings</t>
+  </si>
+  <si>
+    <t>New York | Massachusetts | Rhode Island | New Hampshire | Maine</t>
+  </si>
+  <si>
+    <t>https://washvillecarwash.com/</t>
+  </si>
+  <si>
+    <t>Flash Car Wash</t>
+  </si>
+  <si>
+    <t>Connecticut | Massachusetts | Rhode Island</t>
+  </si>
+  <si>
+    <t>https://flashcarwashes.com/</t>
+  </si>
+  <si>
+    <t>Hurricane Express Wash</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>PassiveInvesting.com</t>
+  </si>
+  <si>
+    <t>Tennessee | South Carolina | North Carolina | Florida | Maryland | Virginia | Alabama</t>
+  </si>
+  <si>
+    <t>https://www.hurricanewash.com/</t>
+  </si>
+  <si>
+    <t>Soapy Joe’s Car Wash</t>
+  </si>
+  <si>
+    <t>https://soapyjoescarwash.com/</t>
+  </si>
+  <si>
+    <t>Waterway Carwash</t>
+  </si>
+  <si>
+    <t>Kansas | Montana | Colorado | Illinois | Ohio</t>
+  </si>
+  <si>
+    <t>https://www.waterway.com/</t>
+  </si>
+  <si>
+    <t>Hoffman Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.hoffmancarwash.com/</t>
+  </si>
+  <si>
+    <t>Trademark Car Wash</t>
+  </si>
+  <si>
+    <t>Princeton Equity Group / Accelerated Brands</t>
+  </si>
+  <si>
+    <t>Texas | Louisiana | Florida | New Mexico | Arizona | Tennessee | Michigan | Missouri</t>
+  </si>
+  <si>
+    <t>https://trademarkcarwash.com/</t>
+  </si>
+  <si>
+    <t>Quick N Clean</t>
+  </si>
+  <si>
+    <t>Arizona | Colorado | Oklahoma | Texas</t>
+  </si>
+  <si>
+    <t>https://quicknclean.net/</t>
+  </si>
+  <si>
+    <t>Ronny's Car Wash</t>
+  </si>
+  <si>
+    <t>Florida | Alabama</t>
+  </si>
+  <si>
+    <t>https://ronnyscarwash.net/</t>
+  </si>
+  <si>
+    <t>Sud Stop Car Wash</t>
+  </si>
+  <si>
+    <t>Real Capital Partners</t>
+  </si>
+  <si>
+    <t>Florida | Georgia | Alabama | North Carolina | South Carolina</t>
+  </si>
+  <si>
+    <t>https://www.sudstopcarwash.com/</t>
+  </si>
+  <si>
+    <t>Thoroughbred Express Auto Wash</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Freestone Capital</t>
+  </si>
+  <si>
+    <t>Indiana | Kentucky | Ohio | Oregon | West Virginia | Washington</t>
+  </si>
+  <si>
+    <t>https://thoroughbredexpress.com/</t>
+  </si>
+  <si>
+    <t>Flagstop Car Wash</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Garnet Station Partners</t>
+  </si>
+  <si>
+    <t>https://www.flagstopcarwash.com/</t>
+  </si>
+  <si>
+    <t>Rocket Carwash</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>City+Ventures</t>
+  </si>
+  <si>
+    <t>Nebraska | Pennsylvania | Texas | California | Iowa | Utah | Florida</t>
+  </si>
+  <si>
+    <t>https://rocketcarwash.com/</t>
+  </si>
+  <si>
+    <t>Wash Masters Car Wash</t>
+  </si>
+  <si>
+    <t>Victron Energy Company</t>
+  </si>
+  <si>
+    <t>https://washmasters.com/</t>
+  </si>
+  <si>
+    <t>Woodie's Wash Shack</t>
+  </si>
+  <si>
+    <t>https://www.woodieswash.com/</t>
+  </si>
+  <si>
+    <t>Dash Car Wash</t>
+  </si>
+  <si>
+    <t>Arizona | Nevada</t>
+  </si>
+  <si>
+    <t>Fast 5 Xpress Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.fast5xpress.com/</t>
+  </si>
+  <si>
+    <t>Mr. Magic Car Wash</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Incline Equity Partners</t>
+  </si>
+  <si>
+    <t>Pennsylvania | West Virginia | Ohio</t>
+  </si>
+  <si>
+    <t>https://mrmagiccarwash.com/</t>
+  </si>
+  <si>
+    <t>Shiny Shell Car Wash</t>
+  </si>
+  <si>
+    <t>Utah | Pennsylvania | Maryland</t>
+  </si>
+  <si>
+    <t>https://www.shinyshell.com/</t>
+  </si>
+  <si>
     <t>The Wash Tub</t>
   </si>
   <si>
     <t>https://www.washtub.com/</t>
   </si>
   <si>
-    <t>Gas N Wash</t>
-  </si>
-  <si>
-    <t>Bow River Capital</t>
-  </si>
-  <si>
-    <t>https://www.gasnwash.net/</t>
-  </si>
-  <si>
-    <t>Hurricane Express Wash</t>
-  </si>
-  <si>
-    <t>South Carolina</t>
-  </si>
-  <si>
-    <t>PassiveInvesting.com</t>
-  </si>
-  <si>
-    <t>Tennessee | South Carolina | North Carolina | Florida | Maryland | Virginia | Alabama</t>
-  </si>
-  <si>
-    <t>https://www.hurricanewash.com/</t>
-  </si>
-  <si>
-    <t>Waterway Carwash</t>
-  </si>
-  <si>
-    <t>Kansas | Montana | Colorado | Illinois | Ohio</t>
-  </si>
-  <si>
-    <t>https://www.waterway.com/</t>
-  </si>
-  <si>
-    <t>Flagstop Car Wash</t>
-  </si>
-  <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t>Garnet Station Partners</t>
-  </si>
-  <si>
-    <t>https://www.flagstopcarwash.com/</t>
-  </si>
-  <si>
-    <t>Hoffman Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.hoffmancarwash.com/</t>
-  </si>
-  <si>
-    <t>Quick N Clean</t>
-  </si>
-  <si>
-    <t>Arizona | Colorado | Oklahoma | Texas</t>
-  </si>
-  <si>
-    <t>https://quicknclean.net/</t>
-  </si>
-  <si>
-    <t>Soapy Joe’s Car Wash</t>
-  </si>
-  <si>
-    <t>https://soapyjoescarwash.com/</t>
-  </si>
-  <si>
-    <t>Thoroughbred Express Auto Wash</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
-  </si>
-  <si>
-    <t>Freestone Capital</t>
-  </si>
-  <si>
-    <t>Indiana | Kentucky | Ohio | Oregon | West Virginia | Washington</t>
-  </si>
-  <si>
-    <t>https://thoroughbredexpress.com/</t>
-  </si>
-  <si>
-    <t>Trademark Car Wash</t>
-  </si>
-  <si>
-    <t>Princeton Equity Group / Accelerated Brands</t>
-  </si>
-  <si>
-    <t>Texas | Louisiana | Florida | New Mexico | Arizona | Tennessee | Michigan | Missouri</t>
-  </si>
-  <si>
-    <t>https://trademarkcarwash.com/</t>
-  </si>
-  <si>
-    <t>Rocket Carwash</t>
-  </si>
-  <si>
-    <t>Nebraska</t>
-  </si>
-  <si>
-    <t>City+Ventures</t>
-  </si>
-  <si>
-    <t>Nebraska | Pennsylvania | Texas | California | Iowa | Utah | Florida</t>
-  </si>
-  <si>
-    <t>https://rocketcarwash.com/</t>
-  </si>
-  <si>
-    <t>Wash Masters Car Wash</t>
-  </si>
-  <si>
-    <t>Victron Energy Company</t>
-  </si>
-  <si>
-    <t>https://washmasters.com/</t>
-  </si>
-  <si>
-    <t>Washville Car Wash</t>
-  </si>
-  <si>
-    <t>Garnett Reynolds Holdings</t>
-  </si>
-  <si>
-    <t>New York | Massachusetts | Rhode Island | New Hampshire | Maine</t>
-  </si>
-  <si>
-    <t>https://washvillecarwash.com/</t>
-  </si>
-  <si>
-    <t>Dash Car Wash</t>
-  </si>
-  <si>
-    <t>Arizona | Nevada</t>
-  </si>
-  <si>
-    <t>Fast 5 Xpress Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.fast5xpress.com/</t>
-  </si>
-  <si>
-    <t>Glide XPRESS Car Wash</t>
-  </si>
-  <si>
-    <t>Tennessee | Missouri | Arkansas | Mississippi</t>
-  </si>
-  <si>
-    <t>https://www.glidexwash.com/</t>
-  </si>
-  <si>
     <t>Carnation Auto Spa</t>
   </si>
   <si>
@@ -721,28 +808,25 @@
     <t>https://carnationautospa.com/</t>
   </si>
   <si>
-    <t>Mighty Wash</t>
-  </si>
-  <si>
-    <t>Texas | New Mexico</t>
-  </si>
-  <si>
-    <t>https://mymightywash.com/</t>
-  </si>
-  <si>
-    <t>Mr. Magic Car Wash</t>
-  </si>
-  <si>
-    <t>Pennsylvania</t>
-  </si>
-  <si>
-    <t>Incline Equity Partners</t>
-  </si>
-  <si>
-    <t>Pennsylvania | West Virginia | Ohio</t>
-  </si>
-  <si>
-    <t>https://mrmagiccarwash.com/</t>
+    <t>Dirty Dog’s Car Wash</t>
+  </si>
+  <si>
+    <t>Cynosure Group</t>
+  </si>
+  <si>
+    <t>Alabama | Florida | Georgia</t>
+  </si>
+  <si>
+    <t>https://dirtydogscarwash.com/</t>
+  </si>
+  <si>
+    <t>Elephant Super Car Wash</t>
+  </si>
+  <si>
+    <t>Washington | Arizona</t>
+  </si>
+  <si>
+    <t>https://elephantcarwash.com/</t>
   </si>
   <si>
     <t>ScrubaDub Auto Wash Centers</t>
@@ -754,40 +838,22 @@
     <t>https://www.scrubadub.com/</t>
   </si>
   <si>
+    <t>Suds Deluxe Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.sudsdeluxe.com/</t>
+  </si>
+  <si>
     <t>Splash Car Wash &amp; Oil Change</t>
   </si>
   <si>
     <t>https://cleancarfast.com</t>
   </si>
   <si>
-    <t>Woodie's Wash Shack</t>
-  </si>
-  <si>
-    <t>https://www.woodieswash.com/</t>
-  </si>
-  <si>
-    <t>Dirty Dog’s Car Wash</t>
-  </si>
-  <si>
-    <t>Cynosure Group</t>
-  </si>
-  <si>
-    <t>Alabama | Florida | Georgia</t>
-  </si>
-  <si>
-    <t>https://dirtydogscarwash.com/</t>
-  </si>
-  <si>
-    <t>Tagg-N-Go</t>
-  </si>
-  <si>
-    <t>Utah</t>
-  </si>
-  <si>
-    <t>Utah | Nevada | Idaho</t>
-  </si>
-  <si>
-    <t>https://taggngo.com/</t>
+    <t>Gate Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://gateexpresscarwash.com/</t>
   </si>
   <si>
     <t>Drive &amp; Shine Car Wash</t>
@@ -799,15 +865,6 @@
     <t>https://driveandshine.com/</t>
   </si>
   <si>
-    <t>Flash Car Wash</t>
-  </si>
-  <si>
-    <t>Connecticut | Massachusetts | Rhode Island</t>
-  </si>
-  <si>
-    <t>https://flashcarwashes.com/</t>
-  </si>
-  <si>
     <t>TruShine Car Wash</t>
   </si>
   <si>
@@ -817,6 +874,30 @@
     <t>https://www.trushinecarwash.com/</t>
   </si>
   <si>
+    <t>WOW Carwash</t>
+  </si>
+  <si>
+    <t>Garnett Station Partners, LLC</t>
+  </si>
+  <si>
+    <t>https://wowwash.com/</t>
+  </si>
+  <si>
+    <t>Big Peach Car Wash</t>
+  </si>
+  <si>
+    <t>Georgia | Tennessee | Florida</t>
+  </si>
+  <si>
+    <t>https://www.bigpeachusa.com/</t>
+  </si>
+  <si>
+    <t>Buddy Bear Car Wash</t>
+  </si>
+  <si>
+    <t>https://buddybearcarwash.com/</t>
+  </si>
+  <si>
     <t>Francis &amp; Sons Car Wash</t>
   </si>
   <si>
@@ -826,19 +907,28 @@
     <t>https://francisandsonscarwash.com/</t>
   </si>
   <si>
+    <t>Blue Tide Car Wash</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>https://bluetidecarwash.com/</t>
+  </si>
+  <si>
     <t>Fuller's Car Wash</t>
   </si>
   <si>
     <t>https://fullerscarwash.com/</t>
   </si>
   <si>
-    <t>Shiny Shell Car Wash</t>
-  </si>
-  <si>
-    <t>Utah | Pennsylvania | Maryland</t>
-  </si>
-  <si>
-    <t>https://www.shinyshell.com/</t>
+    <t>Kaady Car Wash</t>
+  </si>
+  <si>
+    <t>Oregon | Washington | California</t>
+  </si>
+  <si>
+    <t>https://kaady.com/</t>
   </si>
   <si>
     <t>Washman Car Washes</t>
@@ -847,270 +937,222 @@
     <t>https://www.washmanusa.com/</t>
   </si>
   <si>
+    <t>Bliss Car Wash</t>
+  </si>
+  <si>
+    <t>https://blisscarwash.com/</t>
+  </si>
+  <si>
+    <t>Fast Eddie's Car Wash &amp; Oil Change</t>
+  </si>
+  <si>
+    <t>https://www.fasteddiescarcare.com/</t>
+  </si>
+  <si>
+    <t>Raindrop Car Wash</t>
+  </si>
+  <si>
+    <t>https://raindropcarwash.com/</t>
+  </si>
+  <si>
+    <t>Rainforest Carwash &amp; Oil Change</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Louisiana | Mississippi</t>
+  </si>
+  <si>
+    <t>https://rainforestclean.com/</t>
+  </si>
+  <si>
+    <t>Zax Auto Wash</t>
+  </si>
+  <si>
+    <t>https://zaxautowash.com/</t>
+  </si>
+  <si>
+    <t>Car Spa</t>
+  </si>
+  <si>
+    <t>Florida | Georgia | Texas | Virginia</t>
+  </si>
+  <si>
+    <t>https://carspa.net/</t>
+  </si>
+  <si>
+    <t>Haffner's</t>
+  </si>
+  <si>
+    <t>Massachusetts | New Hampshire</t>
+  </si>
+  <si>
+    <t>https://haffners.com/</t>
+  </si>
+  <si>
+    <t>Mr. Sparkle Car Wash</t>
+  </si>
+  <si>
+    <t>Connecticut | Massachusetts | New Jersey</t>
+  </si>
+  <si>
+    <t>https://www.mrsparklecarwash.com/</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Car Wash</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Wyoming | Montana</t>
+  </si>
+  <si>
+    <t>https://rockymountaincarwash.com/</t>
+  </si>
+  <si>
+    <t>Sgt. Clean Car Wash</t>
+  </si>
+  <si>
+    <t>https://sgtclean.com/</t>
+  </si>
+  <si>
+    <t>Shammy Shine Car Washes</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>New Jersey | Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.shammyshine.com/</t>
+  </si>
+  <si>
+    <t>Cheetah Clean Auto Wash</t>
+  </si>
+  <si>
+    <t>Kentucky | Tennessee</t>
+  </si>
+  <si>
+    <t>https://cheetahclean.com/</t>
+  </si>
+  <si>
+    <t>Mach-1 Express Wash</t>
+  </si>
+  <si>
+    <t>Alabama | Georgia | North Carolina | Pennsylvania | Ohio | Delaware | New Jersey | Michigan</t>
+  </si>
+  <si>
+    <t>https://www.mach1expresswash.com/</t>
+  </si>
+  <si>
+    <t>Pelican Pointe Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.pelicanpointecarwash.com/</t>
+  </si>
+  <si>
+    <t>Breeze Thru Car Wash</t>
+  </si>
+  <si>
+    <t>Colorado | Wyoming</t>
+  </si>
+  <si>
+    <t>https://breezethrucarwash.com/</t>
+  </si>
+  <si>
+    <t>Carriage House Car Wash</t>
+  </si>
+  <si>
+    <t>Tire Discounters</t>
+  </si>
+  <si>
+    <t>Ohio | Indiana</t>
+  </si>
+  <si>
+    <t>https://carriagehousecarwash.com/</t>
+  </si>
+  <si>
+    <t>EDGE Express Car Wash</t>
+  </si>
+  <si>
+    <t>North Carolina | South Carolina | Virginia</t>
+  </si>
+  <si>
+    <t>https://www.edgeexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>Metro Express Car Wash</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>Idaho | Montana | Washington | Colorado | California | Missouri | Arizona | Kansas</t>
+  </si>
+  <si>
+    <t>https://www.metroexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>RocketFast Car Wash</t>
+  </si>
+  <si>
+    <t>Louisiana | Arkansas | Texas</t>
+  </si>
+  <si>
+    <t>https://www.rocketfastcarwash.com/</t>
+  </si>
+  <si>
+    <t>The Auto Spa</t>
+  </si>
+  <si>
+    <t>Maryland | Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.washluberepair.com/</t>
+  </si>
+  <si>
+    <t>The Bubble Bath Car Wash</t>
+  </si>
+  <si>
+    <t>San Antonio, TX</t>
+  </si>
+  <si>
+    <t>https://thebubblebathcarwash.com/</t>
+  </si>
+  <si>
+    <t>Valet Auto Wash</t>
+  </si>
+  <si>
+    <t>New Jersey | New York | Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://valetwash.com/</t>
+  </si>
+  <si>
+    <t>All American Car Wash</t>
+  </si>
+  <si>
+    <t>Racer Classic Investments, LLC</t>
+  </si>
+  <si>
+    <t>Texas | Oklahoma</t>
+  </si>
+  <si>
+    <t>https://www.allamericancarwash.biz/</t>
+  </si>
+  <si>
     <t>Bubble Down Car Wash</t>
   </si>
   <si>
-    <t>Locally Owned</t>
+    <t>BTG Pactual</t>
   </si>
   <si>
     <t>https://bubbledown.com/</t>
   </si>
   <si>
-    <t>Elephant Super Car Wash</t>
-  </si>
-  <si>
-    <t>https://elephantcarwash.com/</t>
-  </si>
-  <si>
-    <t>Kaady Car Wash</t>
-  </si>
-  <si>
-    <t>Oregon | Washington | California</t>
-  </si>
-  <si>
-    <t>https://kaady.com/</t>
-  </si>
-  <si>
-    <t>Ronny's Car Wash</t>
-  </si>
-  <si>
-    <t>Florida | Alabama</t>
-  </si>
-  <si>
-    <t>https://ronnyscarwash.net/</t>
-  </si>
-  <si>
-    <t>WOW Carwash</t>
-  </si>
-  <si>
-    <t>Garnett Station Partners, LLC</t>
-  </si>
-  <si>
-    <t>https://wowwash.com/</t>
-  </si>
-  <si>
-    <t>Big Peach Car Wash</t>
-  </si>
-  <si>
-    <t>Georgia | Tennessee | Florida</t>
-  </si>
-  <si>
-    <t>https://www.bigpeachusa.com/</t>
-  </si>
-  <si>
-    <t>Bliss Car Wash</t>
-  </si>
-  <si>
-    <t>https://blisscarwash.com/</t>
-  </si>
-  <si>
-    <t>Buddy Bear Car Wash</t>
-  </si>
-  <si>
-    <t>https://buddybearcarwash.com/</t>
-  </si>
-  <si>
-    <t>Fast Eddie's Car Wash &amp; Oil Change</t>
-  </si>
-  <si>
-    <t>https://www.fasteddiescarcare.com/</t>
-  </si>
-  <si>
-    <t>Gate Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://gateexpresscarwash.com/</t>
-  </si>
-  <si>
-    <t>Raindrop Car Wash</t>
-  </si>
-  <si>
-    <t>https://raindropcarwash.com/</t>
-  </si>
-  <si>
-    <t>Zax Auto Wash</t>
-  </si>
-  <si>
-    <t>https://zaxautowash.com/</t>
-  </si>
-  <si>
-    <t>Haffner's</t>
-  </si>
-  <si>
-    <t>Massachusetts | New Hampshire</t>
-  </si>
-  <si>
-    <t>https://haffners.com/</t>
-  </si>
-  <si>
-    <t>Rainforest Carwash &amp; Oil Change</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
-  </si>
-  <si>
-    <t>Louisiana | Mississippi</t>
-  </si>
-  <si>
-    <t>https://rainforestclean.com/</t>
-  </si>
-  <si>
-    <t>Rocky Mountain Car Wash</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Wyoming | Montana</t>
-  </si>
-  <si>
-    <t>https://rockymountaincarwash.com/</t>
-  </si>
-  <si>
-    <t>Sgt. Clean Car Wash</t>
-  </si>
-  <si>
-    <t>https://sgtclean.com/</t>
-  </si>
-  <si>
-    <t>Shammy Shine Car Washes</t>
-  </si>
-  <si>
-    <t>New Jersey</t>
-  </si>
-  <si>
-    <t>New Jersey | Pennsylvania</t>
-  </si>
-  <si>
-    <t>https://www.shammyshine.com/</t>
-  </si>
-  <si>
-    <t>Car Spa</t>
-  </si>
-  <si>
-    <t>Florida | Georgia | Texas | Virginia</t>
-  </si>
-  <si>
-    <t>https://carspa.net/</t>
-  </si>
-  <si>
-    <t>Cheetah Clean Auto Wash</t>
-  </si>
-  <si>
-    <t>Kentucky | Tennessee</t>
-  </si>
-  <si>
-    <t>https://cheetahclean.com/</t>
-  </si>
-  <si>
-    <t>Mach-1 Express Wash</t>
-  </si>
-  <si>
-    <t>Alabama | Georgia | North Carolina | Pennsylvania | Ohio | Delaware | New Jersey | Michigan</t>
-  </si>
-  <si>
-    <t>https://www.mach1expresswash.com/</t>
-  </si>
-  <si>
-    <t>Sud Stop Car Wash</t>
-  </si>
-  <si>
-    <t>Real Capital Partners</t>
-  </si>
-  <si>
-    <t>Florida | Georgia | Alabama | North Carolina | South Carolina</t>
-  </si>
-  <si>
-    <t>https://www.sudstopcarwash.com/</t>
-  </si>
-  <si>
-    <t>Breeze Thru Car Wash</t>
-  </si>
-  <si>
-    <t>Colorado | Wyoming</t>
-  </si>
-  <si>
-    <t>https://breezethrucarwash.com/</t>
-  </si>
-  <si>
-    <t>Carriage House Car Wash</t>
-  </si>
-  <si>
-    <t>Tire Discounters</t>
-  </si>
-  <si>
-    <t>Ohio | Indiana</t>
-  </si>
-  <si>
-    <t>https://carriagehousecarwash.com/</t>
-  </si>
-  <si>
-    <t>EDGE Express Car Wash</t>
-  </si>
-  <si>
-    <t>North Carolina | South Carolina | Virginia</t>
-  </si>
-  <si>
-    <t>https://www.edgeexpresscarwash.com/</t>
-  </si>
-  <si>
-    <t>Metro Express Car Wash</t>
-  </si>
-  <si>
-    <t>Idaho</t>
-  </si>
-  <si>
-    <t>Idaho | Montana | Washington | Colorado | California | Missouri | Arizona | Kansas</t>
-  </si>
-  <si>
-    <t>https://www.metroexpresscarwash.com/</t>
-  </si>
-  <si>
-    <t>Pelican Pointe Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.pelicanpointecarwash.com/</t>
-  </si>
-  <si>
-    <t>The Auto Spa</t>
-  </si>
-  <si>
-    <t>Maryland | Pennsylvania</t>
-  </si>
-  <si>
-    <t>https://www.washluberepair.com/</t>
-  </si>
-  <si>
-    <t>The Bubble Bath Car Wash</t>
-  </si>
-  <si>
-    <t>San Antonio, TX</t>
-  </si>
-  <si>
-    <t>https://thebubblebathcarwash.com/</t>
-  </si>
-  <si>
-    <t>Valet Auto Wash</t>
-  </si>
-  <si>
-    <t>New Jersey | New York | Pennsylvania</t>
-  </si>
-  <si>
-    <t>https://valetwash.com/</t>
-  </si>
-  <si>
-    <t>All American Car Wash</t>
-  </si>
-  <si>
-    <t>Racer Classic Investments, LLC</t>
-  </si>
-  <si>
-    <t>Texas | Oklahoma</t>
-  </si>
-  <si>
-    <t>https://www.allamericancarwash.biz/</t>
-  </si>
-  <si>
     <t>Charlie’s Car Wash</t>
   </si>
   <si>
@@ -1141,34 +1183,148 @@
     <t>https://ishinecarwash.com/</t>
   </si>
   <si>
+    <t>Speedy Stop Car Wash</t>
+  </si>
+  <si>
+    <t>https://speedystop.com/</t>
+  </si>
+  <si>
+    <t>Team Car Wash</t>
+  </si>
+  <si>
+    <t>https://theteamcarwash.com/</t>
+  </si>
+  <si>
+    <t>Wash-Rite Express Car Wash</t>
+  </si>
+  <si>
+    <t>Bradham Capital Holdings</t>
+  </si>
+  <si>
+    <t>Ohio | Pennsylvania | West Virginia</t>
+  </si>
+  <si>
+    <t>https://www.wash-riteunlimited.com</t>
+  </si>
+  <si>
+    <t>White Horse Auto Wash</t>
+  </si>
+  <si>
+    <t>Virginia | South Carolina</t>
+  </si>
+  <si>
+    <t>https://www.whitehorseautowash.com/</t>
+  </si>
+  <si>
+    <t>Dream Clean Car Wash</t>
+  </si>
+  <si>
+    <t>Cross Timbers Capital Group</t>
+  </si>
+  <si>
+    <t>https://www.dreamcleancw.com/</t>
+  </si>
+  <si>
+    <t>Fast Splash Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.fastsplashcarwash.com/</t>
+  </si>
+  <si>
     <t>Jacksons</t>
   </si>
   <si>
     <t>https://jacksonswash.com/</t>
   </si>
   <si>
-    <t>Speedy Stop Car Wash</t>
-  </si>
-  <si>
-    <t>https://speedystop.com/</t>
-  </si>
-  <si>
-    <t>Team Car Wash</t>
-  </si>
-  <si>
-    <t>https://theteamcarwash.com/</t>
-  </si>
-  <si>
-    <t>Wash-Rite Express Car Wash</t>
-  </si>
-  <si>
-    <t>Bradham Capital Holdings</t>
-  </si>
-  <si>
-    <t>Ohio | Pennsylvania | West Virginia</t>
-  </si>
-  <si>
-    <t>https://www.wash-riteunlimited.com</t>
+    <t>Ocean Blue Car Wash</t>
+  </si>
+  <si>
+    <t>https://oceanbluecarwash.com/</t>
+  </si>
+  <si>
+    <t>Shine Time Super Wash</t>
+  </si>
+  <si>
+    <t>Alabama | Mississippi</t>
+  </si>
+  <si>
+    <t>https://www.shinetimesuperwash.com/</t>
+  </si>
+  <si>
+    <t>Super Clean Car Wash</t>
+  </si>
+  <si>
+    <t>https://supercleanmycar.com/</t>
+  </si>
+  <si>
+    <t>Xtreme Auto Wash</t>
+  </si>
+  <si>
+    <t>7 Flags Car Wash</t>
+  </si>
+  <si>
+    <t>https://7flagscarwash.com/</t>
+  </si>
+  <si>
+    <t>Ducky's Car Wash</t>
+  </si>
+  <si>
+    <t>https://duckysexpress.com/</t>
+  </si>
+  <si>
+    <t>Everclean Car Wash</t>
+  </si>
+  <si>
+    <t>https://evercleancw.com/</t>
+  </si>
+  <si>
+    <t>Hang 10 Car Wash</t>
+  </si>
+  <si>
+    <t>Florida | New Jersey | South Carolina | Virginia</t>
+  </si>
+  <si>
+    <t>https://hang10carwash.com/</t>
+  </si>
+  <si>
+    <t>Mr Wash Car Wash</t>
+  </si>
+  <si>
+    <t>Virginia | Maryland | Delaware</t>
+  </si>
+  <si>
+    <t>https://mrwash.com/</t>
+  </si>
+  <si>
+    <t>Radiant Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.radiantexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>Red Carpet Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.redcarpetcarwash.com/</t>
+  </si>
+  <si>
+    <t>Scenic Suds Car Wash</t>
+  </si>
+  <si>
+    <t>Tennessee | Georgia</t>
+  </si>
+  <si>
+    <t>https://www.scenicsuds.com/</t>
+  </si>
+  <si>
+    <t>Scrub-a-Dub</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>https://scrubadub.biz/</t>
   </si>
   <si>
     <t>WashU Car Wash</t>
@@ -1183,100 +1339,373 @@
     <t>https://www.washucarwash.com/</t>
   </si>
   <si>
-    <t>White Horse Auto Wash</t>
-  </si>
-  <si>
-    <t>Virginia | South Carolina</t>
-  </si>
-  <si>
-    <t>https://www.whitehorseautowash.com/</t>
-  </si>
-  <si>
-    <t>Dream Clean Car Wash</t>
-  </si>
-  <si>
-    <t>Cross Timbers Capital Group</t>
-  </si>
-  <si>
-    <t>https://www.dreamcleancw.com/</t>
-  </si>
-  <si>
-    <t>Fast Splash Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.fastsplashcarwash.com/</t>
-  </si>
-  <si>
-    <t>Hang 10 Car Wash</t>
-  </si>
-  <si>
-    <t>Florida | New Jersey | South Carolina | Virginia</t>
-  </si>
-  <si>
-    <t>https://hang10carwash.com/</t>
-  </si>
-  <si>
-    <t>RocketFast Car Wash</t>
-  </si>
-  <si>
-    <t>Louisiana | Arkansas | Texas</t>
-  </si>
-  <si>
-    <t>https://www.rocketfastcarwash.com/</t>
-  </si>
-  <si>
-    <t>Super Clean Car Wash</t>
-  </si>
-  <si>
-    <t>https://supercleanmycar.com/</t>
-  </si>
-  <si>
-    <t>Xtreme Auto Wash</t>
-  </si>
-  <si>
-    <t>7 Flags Car Wash</t>
-  </si>
-  <si>
-    <t>https://7flagscarwash.com/</t>
-  </si>
-  <si>
-    <t>Ducky's Car Wash</t>
-  </si>
-  <si>
-    <t>https://duckysexpress.com/</t>
-  </si>
-  <si>
-    <t>Mr Wash Car Wash</t>
-  </si>
-  <si>
-    <t>Virginia | Maryland | Delaware</t>
-  </si>
-  <si>
-    <t>https://mrwash.com/</t>
-  </si>
-  <si>
-    <t>Red Carpet Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.redcarpetcarwash.com/</t>
-  </si>
-  <si>
-    <t>Scrub-a-Dub</t>
-  </si>
-  <si>
-    <t>Wisconsin</t>
-  </si>
-  <si>
-    <t>https://scrubadub.biz/</t>
-  </si>
-  <si>
-    <t>Shine Time Super Wash</t>
-  </si>
-  <si>
-    <t>Alabama | Mississippi</t>
-  </si>
-  <si>
-    <t>https://www.shinetimesuperwash.com/</t>
+    <t>Xpress Car Wash</t>
+  </si>
+  <si>
+    <t>Louisiana | Texas</t>
+  </si>
+  <si>
+    <t>https://timeitxpresswash.com/</t>
+  </si>
+  <si>
+    <t>Classy Chassis</t>
+  </si>
+  <si>
+    <t>https://classychassis.com/</t>
+  </si>
+  <si>
+    <t>Valet Car Wash</t>
+  </si>
+  <si>
+    <t>Ontario</t>
+  </si>
+  <si>
+    <t>https://washmycar.ca/</t>
+  </si>
+  <si>
+    <t>Blue Penguin Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.bluepenguincarwash.com/</t>
+  </si>
+  <si>
+    <t>BriteworX Car Washery</t>
+  </si>
+  <si>
+    <t>Missouri | Illinois</t>
+  </si>
+  <si>
+    <t>https://briteworx.com/</t>
+  </si>
+  <si>
+    <t>Cloud 10 Smartwash</t>
+  </si>
+  <si>
+    <t>Pennsylvania | New Jersey</t>
+  </si>
+  <si>
+    <t>https://cloud10smartwash.com/</t>
+  </si>
+  <si>
+    <t>Groove Car Wash</t>
+  </si>
+  <si>
+    <t>Vaquero Ventures</t>
+  </si>
+  <si>
+    <t>Texas | Florida | Oklahoma</t>
+  </si>
+  <si>
+    <t>https://www.groovecarwash.com/</t>
+  </si>
+  <si>
+    <t>Scrubby’s Car Wash</t>
+  </si>
+  <si>
+    <t>South Carolina | North Carolina</t>
+  </si>
+  <si>
+    <t>https://scrubbyscarwashes.com/</t>
+  </si>
+  <si>
+    <t>Skweeky Kleen Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.skweekykleen.com/</t>
+  </si>
+  <si>
+    <t>SpeedWash Car Wash</t>
+  </si>
+  <si>
+    <t>Kentucky | Indiana</t>
+  </si>
+  <si>
+    <t>https://speedwashusa.com/</t>
+  </si>
+  <si>
+    <t>WashGuys Car Wash</t>
+  </si>
+  <si>
+    <t>https://washguystx.com/</t>
+  </si>
+  <si>
+    <t>Sparkle Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://sparklestatus.com/</t>
+  </si>
+  <si>
+    <t>Auto Spa Car Wash (WA)</t>
+  </si>
+  <si>
+    <t>https://www.autospacw.com</t>
+  </si>
+  <si>
+    <t>Benny’s Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.bennyscarwash.com/</t>
+  </si>
+  <si>
+    <t>Driven Car Wash</t>
+  </si>
+  <si>
+    <t>https://drivencarwash.com/</t>
+  </si>
+  <si>
+    <t>Fabulous Freddy’s Car Wash</t>
+  </si>
+  <si>
+    <t>Nevada | Utah</t>
+  </si>
+  <si>
+    <t>https://fabfred.com/</t>
+  </si>
+  <si>
+    <t>Jet Splash Car Wash</t>
+  </si>
+  <si>
+    <t>https://jetsplash.com</t>
+  </si>
+  <si>
+    <t>Rocket Wash</t>
+  </si>
+  <si>
+    <t>North Carolina | South Carolina</t>
+  </si>
+  <si>
+    <t>https://rocketcarwashexpress.com/</t>
+  </si>
+  <si>
+    <t>Velocity Car Wash</t>
+  </si>
+  <si>
+    <t>Colorado | Utah</t>
+  </si>
+  <si>
+    <t>https://www.velocitywash.com/</t>
+  </si>
+  <si>
+    <t>Genie Car Wash</t>
+  </si>
+  <si>
+    <t>California | Arizona</t>
+  </si>
+  <si>
+    <t>https://www.geniecarwash.com/</t>
+  </si>
+  <si>
+    <t>American Pride Xpress Carwash</t>
+  </si>
+  <si>
+    <t>https://americanpridexpress.com/</t>
+  </si>
+  <si>
+    <t>Auto Spa LA</t>
+  </si>
+  <si>
+    <t>https://autospala.com/</t>
+  </si>
+  <si>
+    <t>Pony Express Carwash</t>
+  </si>
+  <si>
+    <t>https://ponycarwash.com/</t>
+  </si>
+  <si>
+    <t>Snap Clean Car Wash</t>
+  </si>
+  <si>
+    <t>https://snapcleancarwash.com/</t>
+  </si>
+  <si>
+    <t>Speedwash</t>
+  </si>
+  <si>
+    <t>https://www.speedwashes.com/</t>
+  </si>
+  <si>
+    <t>TipTop Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.tiptopcarwashes.com/</t>
+  </si>
+  <si>
+    <t>Ocean Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://oceancarwashtx.com/</t>
+  </si>
+  <si>
+    <t>Mint Smartwash</t>
+  </si>
+  <si>
+    <t>Alberta</t>
+  </si>
+  <si>
+    <t>https://mintsmartwash.com/</t>
+  </si>
+  <si>
+    <t>Halo Car Wash</t>
+  </si>
+  <si>
+    <t>https://halowash.com/</t>
+  </si>
+  <si>
+    <t>Cadillac Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.cadillacexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>Clearwave Car Wash</t>
+  </si>
+  <si>
+    <t>Illinois | Michigan</t>
+  </si>
+  <si>
+    <t>https://clearwavecarwash.com/</t>
+  </si>
+  <si>
+    <t>Greenhill Car Wash</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>https://greenhillcarwash.com/</t>
+  </si>
+  <si>
+    <t>H2Go Car Wash</t>
+  </si>
+  <si>
+    <t>Privately Owned</t>
+  </si>
+  <si>
+    <t>https://h2gocarwash.com/</t>
+  </si>
+  <si>
+    <t>Supershine Xpress Carwash</t>
+  </si>
+  <si>
+    <t>https://supershinexpress.com/</t>
+  </si>
+  <si>
+    <t>Washtopia Car Wash</t>
+  </si>
+  <si>
+    <t>https://washtopia.com/</t>
+  </si>
+  <si>
+    <t>The Wave Car Wash (WA)</t>
+  </si>
+  <si>
+    <t>https://www.thewavewash.com/</t>
+  </si>
+  <si>
+    <t>Bebo's Carwash</t>
+  </si>
+  <si>
+    <t>https://www.beboscarwash.com/</t>
+  </si>
+  <si>
+    <t>Endless Clean Car Wash</t>
+  </si>
+  <si>
+    <t>https://endlesscleancarwash.com/</t>
+  </si>
+  <si>
+    <t>Mr. Splash Car Wash</t>
+  </si>
+  <si>
+    <t>Argosy Private Equity</t>
+  </si>
+  <si>
+    <t>https://mrsplashcarwash.com/</t>
+  </si>
+  <si>
+    <t>RaceWash</t>
+  </si>
+  <si>
+    <t>Florida | Indiana | Kentucky</t>
+  </si>
+  <si>
+    <t>https://racewash.com/</t>
+  </si>
+  <si>
+    <t>Shur-Kleen Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.shurkleencarwash.com/</t>
+  </si>
+  <si>
+    <t>Great White Car Wash</t>
+  </si>
+  <si>
+    <t>https://greatwhitewash.com/</t>
+  </si>
+  <si>
+    <t>5 Minute Express Car Wash</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>https://5minuteexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>Camel Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://camelexpress.com/</t>
+  </si>
+  <si>
+    <t>Fast Freddy’s Car Wash</t>
+  </si>
+  <si>
+    <t>https://fastfreddyscarwashes.com/</t>
+  </si>
+  <si>
+    <t>FullSpeed Automotive</t>
+  </si>
+  <si>
+    <t>New Mexico | Texas</t>
+  </si>
+  <si>
+    <t>https://fullspeedautomotive.com/</t>
+  </si>
+  <si>
+    <t>Gleaux Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.gleauxcarwash.com/</t>
+  </si>
+  <si>
+    <t>Magic Brush Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.magicbrushexpress.com/</t>
+  </si>
+  <si>
+    <t>Ridi Stores</t>
+  </si>
+  <si>
+    <t>https://ridistores.com/</t>
+  </si>
+  <si>
+    <t>Screaming Eagle  Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.screamingeagleexpress.com/</t>
+  </si>
+  <si>
+    <t>Soapy Noble Car Wash</t>
+  </si>
+  <si>
+    <t>Connecticut | Massachusetts</t>
+  </si>
+  <si>
+    <t>https://soapynoble.com/</t>
   </si>
   <si>
     <t>Wash Factory Car Wash</t>
@@ -1288,460 +1717,31 @@
     <t>https://www.washfactorycarwash.com/</t>
   </si>
   <si>
-    <t>Xpress Car Wash</t>
-  </si>
-  <si>
-    <t>Louisiana | Texas</t>
-  </si>
-  <si>
-    <t>https://timeitxpresswash.com/</t>
-  </si>
-  <si>
-    <t>Classy Chassis</t>
-  </si>
-  <si>
-    <t>https://classychassis.com/</t>
-  </si>
-  <si>
-    <t>Genie Car Wash</t>
-  </si>
-  <si>
-    <t>California | Arizona</t>
-  </si>
-  <si>
-    <t>https://www.geniecarwash.com/</t>
-  </si>
-  <si>
-    <t>Halo Car Wash</t>
-  </si>
-  <si>
-    <t>Ontario</t>
-  </si>
-  <si>
-    <t>https://halowash.com/</t>
-  </si>
-  <si>
-    <t>Valet Car Wash</t>
-  </si>
-  <si>
-    <t>https://washmycar.ca/</t>
-  </si>
-  <si>
-    <t>Blue Penguin Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.bluepenguincarwash.com/</t>
-  </si>
-  <si>
-    <t>BriteworX Car Washery</t>
-  </si>
-  <si>
-    <t>Missouri | Illinois</t>
-  </si>
-  <si>
-    <t>https://briteworx.com/</t>
-  </si>
-  <si>
-    <t>Cloud 10 Smartwash</t>
-  </si>
-  <si>
-    <t>Pennsylvania | New Jersey</t>
-  </si>
-  <si>
-    <t>https://cloud10smartwash.com/</t>
-  </si>
-  <si>
-    <t>Everclean Car Wash</t>
-  </si>
-  <si>
-    <t>https://evercleancw.com/</t>
-  </si>
-  <si>
-    <t>Groove Car Wash</t>
-  </si>
-  <si>
-    <t>Vaquero Ventures</t>
-  </si>
-  <si>
-    <t>Texas | Florida | Oklahoma</t>
-  </si>
-  <si>
-    <t>https://www.groovecarwash.com/</t>
-  </si>
-  <si>
-    <t>Scenic Suds Car Wash</t>
-  </si>
-  <si>
-    <t>Tennessee | Georgia</t>
-  </si>
-  <si>
-    <t>https://www.scenicsuds.com/</t>
-  </si>
-  <si>
-    <t>Scrubby’s Car Wash</t>
-  </si>
-  <si>
-    <t>South Carolina | North Carolina</t>
-  </si>
-  <si>
-    <t>https://scrubbyscarwashes.com/</t>
-  </si>
-  <si>
-    <t>Skweeky Kleen Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.skweekykleen.com/</t>
-  </si>
-  <si>
-    <t>SpeedWash Car Wash</t>
-  </si>
-  <si>
-    <t>Kentucky | Indiana</t>
-  </si>
-  <si>
-    <t>https://speedwashusa.com/</t>
-  </si>
-  <si>
-    <t>Suds Deluxe Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.sudsdeluxe.com/</t>
-  </si>
-  <si>
-    <t>WashGuys Car Wash</t>
-  </si>
-  <si>
-    <t>https://washguystx.com/</t>
-  </si>
-  <si>
-    <t>Sparkle Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://sparklestatus.com/</t>
-  </si>
-  <si>
-    <t>Auto Spa Car Wash (WA)</t>
-  </si>
-  <si>
-    <t>https://www.autospacw.com</t>
-  </si>
-  <si>
-    <t>Benny’s Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.bennyscarwash.com/</t>
-  </si>
-  <si>
-    <t>Driven Car Wash</t>
-  </si>
-  <si>
-    <t>https://drivencarwash.com/</t>
-  </si>
-  <si>
-    <t>Fabulous Freddy’s Car Wash</t>
-  </si>
-  <si>
-    <t>Nevada | Utah</t>
-  </si>
-  <si>
-    <t>https://fabfred.com/</t>
-  </si>
-  <si>
-    <t>Jet Splash Car Wash</t>
-  </si>
-  <si>
-    <t>https://jetsplash.com</t>
-  </si>
-  <si>
-    <t>Radiant Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.radiantexpresscarwash.com/</t>
-  </si>
-  <si>
-    <t>Rocket Wash</t>
-  </si>
-  <si>
-    <t>North Carolina | South Carolina</t>
-  </si>
-  <si>
-    <t>https://rocketcarwashexpress.com/</t>
-  </si>
-  <si>
-    <t>Velocity Car Wash</t>
-  </si>
-  <si>
-    <t>Colorado | Utah</t>
-  </si>
-  <si>
-    <t>https://www.velocitywash.com/</t>
-  </si>
-  <si>
-    <t>Auto Spa LA</t>
-  </si>
-  <si>
-    <t>https://autospala.com/</t>
-  </si>
-  <si>
-    <t>Clearwave Car Wash</t>
-  </si>
-  <si>
-    <t>Illinois | Michigan</t>
-  </si>
-  <si>
-    <t>https://clearwavecarwash.com/</t>
-  </si>
-  <si>
-    <t>Ocean Blue Car Wash</t>
-  </si>
-  <si>
-    <t>https://oceanbluecarwash.com/</t>
-  </si>
-  <si>
-    <t>Snap Clean Car Wash</t>
-  </si>
-  <si>
-    <t>https://snapcleancarwash.com/</t>
-  </si>
-  <si>
-    <t>Speedwash</t>
-  </si>
-  <si>
-    <t>https://www.speedwashes.com/</t>
-  </si>
-  <si>
-    <t>TipTop Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.tiptopcarwashes.com/</t>
-  </si>
-  <si>
-    <t>Ocean Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://oceancarwashtx.com/</t>
-  </si>
-  <si>
-    <t>Greenhill Car Wash</t>
-  </si>
-  <si>
-    <t>Delaware</t>
-  </si>
-  <si>
-    <t>https://greenhillcarwash.com/</t>
-  </si>
-  <si>
-    <t>H2Go Car Wash</t>
-  </si>
-  <si>
-    <t>Privately Owned</t>
-  </si>
-  <si>
-    <t>https://h2gocarwash.com/</t>
-  </si>
-  <si>
-    <t>Pony Express Carwash</t>
-  </si>
-  <si>
-    <t>https://ponycarwash.com/</t>
-  </si>
-  <si>
-    <t>Washtopia Car Wash</t>
-  </si>
-  <si>
-    <t>https://washtopia.com/</t>
-  </si>
-  <si>
-    <t>The Wave Car Wash (WA)</t>
-  </si>
-  <si>
-    <t>https://www.thewavewash.com/</t>
-  </si>
-  <si>
-    <t>American Pride Xpress Carwash</t>
-  </si>
-  <si>
-    <t>https://americanpridexpress.com/</t>
-  </si>
-  <si>
-    <t>Bebo's Carwash</t>
-  </si>
-  <si>
-    <t>https://www.beboscarwash.com/</t>
-  </si>
-  <si>
-    <t>Blue Tide Car Wash</t>
-  </si>
-  <si>
-    <t>South Dakota</t>
-  </si>
-  <si>
-    <t>https://bluetidecarwash.com/</t>
-  </si>
-  <si>
-    <t>Endless Clean Car Wash</t>
-  </si>
-  <si>
-    <t>https://endlesscleancarwash.com/</t>
-  </si>
-  <si>
-    <t>Mr. Sparkle Car Wash</t>
-  </si>
-  <si>
-    <t>Connecticut | Massachusetts | New Jersey</t>
-  </si>
-  <si>
-    <t>https://www.mrsparklecarwash.com/</t>
-  </si>
-  <si>
-    <t>Mr. Splash Car Wash</t>
-  </si>
-  <si>
-    <t>Argosy Private Equity</t>
-  </si>
-  <si>
-    <t>https://mrsplashcarwash.com/</t>
-  </si>
-  <si>
-    <t>RaceWash</t>
-  </si>
-  <si>
-    <t>Florida | Indiana | Kentucky</t>
-  </si>
-  <si>
-    <t>https://racewash.com/</t>
-  </si>
-  <si>
-    <t>Screaming Eagle  Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.screamingeagleexpress.com/</t>
-  </si>
-  <si>
-    <t>Shur-Kleen Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.shurkleencarwash.com/</t>
+    <t>Waves Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://wavesexpresswash.com/</t>
+  </si>
+  <si>
+    <t>Fast Trak Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.fasttrakcarwash.com/</t>
+  </si>
+  <si>
+    <t>Mint Express</t>
+  </si>
+  <si>
+    <t>https://www.mintexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>Ace Auto Washes</t>
   </si>
   <si>
     <t>Spin Car Wash</t>
   </si>
   <si>
     <t>https://spincarwash.com/</t>
-  </si>
-  <si>
-    <t>Supershine Xpress Carwash</t>
-  </si>
-  <si>
-    <t>https://supershinexpress.com/</t>
-  </si>
-  <si>
-    <t>Mint Smartwash</t>
-  </si>
-  <si>
-    <t>Alberta</t>
-  </si>
-  <si>
-    <t>https://mintsmartwash.com/</t>
-  </si>
-  <si>
-    <t>Great White Car Wash</t>
-  </si>
-  <si>
-    <t>https://greatwhitewash.com/</t>
-  </si>
-  <si>
-    <t>5 Minute Express Car Wash</t>
-  </si>
-  <si>
-    <t>Mississippi</t>
-  </si>
-  <si>
-    <t>https://5minuteexpresscarwash.com/</t>
-  </si>
-  <si>
-    <t>Auto Wash Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.autowashcarwash.com/</t>
-  </si>
-  <si>
-    <t>Cadillac Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.cadillacexpresscarwash.com/</t>
-  </si>
-  <si>
-    <t>Camel Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://camelexpress.com/</t>
-  </si>
-  <si>
-    <t>Fast Freddy’s Car Wash</t>
-  </si>
-  <si>
-    <t>https://fastfreddyscarwashes.com/</t>
-  </si>
-  <si>
-    <t>FullSpeed Automotive</t>
-  </si>
-  <si>
-    <t>New Mexico | Texas</t>
-  </si>
-  <si>
-    <t>https://fullspeedautomotive.com/</t>
-  </si>
-  <si>
-    <t>Gleaux Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.gleauxcarwash.com/</t>
-  </si>
-  <si>
-    <t>Magic Brush Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.magicbrushexpress.com/</t>
-  </si>
-  <si>
-    <t>Ridi Stores</t>
-  </si>
-  <si>
-    <t>https://ridistores.com/</t>
-  </si>
-  <si>
-    <t>Soapy Noble Car Wash</t>
-  </si>
-  <si>
-    <t>Connecticut | Massachusetts</t>
-  </si>
-  <si>
-    <t>https://soapynoble.com/</t>
-  </si>
-  <si>
-    <t>Waves Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://wavesexpresswash.com/</t>
-  </si>
-  <si>
-    <t>Fast Trak Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.fasttrakcarwash.com/</t>
-  </si>
-  <si>
-    <t>Mint Express</t>
-  </si>
-  <si>
-    <t>https://www.mintexpresscarwash.com/</t>
-  </si>
-  <si>
-    <t>Bubbles Car Washes and Detail Centres</t>
-  </si>
-  <si>
-    <t>https://bubbles.ca/</t>
   </si>
 </sst>
 </file>
@@ -2331,22 +2331,22 @@
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2002.0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>250.0</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>213.0</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -2369,28 +2369,28 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2019.0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>213.0</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="2">
-        <v>2004.0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>197.0</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -2413,19 +2413,19 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2">
-        <v>1993.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E10" s="2">
-        <v>192.0</v>
+        <v>197.0</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>50</v>
@@ -2463,22 +2463,22 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1993.0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>192.0</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>154.0</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -2501,28 +2501,28 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2">
-        <v>2015.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E12" s="2">
         <v>154.0</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -2545,19 +2545,19 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2">
-        <v>2002.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E13" s="2">
-        <v>150.0</v>
+        <v>144.0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>64</v>
@@ -2601,7 +2601,7 @@
         <v>2018.0</v>
       </c>
       <c r="E14" s="2">
-        <v>141.0</v>
+        <v>132.0</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>31</v>
@@ -2686,19 +2686,19 @@
         <v>77</v>
       </c>
       <c r="D16" s="2">
-        <v>2022.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E16" s="2">
-        <v>104.0</v>
+        <v>100.0</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2721,25 +2721,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2022.0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>92.0</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="2">
-        <v>2010.0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>100.0</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>84</v>
@@ -2815,22 +2815,22 @@
         <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="D19" s="2">
         <v>2021.0</v>
       </c>
       <c r="E19" s="2">
-        <v>83.0</v>
+        <v>91.0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -2853,28 +2853,28 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D20" s="2">
-        <v>2021.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E20" s="2">
-        <v>77.0</v>
+        <v>85.0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2897,28 +2897,28 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="D21" s="2">
-        <v>1981.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E21" s="2">
-        <v>77.0</v>
+        <v>83.0</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -2941,28 +2941,28 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2">
         <v>2015.0</v>
       </c>
       <c r="E22" s="2">
-        <v>71.0</v>
+        <v>83.0</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -2985,19 +2985,19 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="D23" s="2">
-        <v>2016.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E23" s="2">
-        <v>68.0</v>
+        <v>77.0</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>106</v>
@@ -3035,13 +3035,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D24" s="2">
-        <v>2019.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E24" s="2">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>110</v>
@@ -3082,19 +3082,19 @@
         <v>114</v>
       </c>
       <c r="D25" s="2">
-        <v>1970.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E25" s="2">
-        <v>58.0</v>
+        <v>60.0</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -3117,28 +3117,28 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1953.0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>59.0</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="2">
-        <v>2007.0</v>
-      </c>
-      <c r="E26" s="2">
-        <v>58.0</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -3161,28 +3161,28 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="D27" s="2">
-        <v>2015.0</v>
+        <v>1970.0</v>
       </c>
       <c r="E27" s="2">
-        <v>54.0</v>
+        <v>58.0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -3205,28 +3205,28 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="D28" s="2">
-        <v>1957.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E28" s="2">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -3249,28 +3249,28 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="D29" s="2">
-        <v>1948.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E29" s="2">
-        <v>50.0</v>
+        <v>54.0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -3293,28 +3293,28 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="D30" s="2">
-        <v>2012.0</v>
+        <v>1948.0</v>
       </c>
       <c r="E30" s="2">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -3337,28 +3337,26 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="D31" s="2">
-        <v>1953.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E31" s="2">
-        <v>49.0</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>136</v>
-      </c>
+        <v>51.0</v>
+      </c>
+      <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -3381,28 +3379,28 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="D32" s="2">
-        <v>1997.0</v>
+        <v>1957.0</v>
       </c>
       <c r="E32" s="2">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -3425,28 +3423,28 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2">
-        <v>1959.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E33" s="2">
-        <v>47.0</v>
+        <v>50.0</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -3469,28 +3467,28 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D34" s="2">
-        <v>2009.0</v>
+        <v>1988.0</v>
       </c>
       <c r="E34" s="2">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -3513,28 +3511,28 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="D35" s="2">
-        <v>2020.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E35" s="2">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="G35" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -3557,28 +3555,28 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="D36" s="2">
-        <v>1988.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E36" s="2">
-        <v>45.0</v>
+        <v>48.0</v>
       </c>
       <c r="F36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -3601,28 +3599,28 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="D37" s="2">
-        <v>1995.0</v>
+        <v>1959.0</v>
       </c>
       <c r="E37" s="2">
-        <v>42.0</v>
+        <v>47.0</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -3645,28 +3643,28 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D38" s="2">
-        <v>2013.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E38" s="2">
-        <v>42.0</v>
+        <v>46.0</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -3689,28 +3687,28 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="D39" s="2">
-        <v>1976.0</v>
+        <v>1948.0</v>
       </c>
       <c r="E39" s="2">
-        <v>41.0</v>
+        <v>44.0</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -3733,28 +3731,28 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D40" s="2">
-        <v>1948.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E40" s="2">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>36</v>
+        <v>167</v>
       </c>
       <c r="G40" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -3777,19 +3775,19 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="D41" s="2">
-        <v>2011.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E41" s="2">
-        <v>36.0</v>
+        <v>41.0</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>36</v>
@@ -3827,10 +3825,10 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D42" s="2">
-        <v>2018.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E42" s="2">
         <v>36.0</v>
@@ -3871,22 +3869,22 @@
         <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="D43" s="2">
-        <v>1967.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E43" s="2">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G43" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -3909,25 +3907,25 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D44" s="2">
-        <v>1986.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E44" s="2">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>182</v>
@@ -3959,19 +3957,19 @@
         <v>9</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D45" s="2">
-        <v>2013.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E45" s="2">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
       <c r="F45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>185</v>
@@ -4003,22 +4001,22 @@
         <v>9</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1967.0</v>
+      </c>
+      <c r="E46" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D46" s="2">
-        <v>2015.0</v>
-      </c>
-      <c r="E46" s="2">
-        <v>30.0</v>
-      </c>
-      <c r="F46" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -4041,28 +4039,28 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="D47" s="2">
-        <v>1970.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E47" s="2">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G47" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -4085,28 +4083,28 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2018.0</v>
+      </c>
+      <c r="E48" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="D48" s="2">
-        <v>1981.0</v>
-      </c>
-      <c r="E48" s="2">
-        <v>28.0</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -4129,25 +4127,25 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="D49" s="2">
-        <v>1965.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E49" s="2">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>36</v>
+        <v>197</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>199</v>
@@ -4179,13 +4177,13 @@
         <v>9</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="D50" s="2">
-        <v>1992.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E50" s="2">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>36</v>
@@ -4223,22 +4221,22 @@
         <v>9</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="D51" s="2">
-        <v>2011.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E51" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>36</v>
+        <v>30.0</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -4261,25 +4259,25 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="D52" s="2">
-        <v>2020.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E52" s="2">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>207</v>
+        <v>36</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>209</v>
@@ -4311,22 +4309,22 @@
         <v>9</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D53" s="2">
-        <v>2004.0</v>
+        <v>1970.0</v>
       </c>
       <c r="E53" s="2">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H53" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -4349,28 +4347,28 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>215</v>
+        <v>138</v>
       </c>
       <c r="D54" s="2">
-        <v>2000.0</v>
+        <v>1965.0</v>
       </c>
       <c r="E54" s="2">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -4393,28 +4391,28 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D55" s="2">
         <v>2004.0</v>
       </c>
       <c r="E55" s="2">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>59</v>
+        <v>217</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4437,28 +4435,28 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>178</v>
+        <v>15</v>
       </c>
       <c r="D56" s="2">
-        <v>2019.0</v>
+        <v>1992.0</v>
       </c>
       <c r="E56" s="2">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>223</v>
+        <v>36</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -4481,23 +4479,29 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="1"/>
+      <c r="C57" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="D57" s="2">
-        <v>2021.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E57" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="F57" s="1"/>
+        <v>27.0</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G57" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H57" s="1"/>
+        <v>223</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -4519,28 +4523,28 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D58" s="2">
-        <v>2013.0</v>
+        <v>2024.0</v>
       </c>
       <c r="E58" s="2">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>36</v>
+        <v>226</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -4563,28 +4567,28 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>72</v>
+        <v>230</v>
       </c>
       <c r="D59" s="2">
-        <v>2018.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E59" s="2">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>36</v>
+        <v>231</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -4607,28 +4611,28 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>59</v>
+        <v>235</v>
       </c>
       <c r="D60" s="2">
-        <v>2021.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E60" s="2">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>59</v>
+        <v>235</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -4651,28 +4655,28 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>59</v>
+        <v>239</v>
       </c>
       <c r="D61" s="2">
-        <v>2012.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E61" s="2">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -4695,28 +4699,28 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>240</v>
+        <v>63</v>
       </c>
       <c r="D62" s="2">
-        <v>1959.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E62" s="2">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>242</v>
+        <v>63</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -4739,28 +4743,28 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D63" s="2">
-        <v>1966.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E63" s="2">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -4783,29 +4787,23 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="C64" s="1"/>
       <c r="D64" s="2">
-        <v>1981.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E64" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>24.0</v>
+      </c>
+      <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>248</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -4827,28 +4825,28 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D65" s="2">
-        <v>2019.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E65" s="2">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -4871,28 +4869,28 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>25</v>
+        <v>253</v>
       </c>
       <c r="D66" s="2">
-        <v>2019.0</v>
+        <v>1959.0</v>
       </c>
       <c r="E66" s="2">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -4915,28 +4913,28 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="D67" s="2">
-        <v>2016.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E67" s="2">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
@@ -4959,25 +4957,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="D68" s="2">
-        <v>1997.0</v>
+        <v>1986.0</v>
       </c>
       <c r="E68" s="2">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>260</v>
+        <v>63</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>261</v>
@@ -5009,19 +5007,19 @@
         <v>9</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="D69" s="2">
-        <v>2012.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E69" s="2">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>36</v>
+        <v>263</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>263</v>
+        <v>63</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>264</v>
@@ -5053,22 +5051,22 @@
         <v>9</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D70" s="2">
         <v>2019.0</v>
       </c>
       <c r="E70" s="2">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
@@ -5091,28 +5089,28 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="D71" s="2">
-        <v>1997.0</v>
+        <v>1951.0</v>
       </c>
       <c r="E71" s="2">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>269</v>
+        <v>36</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>15</v>
+        <v>270</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -5135,28 +5133,28 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="D72" s="2">
-        <v>1960.0</v>
+        <v>1966.0</v>
       </c>
       <c r="E72" s="2">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>40</v>
+        <v>273</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -5179,28 +5177,28 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>256</v>
+        <v>63</v>
       </c>
       <c r="D73" s="2">
-        <v>2012.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E73" s="2">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>274</v>
+        <v>63</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -5223,28 +5221,28 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="D74" s="2">
-        <v>1995.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E74" s="2">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -5267,25 +5265,25 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D75" s="2">
-        <v>2020.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E75" s="2">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>279</v>
+        <v>36</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>280</v>
@@ -5317,22 +5315,22 @@
         <v>9</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D76" s="2">
-        <v>1951.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E76" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -5355,28 +5353,28 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="D77" s="2">
-        <v>1976.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E77" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -5399,28 +5397,28 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="D78" s="2">
-        <v>2018.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E78" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>287</v>
+        <v>156</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -5443,28 +5441,28 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>142</v>
+        <v>25</v>
       </c>
       <c r="D79" s="2">
-        <v>2016.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E79" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>290</v>
+        <v>36</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>142</v>
+        <v>291</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -5487,25 +5485,25 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D80" s="2">
-        <v>2021.0</v>
+        <v>1982.0</v>
       </c>
       <c r="E80" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>293</v>
+        <v>44</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>294</v>
@@ -5537,22 +5535,22 @@
         <v>9</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D81" s="2">
-        <v>2019.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E81" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>36</v>
+        <v>296</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -5575,28 +5573,26 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D82" s="2">
-        <v>1982.0</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="D82" s="1"/>
       <c r="E82" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>40</v>
+        <v>299</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -5619,28 +5615,28 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D83" s="2">
-        <v>1977.0</v>
+        <v>1960.0</v>
       </c>
       <c r="E83" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -5663,28 +5659,28 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D84" s="2">
-        <v>2017.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E84" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -5707,28 +5703,28 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="D85" s="2">
-        <v>2017.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E85" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -5751,16 +5747,16 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D86" s="2">
-        <v>2015.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E86" s="2">
         <v>17.0</v>
@@ -5769,10 +5765,10 @@
         <v>36</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -5795,28 +5791,28 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="D87" s="2">
-        <v>1995.0</v>
+        <v>1977.0</v>
       </c>
       <c r="E87" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>308</v>
+        <v>35</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -5839,25 +5835,25 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>311</v>
+        <v>171</v>
       </c>
       <c r="D88" s="2">
-        <v>1993.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E88" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>312</v>
+        <v>171</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>313</v>
@@ -5892,10 +5888,10 @@
         <v>315</v>
       </c>
       <c r="D89" s="2">
-        <v>2001.0</v>
+        <v>1993.0</v>
       </c>
       <c r="E89" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>36</v>
@@ -5933,19 +5929,19 @@
         <v>9</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D90" s="2">
-        <v>2013.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E90" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>319</v>
@@ -5977,10 +5973,10 @@
         <v>9</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>321</v>
+        <v>63</v>
       </c>
       <c r="D91" s="2">
-        <v>1976.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E91" s="2">
         <v>16.0</v>
@@ -5989,10 +5985,10 @@
         <v>36</v>
       </c>
       <c r="G91" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="H91" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
@@ -6015,28 +6011,28 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="D92" s="2">
-        <v>1999.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E92" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G92" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H92" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -6059,28 +6055,28 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="D93" s="2">
-        <v>2007.0</v>
+        <v>1966.0</v>
       </c>
       <c r="E93" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G93" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -6103,19 +6099,19 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="D94" s="2">
-        <v>2018.0</v>
+        <v>2001.0</v>
       </c>
       <c r="E94" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>36</v>
@@ -6153,22 +6149,22 @@
         <v>9</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D95" s="2">
-        <v>2024.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E95" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H95" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>336</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -6191,28 +6187,28 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>54</v>
+        <v>336</v>
       </c>
       <c r="D96" s="2">
-        <v>2007.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E96" s="2">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G96" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>338</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>339</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -6235,28 +6231,28 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="D97" s="2">
-        <v>2019.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E97" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="F97" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -6279,28 +6275,28 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="D98" s="2">
-        <v>2020.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E98" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -6323,28 +6319,28 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
       <c r="D99" s="2">
-        <v>1969.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E99" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -6367,16 +6363,16 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>311</v>
+        <v>58</v>
       </c>
       <c r="D100" s="2">
-        <v>2000.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E100" s="2">
         <v>14.0</v>
@@ -6385,10 +6381,10 @@
         <v>36</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -6411,28 +6407,28 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="D101" s="2">
-        <v>1987.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E101" s="2">
         <v>14.0</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>36</v>
+        <v>351</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -6455,26 +6451,28 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="D102" s="2">
-        <v>2008.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E102" s="2">
         <v>14.0</v>
       </c>
-      <c r="F102" s="1"/>
+      <c r="F102" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G102" s="1" t="s">
-        <v>59</v>
+        <v>355</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -6497,16 +6495,16 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="D103" s="2">
-        <v>1994.0</v>
+        <v>1969.0</v>
       </c>
       <c r="E103" s="2">
         <v>14.0</v>
@@ -6515,10 +6513,10 @@
         <v>36</v>
       </c>
       <c r="G103" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -6541,28 +6539,28 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>59</v>
+        <v>315</v>
       </c>
       <c r="D104" s="2">
-        <v>1997.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E104" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F104" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="H104" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -6585,28 +6583,28 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>367</v>
+        <v>114</v>
       </c>
       <c r="D105" s="2">
-        <v>1981.0</v>
+        <v>1987.0</v>
       </c>
       <c r="E105" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -6629,26 +6627,26 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D106" s="2">
-        <v>2013.0</v>
+        <v>2008.0</v>
       </c>
       <c r="E106" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>372</v>
+        <v>63</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -6671,28 +6669,28 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>59</v>
+        <v>336</v>
       </c>
       <c r="D107" s="2">
-        <v>2015.0</v>
+        <v>1994.0</v>
       </c>
       <c r="E107" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>59</v>
+        <v>371</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -6715,28 +6713,28 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D108" s="2">
-        <v>1980.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E108" s="2">
         <v>13.0</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>36</v>
+        <v>374</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>15</v>
+        <v>375</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -6759,25 +6757,25 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D109" s="2">
-        <v>1983.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E109" s="2">
         <v>13.0</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>36</v>
+        <v>378</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>379</v>
@@ -6809,10 +6807,10 @@
         <v>9</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>321</v>
+        <v>381</v>
       </c>
       <c r="D110" s="2">
-        <v>2020.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E110" s="2">
         <v>13.0</v>
@@ -6821,10 +6819,10 @@
         <v>36</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>321</v>
+        <v>382</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -6847,28 +6845,26 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>25</v>
+        <v>385</v>
       </c>
       <c r="D111" s="2">
-        <v>2021.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E111" s="2">
         <v>13.0</v>
       </c>
-      <c r="F111" s="1" t="s">
-        <v>383</v>
-      </c>
+      <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -6891,25 +6887,25 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D112" s="2">
-        <v>2019.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E112" s="2">
         <v>13.0</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>387</v>
+        <v>36</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>388</v>
+        <v>63</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>389</v>
@@ -6941,10 +6937,10 @@
         <v>9</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>195</v>
+        <v>63</v>
       </c>
       <c r="D113" s="2">
-        <v>2010.0</v>
+        <v>1983.0</v>
       </c>
       <c r="E113" s="2">
         <v>13.0</v>
@@ -6953,10 +6949,10 @@
         <v>36</v>
       </c>
       <c r="G113" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H113" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>392</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6979,28 +6975,28 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>40</v>
+        <v>336</v>
       </c>
       <c r="D114" s="2">
-        <v>2023.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E114" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>394</v>
+        <v>36</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>40</v>
+        <v>336</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -7023,25 +7019,25 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D115" s="2">
-        <v>2017.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E115" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>36</v>
+        <v>395</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>35</v>
+        <v>396</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>397</v>
@@ -7073,13 +7069,13 @@
         <v>9</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="D116" s="2">
-        <v>2023.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E116" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>36</v>
@@ -7117,19 +7113,19 @@
         <v>9</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>311</v>
+        <v>44</v>
       </c>
       <c r="D117" s="2">
-        <v>2013.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E117" s="2">
         <v>12.0</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>36</v>
+        <v>402</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>402</v>
+        <v>44</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>403</v>
@@ -7161,10 +7157,10 @@
         <v>9</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D118" s="2">
-        <v>1990.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E118" s="2">
         <v>12.0</v>
@@ -7173,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>405</v>
@@ -7205,10 +7201,10 @@
         <v>9</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>371</v>
+        <v>15</v>
       </c>
       <c r="D119" s="2">
-        <v>2006.0</v>
+        <v>1980.0</v>
       </c>
       <c r="E119" s="2">
         <v>12.0</v>
@@ -7217,9 +7213,11 @@
         <v>36</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="H119" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>407</v>
+      </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
@@ -7241,28 +7239,28 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D120" s="2">
-        <v>1964.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E120" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
@@ -7285,28 +7283,28 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="D121" s="2">
-        <v>1993.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E121" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
@@ -7329,28 +7327,28 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="D122" s="2">
-        <v>1958.0</v>
+        <v>1990.0</v>
       </c>
       <c r="E122" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
@@ -7373,29 +7371,27 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>20</v>
+        <v>385</v>
       </c>
       <c r="D123" s="2">
-        <v>1950.0</v>
+        <v>2006.0</v>
       </c>
       <c r="E123" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>415</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="H123" s="1"/>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
@@ -7423,10 +7419,10 @@
         <v>9</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="D124" s="2">
-        <v>1947.0</v>
+        <v>1964.0</v>
       </c>
       <c r="E124" s="2">
         <v>11.0</v>
@@ -7435,10 +7431,10 @@
         <v>36</v>
       </c>
       <c r="G124" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>418</v>
       </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
@@ -7461,16 +7457,16 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="D125" s="2">
-        <v>2007.0</v>
+        <v>1993.0</v>
       </c>
       <c r="E125" s="2">
         <v>11.0</v>
@@ -7479,10 +7475,10 @@
         <v>36</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
@@ -7505,16 +7501,16 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D126" s="2">
-        <v>2011.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E126" s="2">
         <v>11.0</v>
@@ -7523,10 +7519,10 @@
         <v>36</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>423</v>
+        <v>44</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
@@ -7549,15 +7545,17 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="D127" s="1"/>
+        <v>235</v>
+      </c>
+      <c r="D127" s="2">
+        <v>2023.0</v>
+      </c>
       <c r="E127" s="2">
         <v>11.0</v>
       </c>
@@ -7565,10 +7563,10 @@
         <v>36</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
@@ -7591,26 +7589,28 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>126</v>
+        <v>235</v>
       </c>
       <c r="D128" s="2">
-        <v>1985.0</v>
+        <v>1958.0</v>
       </c>
       <c r="E128" s="2">
         <v>11.0</v>
       </c>
-      <c r="F128" s="1"/>
+      <c r="F128" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G128" s="1" t="s">
-        <v>126</v>
+        <v>426</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
@@ -7633,26 +7633,28 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D129" s="2">
-        <v>1982.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E129" s="2">
         <v>11.0</v>
       </c>
-      <c r="F129" s="1"/>
+      <c r="F129" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G129" s="1" t="s">
-        <v>431</v>
+        <v>77</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
@@ -7675,24 +7677,28 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="D130" s="2">
-        <v>2019.0</v>
+        <v>1950.0</v>
       </c>
       <c r="E130" s="2">
         <v>11.0</v>
       </c>
-      <c r="F130" s="1"/>
-      <c r="G130" s="1"/>
+      <c r="F130" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="H130" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -7715,24 +7721,28 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>434</v>
+        <v>72</v>
       </c>
       <c r="D131" s="2">
-        <v>1991.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E131" s="2">
         <v>11.0</v>
       </c>
-      <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
+      <c r="F131" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>433</v>
+      </c>
       <c r="H131" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -7755,28 +7765,28 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>25</v>
+        <v>436</v>
       </c>
       <c r="D132" s="2">
-        <v>2022.0</v>
+        <v>1947.0</v>
       </c>
       <c r="E132" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>155</v>
+        <v>436</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -7799,28 +7809,28 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D133" s="2">
-        <v>2016.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E133" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>36</v>
+        <v>439</v>
       </c>
       <c r="G133" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="H133" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="H133" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -7843,28 +7853,26 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D134" s="2">
-        <v>2018.0</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="D134" s="1"/>
       <c r="E134" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G134" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H134" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>445</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -7887,28 +7895,26 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="D135" s="2">
-        <v>2019.0</v>
+        <v>1985.0</v>
       </c>
       <c r="E135" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>11.0</v>
+      </c>
+      <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -7931,28 +7937,24 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>59</v>
+        <v>448</v>
       </c>
       <c r="D136" s="2">
-        <v>2022.0</v>
+        <v>1991.0</v>
       </c>
       <c r="E136" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="F136" s="1" t="s">
+        <v>11.0</v>
+      </c>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -7975,16 +7977,16 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D137" s="2">
-        <v>2018.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E137" s="2">
         <v>10.0</v>
@@ -7993,10 +7995,10 @@
         <v>36</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>453</v>
+        <v>148</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -8019,16 +8021,16 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>187</v>
+        <v>30</v>
       </c>
       <c r="D138" s="2">
-        <v>2015.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E138" s="2">
         <v>10.0</v>
@@ -8037,10 +8039,10 @@
         <v>36</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -8063,16 +8065,16 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="D139" s="2">
-        <v>2005.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E139" s="2">
         <v>10.0</v>
@@ -8081,10 +8083,10 @@
         <v>36</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>25</v>
+        <v>456</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -8107,28 +8109,28 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>206</v>
+        <v>63</v>
       </c>
       <c r="D140" s="2">
-        <v>1999.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E140" s="2">
         <v>10.0</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>36</v>
+        <v>459</v>
       </c>
       <c r="G140" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H140" s="3" t="s">
         <v>461</v>
-      </c>
-      <c r="H140" s="3" t="s">
-        <v>462</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -8151,16 +8153,16 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="D141" s="2">
-        <v>2019.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E141" s="2">
         <v>10.0</v>
@@ -8169,7 +8171,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>59</v>
+        <v>463</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>464</v>
@@ -8201,10 +8203,10 @@
         <v>9</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D142" s="2">
-        <v>2009.0</v>
+        <v>2005.0</v>
       </c>
       <c r="E142" s="2">
         <v>10.0</v>
@@ -8213,7 +8215,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="H142" s="3" t="s">
         <v>466</v>
@@ -8245,20 +8247,22 @@
         <v>9</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="D143" s="2">
-        <v>2009.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E143" s="2">
         <v>10.0</v>
       </c>
-      <c r="F143" s="1"/>
+      <c r="F143" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G143" s="1" t="s">
-        <v>40</v>
+        <v>468</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -8281,28 +8285,28 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="D144" s="2">
-        <v>2002.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E144" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -8325,28 +8329,26 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>311</v>
+        <v>44</v>
       </c>
       <c r="D145" s="2">
-        <v>1951.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E145" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>311</v>
+        <v>44</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -8369,16 +8371,16 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="D146" s="2">
-        <v>2021.0</v>
+        <v>2002.0</v>
       </c>
       <c r="E146" s="2">
         <v>9.0</v>
@@ -8387,10 +8389,10 @@
         <v>36</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -8413,16 +8415,16 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>142</v>
+        <v>315</v>
       </c>
       <c r="D147" s="2">
-        <v>1998.0</v>
+        <v>1951.0</v>
       </c>
       <c r="E147" s="2">
         <v>9.0</v>
@@ -8431,7 +8433,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>476</v>
+        <v>315</v>
       </c>
       <c r="H147" s="3" t="s">
         <v>477</v>
@@ -8463,10 +8465,10 @@
         <v>9</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="D148" s="2">
-        <v>2003.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E148" s="2">
         <v>9.0</v>
@@ -8475,7 +8477,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>215</v>
+        <v>44</v>
       </c>
       <c r="H148" s="3" t="s">
         <v>479</v>
@@ -8507,10 +8509,10 @@
         <v>9</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="D149" s="2">
-        <v>2019.0</v>
+        <v>1998.0</v>
       </c>
       <c r="E149" s="2">
         <v>9.0</v>
@@ -8519,10 +8521,10 @@
         <v>36</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I149" s="1"/>
       <c r="J149" s="1"/>
@@ -8545,23 +8547,25 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>10</v>
+        <v>239</v>
       </c>
       <c r="D150" s="2">
-        <v>2021.0</v>
+        <v>2003.0</v>
       </c>
       <c r="E150" s="2">
         <v>9.0</v>
       </c>
-      <c r="F150" s="1"/>
+      <c r="F150" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G150" s="1" t="s">
-        <v>483</v>
+        <v>239</v>
       </c>
       <c r="H150" s="3" t="s">
         <v>484</v>
@@ -8593,7 +8597,7 @@
         <v>9</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="D151" s="2">
         <v>2021.0</v>
@@ -8601,9 +8605,7 @@
       <c r="E151" s="2">
         <v>9.0</v>
       </c>
-      <c r="F151" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F151" s="1"/>
       <c r="G151" s="1" t="s">
         <v>486</v>
       </c>
@@ -8637,22 +8639,22 @@
         <v>9</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>311</v>
+        <v>58</v>
       </c>
       <c r="D152" s="2">
-        <v>1998.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E152" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>311</v>
+        <v>489</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
@@ -8675,28 +8677,26 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D153" s="2">
-        <v>2016.0</v>
+        <v>1982.0</v>
       </c>
       <c r="E153" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>9.0</v>
+      </c>
+      <c r="F153" s="1"/>
       <c r="G153" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
@@ -8719,16 +8719,16 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D154" s="2">
-        <v>2004.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E154" s="2">
         <v>8.0</v>
@@ -8737,10 +8737,10 @@
         <v>36</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I154" s="1"/>
       <c r="J154" s="1"/>
@@ -8763,16 +8763,16 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>59</v>
+        <v>315</v>
       </c>
       <c r="D155" s="2">
-        <v>2017.0</v>
+        <v>1998.0</v>
       </c>
       <c r="E155" s="2">
         <v>8.0</v>
@@ -8781,10 +8781,10 @@
         <v>36</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>59</v>
+        <v>315</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
@@ -8807,16 +8807,16 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="D156" s="2">
-        <v>2014.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E156" s="2">
         <v>8.0</v>
@@ -8825,10 +8825,10 @@
         <v>36</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
@@ -8851,26 +8851,28 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="D157" s="2">
-        <v>2024.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E157" s="2">
         <v>8.0</v>
       </c>
-      <c r="F157" s="1"/>
+      <c r="F157" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G157" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
@@ -8893,26 +8895,28 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D158" s="2">
-        <v>2011.0</v>
+        <v>2014.0</v>
       </c>
       <c r="E158" s="2">
         <v>8.0</v>
       </c>
-      <c r="F158" s="1"/>
+      <c r="F158" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G158" s="1" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
@@ -8935,23 +8939,23 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>504</v>
+        <v>134</v>
       </c>
       <c r="D159" s="2">
-        <v>2009.0</v>
+        <v>2024.0</v>
       </c>
       <c r="E159" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
-        <v>504</v>
+        <v>134</v>
       </c>
       <c r="H159" s="3" t="s">
         <v>505</v>
@@ -8983,22 +8987,20 @@
         <v>9</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D160" s="2">
-        <v>2010.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E160" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F160" s="1" t="s">
+        <v>8.0</v>
+      </c>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H160" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H160" s="3" t="s">
-        <v>508</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -9021,25 +9023,23 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>348</v>
+        <v>509</v>
       </c>
       <c r="D161" s="2">
-        <v>2018.0</v>
+        <v>2014.0</v>
       </c>
       <c r="E161" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F161" s="1"/>
       <c r="G161" s="1" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="H161" s="3" t="s">
         <v>510</v>
@@ -9071,20 +9071,16 @@
         <v>9</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>72</v>
+        <v>448</v>
       </c>
       <c r="D162" s="2">
-        <v>2016.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E162" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1"/>
       <c r="H162" s="3" t="s">
         <v>512</v>
       </c>
@@ -9115,17 +9111,19 @@
         <v>9</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="D163" s="2">
-        <v>2005.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E163" s="2">
         <v>7.0</v>
       </c>
-      <c r="F163" s="1"/>
+      <c r="F163" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G163" s="1" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="H163" s="3" t="s">
         <v>514</v>
@@ -9157,22 +9155,22 @@
         <v>9</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="D164" s="2">
-        <v>1981.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E164" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>10</v>
+        <v>516</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -9195,26 +9193,26 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>165</v>
+        <v>519</v>
       </c>
       <c r="D165" s="2">
-        <v>1964.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E165" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="1" t="s">
-        <v>165</v>
+        <v>519</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -9237,26 +9235,28 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D166" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="D166" s="2">
+        <v>2010.0</v>
+      </c>
       <c r="E166" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>36</v>
+        <v>522</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>520</v>
+        <v>20</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
@@ -9279,28 +9279,28 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D167" s="2">
-        <v>2018.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E167" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
@@ -9323,28 +9323,28 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="D168" s="2">
-        <v>1966.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E168" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>525</v>
+        <v>72</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
@@ -9367,25 +9367,23 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>417</v>
+        <v>141</v>
       </c>
       <c r="D169" s="2">
-        <v>2010.0</v>
+        <v>2005.0</v>
       </c>
       <c r="E169" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>528</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F169" s="1"/>
       <c r="G169" s="1" t="s">
-        <v>417</v>
+        <v>141</v>
       </c>
       <c r="H169" s="3" t="s">
         <v>529</v>
@@ -9417,22 +9415,20 @@
         <v>9</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="D170" s="2">
-        <v>2010.0</v>
+        <v>1964.0</v>
       </c>
       <c r="E170" s="2">
         <v>6.0</v>
       </c>
-      <c r="F170" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F170" s="1"/>
       <c r="G170" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H170" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="H170" s="3" t="s">
-        <v>532</v>
       </c>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
@@ -9455,16 +9451,16 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D171" s="2">
-        <v>2023.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E171" s="2">
         <v>6.0</v>
@@ -9473,10 +9469,10 @@
         <v>36</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -9499,25 +9495,25 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>126</v>
+        <v>436</v>
       </c>
       <c r="D172" s="2">
-        <v>1985.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E172" s="2">
         <v>6.0</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>36</v>
+        <v>535</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>126</v>
+        <v>436</v>
       </c>
       <c r="H172" s="3" t="s">
         <v>536</v>
@@ -9549,10 +9545,10 @@
         <v>9</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D173" s="2">
-        <v>2018.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E173" s="2">
         <v>6.0</v>
@@ -9561,10 +9557,10 @@
         <v>36</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
@@ -9587,16 +9583,16 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="D174" s="2">
-        <v>2019.0</v>
+        <v>1985.0</v>
       </c>
       <c r="E174" s="2">
         <v>6.0</v>
@@ -9605,10 +9601,10 @@
         <v>36</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
@@ -9631,24 +9627,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>542</v>
+        <v>509</v>
       </c>
       <c r="D175" s="2">
-        <v>2014.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E175" s="2">
         <v>6.0</v>
       </c>
       <c r="F175" s="1"/>
-      <c r="G175" s="1" t="s">
-        <v>315</v>
-      </c>
+      <c r="G175" s="1"/>
       <c r="H175" s="3" t="s">
         <v>543</v>
       </c>
@@ -9679,18 +9673,22 @@
         <v>9</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D176" s="2">
-        <v>2019.0</v>
+        <v>2006.0</v>
       </c>
       <c r="E176" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="F176" s="1"/>
-      <c r="G176" s="1"/>
+        <v>5.0</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="H176" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I176" s="1"/>
       <c r="J176" s="1"/>
@@ -9713,25 +9711,23 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>547</v>
+        <v>72</v>
       </c>
       <c r="D177" s="2">
-        <v>2006.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E177" s="2">
         <v>5.0</v>
       </c>
-      <c r="F177" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F177" s="1"/>
       <c r="G177" s="1" t="s">
-        <v>547</v>
+        <v>72</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>548</v>
@@ -9763,17 +9759,19 @@
         <v>9</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="D178" s="2">
-        <v>1981.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E178" s="2">
         <v>5.0</v>
       </c>
-      <c r="F178" s="1"/>
+      <c r="F178" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G178" s="1" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="H178" s="3" t="s">
         <v>550</v>
@@ -9805,10 +9803,10 @@
         <v>9</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D179" s="2">
-        <v>2012.0</v>
+        <v>1978.0</v>
       </c>
       <c r="E179" s="2">
         <v>5.0</v>
@@ -9817,10 +9815,10 @@
         <v>36</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>59</v>
+        <v>552</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I179" s="1"/>
       <c r="J179" s="1"/>
@@ -9843,26 +9841,26 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D180" s="2">
-        <v>2016.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E180" s="2">
         <v>5.0</v>
       </c>
       <c r="F180" s="1"/>
       <c r="G180" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I180" s="1"/>
       <c r="J180" s="1"/>
@@ -9885,16 +9883,16 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="D181" s="2">
-        <v>2018.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E181" s="2">
         <v>5.0</v>
@@ -9903,10 +9901,10 @@
         <v>36</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I181" s="1"/>
       <c r="J181" s="1"/>
@@ -9929,16 +9927,16 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D182" s="2">
-        <v>1978.0</v>
+        <v>2002.0</v>
       </c>
       <c r="E182" s="2">
         <v>5.0</v>
@@ -9947,7 +9945,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>558</v>
+        <v>68</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>559</v>
@@ -9979,17 +9977,19 @@
         <v>9</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D183" s="2">
-        <v>2019.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E183" s="2">
         <v>5.0</v>
       </c>
-      <c r="F183" s="1"/>
+      <c r="F183" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G183" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>561</v>
@@ -10021,10 +10021,10 @@
         <v>9</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="D184" s="2">
-        <v>2021.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E184" s="2">
         <v>5.0</v>
@@ -10033,10 +10033,10 @@
         <v>36</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>20</v>
+        <v>563</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I184" s="1"/>
       <c r="J184" s="1"/>
@@ -10059,16 +10059,16 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D185" s="2">
-        <v>2002.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E185" s="2">
         <v>5.0</v>
@@ -10077,10 +10077,10 @@
         <v>36</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>68</v>
+        <v>566</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I185" s="1"/>
       <c r="J185" s="1"/>
@@ -10103,16 +10103,16 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>96</v>
+        <v>204</v>
       </c>
       <c r="D186" s="2">
-        <v>2022.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E186" s="2">
         <v>5.0</v>
@@ -10121,10 +10121,10 @@
         <v>36</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>567</v>
+        <v>204</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I186" s="1"/>
       <c r="J186" s="1"/>
@@ -10147,28 +10147,26 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>187</v>
+        <v>63</v>
       </c>
       <c r="D187" s="2">
-        <v>2017.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E187" s="2">
         <v>5.0</v>
       </c>
-      <c r="F187" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F187" s="1"/>
       <c r="G187" s="1" t="s">
-        <v>187</v>
+        <v>63</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I187" s="1"/>
       <c r="J187" s="1"/>
@@ -10191,26 +10189,26 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D188" s="2">
-        <v>2009.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E188" s="2">
         <v>5.0</v>
       </c>
       <c r="F188" s="1"/>
       <c r="G188" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
@@ -10233,27 +10231,21 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D189" s="2">
-        <v>2018.0</v>
-      </c>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
       <c r="E189" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F189" s="1"/>
-      <c r="G189" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H189" s="3" t="s">
-        <v>574</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G189" s="1"/>
+      <c r="H189" s="1"/>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
       <c r="K189" s="1"/>
@@ -10281,16 +10273,20 @@
         <v>9</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>542</v>
+        <v>77</v>
       </c>
       <c r="D190" s="2">
-        <v>1983.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E190" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F190" s="1"/>
-      <c r="G190" s="1"/>
+        <v>3.0</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="H190" s="3" t="s">
         <v>576</v>
       </c>
@@ -33039,25 +33035,25 @@
     <hyperlink r:id="rId42" ref="H43"/>
     <hyperlink r:id="rId43" ref="H44"/>
     <hyperlink r:id="rId44" ref="H45"/>
-    <hyperlink r:id="rId45" ref="F46"/>
-    <hyperlink r:id="rId46" ref="H46"/>
-    <hyperlink r:id="rId47" ref="H47"/>
-    <hyperlink r:id="rId48" ref="H48"/>
-    <hyperlink r:id="rId49" ref="H49"/>
-    <hyperlink r:id="rId50" ref="H50"/>
+    <hyperlink r:id="rId45" ref="H46"/>
+    <hyperlink r:id="rId46" ref="H47"/>
+    <hyperlink r:id="rId47" ref="H48"/>
+    <hyperlink r:id="rId48" ref="H49"/>
+    <hyperlink r:id="rId49" ref="H50"/>
+    <hyperlink r:id="rId50" ref="F51"/>
     <hyperlink r:id="rId51" ref="H51"/>
     <hyperlink r:id="rId52" ref="H52"/>
     <hyperlink r:id="rId53" ref="H53"/>
     <hyperlink r:id="rId54" ref="H54"/>
     <hyperlink r:id="rId55" ref="H55"/>
     <hyperlink r:id="rId56" ref="H56"/>
-    <hyperlink r:id="rId57" ref="H58"/>
-    <hyperlink r:id="rId58" ref="H59"/>
-    <hyperlink r:id="rId59" ref="H60"/>
-    <hyperlink r:id="rId60" ref="H61"/>
-    <hyperlink r:id="rId61" ref="H62"/>
-    <hyperlink r:id="rId62" ref="H63"/>
-    <hyperlink r:id="rId63" ref="H64"/>
+    <hyperlink r:id="rId57" ref="H57"/>
+    <hyperlink r:id="rId58" ref="H58"/>
+    <hyperlink r:id="rId59" ref="H59"/>
+    <hyperlink r:id="rId60" ref="H60"/>
+    <hyperlink r:id="rId61" ref="H61"/>
+    <hyperlink r:id="rId62" ref="H62"/>
+    <hyperlink r:id="rId63" ref="H63"/>
     <hyperlink r:id="rId64" ref="H65"/>
     <hyperlink r:id="rId65" ref="H66"/>
     <hyperlink r:id="rId66" ref="H67"/>
@@ -33112,10 +33108,10 @@
     <hyperlink r:id="rId115" ref="H116"/>
     <hyperlink r:id="rId116" ref="H117"/>
     <hyperlink r:id="rId117" ref="H118"/>
-    <hyperlink r:id="rId118" ref="H120"/>
-    <hyperlink r:id="rId119" ref="H121"/>
-    <hyperlink r:id="rId120" ref="H122"/>
-    <hyperlink r:id="rId121" ref="H123"/>
+    <hyperlink r:id="rId118" ref="H119"/>
+    <hyperlink r:id="rId119" ref="H120"/>
+    <hyperlink r:id="rId120" ref="H121"/>
+    <hyperlink r:id="rId121" ref="H122"/>
     <hyperlink r:id="rId122" ref="H124"/>
     <hyperlink r:id="rId123" ref="H125"/>
     <hyperlink r:id="rId124" ref="H126"/>
@@ -33181,9 +33177,8 @@
     <hyperlink r:id="rId184" ref="H186"/>
     <hyperlink r:id="rId185" ref="H187"/>
     <hyperlink r:id="rId186" ref="H188"/>
-    <hyperlink r:id="rId187" ref="H189"/>
-    <hyperlink r:id="rId188" ref="H190"/>
+    <hyperlink r:id="rId187" ref="H190"/>
   </hyperlinks>
-  <drawing r:id="rId189"/>
+  <drawing r:id="rId188"/>
 </worksheet>
 </file>
--- a/Car_Wash_Advisory_Companies.xlsx
+++ b/Car_Wash_Advisory_Companies.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="575">
   <si>
     <t>Company Name</t>
   </si>
@@ -277,6 +277,42 @@
     <t>https://www.autobell.com/</t>
   </si>
   <si>
+    <t>Caliber Car Wash</t>
+  </si>
+  <si>
+    <t>Percheron Capital</t>
+  </si>
+  <si>
+    <t>Alabama | Florida | Georgia | North Carolina | South Carolina | Texas</t>
+  </si>
+  <si>
+    <t>https://calibercarwash.com/</t>
+  </si>
+  <si>
+    <t>ClearWater Express Wash</t>
+  </si>
+  <si>
+    <t>Texas | California</t>
+  </si>
+  <si>
+    <t>https://www.clearwaterexpresswash.com</t>
+  </si>
+  <si>
+    <t>Tsunami Express</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Point72 Ventures</t>
+  </si>
+  <si>
+    <t>Arkansas | Indiana | Illinois | Kansas | Michigan | Missouri | Minnesota | Ohio | Wisconsin</t>
+  </si>
+  <si>
+    <t>https://www.tsunamiexpress.com/</t>
+  </si>
+  <si>
     <t>LUV Car Wash</t>
   </si>
   <si>
@@ -289,42 +325,6 @@
     <t>https://luvcarwash.com/</t>
   </si>
   <si>
-    <t>Caliber Car Wash</t>
-  </si>
-  <si>
-    <t>Percheron Capital</t>
-  </si>
-  <si>
-    <t>Alabama | Florida | Georgia | North Carolina | South Carolina | Texas</t>
-  </si>
-  <si>
-    <t>https://calibercarwash.com/</t>
-  </si>
-  <si>
-    <t>ClearWater Express Wash</t>
-  </si>
-  <si>
-    <t>Texas | California</t>
-  </si>
-  <si>
-    <t>https://www.clearwaterexpresswash.com</t>
-  </si>
-  <si>
-    <t>Tsunami Express</t>
-  </si>
-  <si>
-    <t>Oregon</t>
-  </si>
-  <si>
-    <t>Point72 Ventures</t>
-  </si>
-  <si>
-    <t>Arkansas | Indiana | Illinois | Kansas | Michigan | Missouri | Minnesota | Ohio | Wisconsin</t>
-  </si>
-  <si>
-    <t>https://www.tsunamiexpress.com/</t>
-  </si>
-  <si>
     <t>Splash Car Wash</t>
   </si>
   <si>
@@ -751,12 +751,6 @@
     <t>https://washmasters.com/</t>
   </si>
   <si>
-    <t>Woodie's Wash Shack</t>
-  </si>
-  <si>
-    <t>https://www.woodieswash.com/</t>
-  </si>
-  <si>
     <t>Dash Car Wash</t>
   </si>
   <si>
@@ -1177,115 +1171,115 @@
     <t>https://www.iqcarwash.com/</t>
   </si>
   <si>
+    <t>Speedy Stop Car Wash</t>
+  </si>
+  <si>
+    <t>https://speedystop.com/</t>
+  </si>
+  <si>
+    <t>Team Car Wash</t>
+  </si>
+  <si>
+    <t>https://theteamcarwash.com/</t>
+  </si>
+  <si>
+    <t>Wash-Rite Express Car Wash</t>
+  </si>
+  <si>
+    <t>Bradham Capital Holdings</t>
+  </si>
+  <si>
+    <t>Ohio | Pennsylvania | West Virginia</t>
+  </si>
+  <si>
+    <t>https://www.wash-riteunlimited.com</t>
+  </si>
+  <si>
+    <t>White Horse Auto Wash</t>
+  </si>
+  <si>
+    <t>Virginia | South Carolina</t>
+  </si>
+  <si>
+    <t>https://www.whitehorseautowash.com/</t>
+  </si>
+  <si>
+    <t>Dream Clean Car Wash</t>
+  </si>
+  <si>
+    <t>Cross Timbers Capital Group</t>
+  </si>
+  <si>
+    <t>https://www.dreamcleancw.com/</t>
+  </si>
+  <si>
+    <t>Fast Splash Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.fastsplashcarwash.com/</t>
+  </si>
+  <si>
+    <t>Jacksons</t>
+  </si>
+  <si>
+    <t>https://jacksonswash.com/</t>
+  </si>
+  <si>
+    <t>Ocean Blue Car Wash</t>
+  </si>
+  <si>
+    <t>https://oceanbluecarwash.com/</t>
+  </si>
+  <si>
+    <t>Shine Time Super Wash</t>
+  </si>
+  <si>
+    <t>Alabama | Mississippi</t>
+  </si>
+  <si>
+    <t>https://www.shinetimesuperwash.com/</t>
+  </si>
+  <si>
+    <t>Super Clean Car Wash</t>
+  </si>
+  <si>
+    <t>https://supercleanmycar.com/</t>
+  </si>
+  <si>
+    <t>Xtreme Auto Wash</t>
+  </si>
+  <si>
+    <t>7 Flags Car Wash</t>
+  </si>
+  <si>
+    <t>https://7flagscarwash.com/</t>
+  </si>
+  <si>
+    <t>Ducky's Car Wash</t>
+  </si>
+  <si>
+    <t>https://duckysexpress.com/</t>
+  </si>
+  <si>
+    <t>Everclean Car Wash</t>
+  </si>
+  <si>
+    <t>https://evercleancw.com/</t>
+  </si>
+  <si>
+    <t>Hang 10 Car Wash</t>
+  </si>
+  <si>
+    <t>Florida | New Jersey | South Carolina | Virginia</t>
+  </si>
+  <si>
+    <t>https://hang10carwash.com/</t>
+  </si>
+  <si>
     <t>iShine Express Car Wash &amp; Detail</t>
   </si>
   <si>
     <t>https://ishinecarwash.com/</t>
-  </si>
-  <si>
-    <t>Speedy Stop Car Wash</t>
-  </si>
-  <si>
-    <t>https://speedystop.com/</t>
-  </si>
-  <si>
-    <t>Team Car Wash</t>
-  </si>
-  <si>
-    <t>https://theteamcarwash.com/</t>
-  </si>
-  <si>
-    <t>Wash-Rite Express Car Wash</t>
-  </si>
-  <si>
-    <t>Bradham Capital Holdings</t>
-  </si>
-  <si>
-    <t>Ohio | Pennsylvania | West Virginia</t>
-  </si>
-  <si>
-    <t>https://www.wash-riteunlimited.com</t>
-  </si>
-  <si>
-    <t>White Horse Auto Wash</t>
-  </si>
-  <si>
-    <t>Virginia | South Carolina</t>
-  </si>
-  <si>
-    <t>https://www.whitehorseautowash.com/</t>
-  </si>
-  <si>
-    <t>Dream Clean Car Wash</t>
-  </si>
-  <si>
-    <t>Cross Timbers Capital Group</t>
-  </si>
-  <si>
-    <t>https://www.dreamcleancw.com/</t>
-  </si>
-  <si>
-    <t>Fast Splash Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.fastsplashcarwash.com/</t>
-  </si>
-  <si>
-    <t>Jacksons</t>
-  </si>
-  <si>
-    <t>https://jacksonswash.com/</t>
-  </si>
-  <si>
-    <t>Ocean Blue Car Wash</t>
-  </si>
-  <si>
-    <t>https://oceanbluecarwash.com/</t>
-  </si>
-  <si>
-    <t>Shine Time Super Wash</t>
-  </si>
-  <si>
-    <t>Alabama | Mississippi</t>
-  </si>
-  <si>
-    <t>https://www.shinetimesuperwash.com/</t>
-  </si>
-  <si>
-    <t>Super Clean Car Wash</t>
-  </si>
-  <si>
-    <t>https://supercleanmycar.com/</t>
-  </si>
-  <si>
-    <t>Xtreme Auto Wash</t>
-  </si>
-  <si>
-    <t>7 Flags Car Wash</t>
-  </si>
-  <si>
-    <t>https://7flagscarwash.com/</t>
-  </si>
-  <si>
-    <t>Ducky's Car Wash</t>
-  </si>
-  <si>
-    <t>https://duckysexpress.com/</t>
-  </si>
-  <si>
-    <t>Everclean Car Wash</t>
-  </si>
-  <si>
-    <t>https://evercleancw.com/</t>
-  </si>
-  <si>
-    <t>Hang 10 Car Wash</t>
-  </si>
-  <si>
-    <t>Florida | New Jersey | South Carolina | Virginia</t>
-  </si>
-  <si>
-    <t>https://hang10carwash.com/</t>
   </si>
   <si>
     <t>Mr Wash Car Wash</t>
@@ -2733,7 +2727,7 @@
         <v>2022.0</v>
       </c>
       <c r="E17" s="2">
-        <v>92.0</v>
+        <v>95.0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>82</v>
@@ -2815,13 +2809,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D19" s="2">
-        <v>2021.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E19" s="2">
-        <v>91.0</v>
+        <v>85.0</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>89</v>
@@ -2859,22 +2853,22 @@
         <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="D20" s="2">
-        <v>2019.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E20" s="2">
-        <v>85.0</v>
+        <v>83.0</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2897,28 +2891,28 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="D21" s="2">
-        <v>2021.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E21" s="2">
         <v>83.0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -2941,19 +2935,19 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D22" s="2">
-        <v>2015.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E22" s="2">
-        <v>83.0</v>
+        <v>81.0</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>101</v>
@@ -4748,24 +4742,18 @@
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="C63" s="1"/>
       <c r="D63" s="2">
-        <v>2019.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E63" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>24.0</v>
+      </c>
+      <c r="F63" s="1"/>
       <c r="G63" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H63" s="3" t="s">
         <v>247</v>
       </c>
+      <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -4792,18 +4780,24 @@
       <c r="B64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="1"/>
+      <c r="C64" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="D64" s="2">
-        <v>2021.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E64" s="2">
         <v>24.0</v>
       </c>
-      <c r="F64" s="1"/>
+      <c r="F64" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -4831,22 +4825,22 @@
         <v>9</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="D65" s="2">
-        <v>2013.0</v>
+        <v>1959.0</v>
       </c>
       <c r="E65" s="2">
         <v>24.0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>20</v>
+        <v>253</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -4869,28 +4863,28 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>253</v>
+        <v>190</v>
       </c>
       <c r="D66" s="2">
-        <v>1959.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E66" s="2">
         <v>24.0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -4913,16 +4907,16 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="D67" s="2">
-        <v>2012.0</v>
+        <v>1986.0</v>
       </c>
       <c r="E67" s="2">
         <v>24.0</v>
@@ -4931,7 +4925,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>258</v>
+        <v>63</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>259</v>
@@ -4966,19 +4960,19 @@
         <v>63</v>
       </c>
       <c r="D68" s="2">
-        <v>1986.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E68" s="2">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>36</v>
+        <v>261</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
@@ -5001,28 +4995,28 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D69" s="2">
-        <v>2021.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E69" s="2">
         <v>23.0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>63</v>
+        <v>265</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
@@ -5045,28 +5039,28 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="D70" s="2">
-        <v>2019.0</v>
+        <v>1951.0</v>
       </c>
       <c r="E70" s="2">
         <v>23.0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>266</v>
+        <v>36</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
@@ -5089,16 +5083,16 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="D71" s="2">
-        <v>1951.0</v>
+        <v>1966.0</v>
       </c>
       <c r="E71" s="2">
         <v>23.0</v>
@@ -5107,10 +5101,10 @@
         <v>36</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -5133,16 +5127,16 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="D72" s="2">
-        <v>1966.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E72" s="2">
         <v>23.0</v>
@@ -5151,7 +5145,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>273</v>
+        <v>63</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>274</v>
@@ -5183,19 +5177,19 @@
         <v>9</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="D73" s="2">
-        <v>2019.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E73" s="2">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>276</v>
@@ -5227,19 +5221,19 @@
         <v>9</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D74" s="2">
-        <v>1981.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E74" s="2">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>278</v>
@@ -5271,22 +5265,22 @@
         <v>9</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="D75" s="2">
-        <v>2017.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E75" s="2">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>77</v>
+        <v>280</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -5309,16 +5303,16 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="D76" s="2">
-        <v>1997.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E76" s="2">
         <v>20.0</v>
@@ -5327,10 +5321,10 @@
         <v>36</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -5353,28 +5347,28 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="D77" s="2">
-        <v>2019.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E77" s="2">
         <v>20.0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>36</v>
+        <v>286</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>285</v>
+        <v>156</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -5397,28 +5391,28 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="D78" s="2">
-        <v>2016.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E78" s="2">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>288</v>
+        <v>36</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>156</v>
+        <v>289</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -5441,16 +5435,16 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D79" s="2">
-        <v>2021.0</v>
+        <v>1982.0</v>
       </c>
       <c r="E79" s="2">
         <v>19.0</v>
@@ -5459,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>291</v>
+        <v>44</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>292</v>
@@ -5491,22 +5485,22 @@
         <v>9</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="D80" s="2">
-        <v>1982.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E80" s="2">
         <v>19.0</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>36</v>
+        <v>294</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -5529,28 +5523,26 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="2">
-        <v>1997.0</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="D81" s="1"/>
       <c r="E81" s="2">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>296</v>
+        <v>36</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>15</v>
+        <v>297</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -5573,15 +5565,17 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D82" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="D82" s="2">
+        <v>1960.0</v>
+      </c>
       <c r="E82" s="2">
         <v>18.0</v>
       </c>
@@ -5589,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>299</v>
+        <v>44</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>300</v>
@@ -5621,10 +5615,10 @@
         <v>9</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="D83" s="2">
-        <v>1960.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E83" s="2">
         <v>18.0</v>
@@ -5633,10 +5627,10 @@
         <v>36</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>44</v>
+        <v>302</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -5659,16 +5653,16 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D84" s="2">
-        <v>1976.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E84" s="2">
         <v>18.0</v>
@@ -5677,7 +5671,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>304</v>
+        <v>96</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>305</v>
@@ -5709,19 +5703,19 @@
         <v>9</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D85" s="2">
-        <v>1995.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E85" s="2">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>307</v>
@@ -5753,10 +5747,10 @@
         <v>9</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D86" s="2">
-        <v>2019.0</v>
+        <v>1977.0</v>
       </c>
       <c r="E86" s="2">
         <v>17.0</v>
@@ -5765,7 +5759,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>309</v>
@@ -5797,10 +5791,10 @@
         <v>9</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>35</v>
+        <v>171</v>
       </c>
       <c r="D87" s="2">
-        <v>1977.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E87" s="2">
         <v>17.0</v>
@@ -5809,7 +5803,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>35</v>
+        <v>171</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>311</v>
@@ -5841,10 +5835,10 @@
         <v>9</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>171</v>
+        <v>313</v>
       </c>
       <c r="D88" s="2">
-        <v>2017.0</v>
+        <v>1993.0</v>
       </c>
       <c r="E88" s="2">
         <v>17.0</v>
@@ -5853,10 +5847,10 @@
         <v>36</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>171</v>
+        <v>314</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -5879,16 +5873,16 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>315</v>
+        <v>35</v>
       </c>
       <c r="D89" s="2">
-        <v>1993.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E89" s="2">
         <v>17.0</v>
@@ -5897,7 +5891,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>316</v>
+        <v>35</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>317</v>
@@ -5929,22 +5923,22 @@
         <v>9</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D90" s="2">
-        <v>2015.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E90" s="2">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>35</v>
+        <v>319</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -5967,16 +5961,16 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="D91" s="2">
-        <v>1999.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E91" s="2">
         <v>16.0</v>
@@ -5985,10 +5979,10 @@
         <v>36</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
@@ -6011,16 +6005,16 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="D92" s="2">
-        <v>1995.0</v>
+        <v>1966.0</v>
       </c>
       <c r="E92" s="2">
         <v>16.0</v>
@@ -6029,10 +6023,10 @@
         <v>36</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -6055,16 +6049,16 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>105</v>
+        <v>328</v>
       </c>
       <c r="D93" s="2">
-        <v>1966.0</v>
+        <v>2001.0</v>
       </c>
       <c r="E93" s="2">
         <v>16.0</v>
@@ -6073,10 +6067,10 @@
         <v>36</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -6099,16 +6093,16 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>330</v>
+        <v>68</v>
       </c>
       <c r="D94" s="2">
-        <v>2001.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E94" s="2">
         <v>16.0</v>
@@ -6117,7 +6111,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>331</v>
+        <v>68</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>332</v>
@@ -6149,10 +6143,10 @@
         <v>9</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>68</v>
+        <v>334</v>
       </c>
       <c r="D95" s="2">
-        <v>2013.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E95" s="2">
         <v>16.0</v>
@@ -6161,10 +6155,10 @@
         <v>36</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>68</v>
+        <v>335</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -6187,28 +6181,28 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>336</v>
+        <v>230</v>
       </c>
       <c r="D96" s="2">
-        <v>1976.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E96" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -6231,16 +6225,16 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="D97" s="2">
-        <v>2007.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E97" s="2">
         <v>15.0</v>
@@ -6249,10 +6243,10 @@
         <v>36</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -6275,16 +6269,16 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>171</v>
+        <v>313</v>
       </c>
       <c r="D98" s="2">
-        <v>2018.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E98" s="2">
         <v>15.0</v>
@@ -6293,7 +6287,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>344</v>
@@ -6325,22 +6319,22 @@
         <v>9</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>315</v>
+        <v>58</v>
       </c>
       <c r="D99" s="2">
-        <v>2000.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E99" s="2">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -6363,28 +6357,28 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D100" s="2">
-        <v>2007.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E100" s="2">
         <v>14.0</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>36</v>
+        <v>349</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -6407,28 +6401,28 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D101" s="2">
-        <v>2019.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E101" s="2">
         <v>14.0</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>351</v>
+        <v>36</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -6451,16 +6445,16 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>10</v>
+        <v>356</v>
       </c>
       <c r="D102" s="2">
-        <v>2020.0</v>
+        <v>1969.0</v>
       </c>
       <c r="E102" s="2">
         <v>14.0</v>
@@ -6469,10 +6463,10 @@
         <v>36</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -6495,16 +6489,16 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="D103" s="2">
-        <v>1969.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E103" s="2">
         <v>14.0</v>
@@ -6513,10 +6507,10 @@
         <v>36</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -6539,16 +6533,16 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>315</v>
+        <v>114</v>
       </c>
       <c r="D104" s="2">
-        <v>2013.0</v>
+        <v>1987.0</v>
       </c>
       <c r="E104" s="2">
         <v>14.0</v>
@@ -6557,10 +6551,10 @@
         <v>36</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -6583,28 +6577,26 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>114</v>
+        <v>366</v>
       </c>
       <c r="D105" s="2">
-        <v>1987.0</v>
+        <v>2008.0</v>
       </c>
       <c r="E105" s="2">
         <v>14.0</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F105" s="1"/>
       <c r="G105" s="1" t="s">
-        <v>365</v>
+        <v>63</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -6627,26 +6619,28 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="D106" s="2">
-        <v>2008.0</v>
+        <v>1994.0</v>
       </c>
       <c r="E106" s="2">
         <v>14.0</v>
       </c>
-      <c r="F106" s="1"/>
+      <c r="F106" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G106" s="1" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -6669,28 +6663,28 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>336</v>
+        <v>63</v>
       </c>
       <c r="D107" s="2">
-        <v>1994.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E107" s="2">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>36</v>
+        <v>372</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -6713,28 +6707,28 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D108" s="2">
-        <v>1997.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E108" s="2">
         <v>13.0</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>375</v>
+        <v>77</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -6757,28 +6751,28 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>77</v>
+        <v>379</v>
       </c>
       <c r="D109" s="2">
-        <v>2020.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E109" s="2">
         <v>13.0</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>378</v>
+        <v>36</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6801,28 +6795,26 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D110" s="2">
-        <v>1981.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E110" s="2">
         <v>13.0</v>
       </c>
-      <c r="F110" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F110" s="1"/>
       <c r="G110" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -6845,23 +6837,25 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>385</v>
+        <v>63</v>
       </c>
       <c r="D111" s="2">
-        <v>2013.0</v>
+        <v>1983.0</v>
       </c>
       <c r="E111" s="2">
         <v>13.0</v>
       </c>
-      <c r="F111" s="1"/>
+      <c r="F111" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G111" s="1" t="s">
-        <v>386</v>
+        <v>63</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>387</v>
@@ -6893,10 +6887,10 @@
         <v>9</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="D112" s="2">
-        <v>2015.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E112" s="2">
         <v>13.0</v>
@@ -6905,7 +6899,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>389</v>
@@ -6937,22 +6931,22 @@
         <v>9</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D113" s="2">
-        <v>1983.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E113" s="2">
         <v>13.0</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>36</v>
+        <v>391</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>63</v>
+        <v>392</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6975,16 +6969,16 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>336</v>
+        <v>235</v>
       </c>
       <c r="D114" s="2">
-        <v>2020.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E114" s="2">
         <v>13.0</v>
@@ -6993,10 +6987,10 @@
         <v>36</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -7019,28 +7013,28 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D115" s="2">
-        <v>2021.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E115" s="2">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>396</v>
+        <v>44</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -7063,28 +7057,28 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="D116" s="2">
-        <v>2010.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E116" s="2">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>399</v>
+        <v>35</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -7107,25 +7101,25 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="D117" s="2">
-        <v>2023.0</v>
+        <v>1980.0</v>
       </c>
       <c r="E117" s="2">
         <v>12.0</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>402</v>
+        <v>36</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>403</v>
@@ -7157,10 +7151,10 @@
         <v>9</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D118" s="2">
-        <v>2017.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E118" s="2">
         <v>12.0</v>
@@ -7169,7 +7163,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>405</v>
@@ -7201,10 +7195,10 @@
         <v>9</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>15</v>
+        <v>171</v>
       </c>
       <c r="D119" s="2">
-        <v>1980.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E119" s="2">
         <v>12.0</v>
@@ -7213,10 +7207,10 @@
         <v>36</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>15</v>
+        <v>407</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
@@ -7239,16 +7233,16 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D120" s="2">
-        <v>2004.0</v>
+        <v>1990.0</v>
       </c>
       <c r="E120" s="2">
         <v>12.0</v>
@@ -7257,10 +7251,10 @@
         <v>36</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
@@ -7283,16 +7277,16 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>171</v>
+        <v>383</v>
       </c>
       <c r="D121" s="2">
-        <v>2007.0</v>
+        <v>2006.0</v>
       </c>
       <c r="E121" s="2">
         <v>12.0</v>
@@ -7301,11 +7295,9 @@
         <v>36</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>412</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="H121" s="1"/>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
@@ -7327,7 +7319,7 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>9</v>
@@ -7336,10 +7328,10 @@
         <v>20</v>
       </c>
       <c r="D122" s="2">
-        <v>1990.0</v>
+        <v>1964.0</v>
       </c>
       <c r="E122" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>36</v>
@@ -7348,7 +7340,7 @@
         <v>20</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
@@ -7371,27 +7363,29 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>385</v>
+        <v>20</v>
       </c>
       <c r="D123" s="2">
-        <v>2006.0</v>
+        <v>1993.0</v>
       </c>
       <c r="E123" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="H123" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>415</v>
+      </c>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
@@ -7419,10 +7413,10 @@
         <v>9</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D124" s="2">
-        <v>1964.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E124" s="2">
         <v>11.0</v>
@@ -7431,7 +7425,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>417</v>
@@ -7463,10 +7457,10 @@
         <v>9</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="D125" s="2">
-        <v>1993.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E125" s="2">
         <v>11.0</v>
@@ -7475,10 +7469,10 @@
         <v>36</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>20</v>
+        <v>419</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
@@ -7501,16 +7495,16 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D126" s="2">
-        <v>2019.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E126" s="2">
         <v>11.0</v>
@@ -7519,10 +7513,10 @@
         <v>36</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
@@ -7545,7 +7539,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>9</v>
@@ -7554,7 +7548,7 @@
         <v>235</v>
       </c>
       <c r="D127" s="2">
-        <v>2023.0</v>
+        <v>1958.0</v>
       </c>
       <c r="E127" s="2">
         <v>11.0</v>
@@ -7563,10 +7557,10 @@
         <v>36</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
@@ -7589,16 +7583,16 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>235</v>
+        <v>77</v>
       </c>
       <c r="D128" s="2">
-        <v>1958.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E128" s="2">
         <v>11.0</v>
@@ -7607,7 +7601,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>426</v>
+        <v>77</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>427</v>
@@ -7639,10 +7633,10 @@
         <v>9</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="D129" s="2">
-        <v>2019.0</v>
+        <v>1950.0</v>
       </c>
       <c r="E129" s="2">
         <v>11.0</v>
@@ -7651,7 +7645,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="H129" s="3" t="s">
         <v>429</v>
@@ -7683,10 +7677,10 @@
         <v>9</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D130" s="2">
-        <v>1950.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E130" s="2">
         <v>11.0</v>
@@ -7695,10 +7689,10 @@
         <v>36</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>20</v>
+        <v>431</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -7721,16 +7715,16 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>72</v>
+        <v>434</v>
       </c>
       <c r="D131" s="2">
-        <v>2018.0</v>
+        <v>1947.0</v>
       </c>
       <c r="E131" s="2">
         <v>11.0</v>
@@ -7739,10 +7733,10 @@
         <v>36</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -7765,28 +7759,28 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>436</v>
+        <v>44</v>
       </c>
       <c r="D132" s="2">
-        <v>1947.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E132" s="2">
         <v>11.0</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>36</v>
+        <v>437</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -7809,28 +7803,26 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D133" s="2">
-        <v>2019.0</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="D133" s="1"/>
       <c r="E133" s="2">
         <v>11.0</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>439</v>
+        <v>36</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -7853,23 +7845,23 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D134" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="D134" s="2">
+        <v>1985.0</v>
+      </c>
       <c r="E134" s="2">
         <v>11.0</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F134" s="1"/>
       <c r="G134" s="1" t="s">
-        <v>443</v>
+        <v>141</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>444</v>
@@ -7901,20 +7893,18 @@
         <v>9</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="D135" s="2">
-        <v>1985.0</v>
+        <v>1991.0</v>
       </c>
       <c r="E135" s="2">
         <v>11.0</v>
       </c>
       <c r="F135" s="1"/>
-      <c r="G135" s="1" t="s">
-        <v>141</v>
-      </c>
+      <c r="G135" s="1"/>
       <c r="H135" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -7937,22 +7927,26 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>448</v>
+        <v>25</v>
       </c>
       <c r="D136" s="2">
-        <v>1991.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E136" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
+        <v>10.0</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="H136" s="3" t="s">
         <v>449</v>
       </c>
@@ -7983,10 +7977,10 @@
         <v>9</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D137" s="2">
-        <v>2022.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E137" s="2">
         <v>10.0</v>
@@ -7995,10 +7989,10 @@
         <v>36</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>148</v>
+        <v>451</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -8021,16 +8015,16 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="D138" s="2">
-        <v>2016.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E138" s="2">
         <v>10.0</v>
@@ -8039,10 +8033,10 @@
         <v>36</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -8065,28 +8059,28 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D139" s="2">
-        <v>2018.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E139" s="2">
         <v>10.0</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>36</v>
+        <v>457</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -8109,28 +8103,28 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>63</v>
+        <v>204</v>
       </c>
       <c r="D140" s="2">
-        <v>2022.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E140" s="2">
         <v>10.0</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>459</v>
+        <v>36</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -8153,16 +8147,16 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="D141" s="2">
-        <v>2015.0</v>
+        <v>2005.0</v>
       </c>
       <c r="E141" s="2">
         <v>10.0</v>
@@ -8171,7 +8165,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>463</v>
+        <v>25</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>464</v>
@@ -8203,10 +8197,10 @@
         <v>9</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="D142" s="2">
-        <v>2005.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E142" s="2">
         <v>10.0</v>
@@ -8215,10 +8209,10 @@
         <v>36</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>25</v>
+        <v>466</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -8241,16 +8235,16 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>230</v>
+        <v>63</v>
       </c>
       <c r="D143" s="2">
-        <v>1999.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E143" s="2">
         <v>10.0</v>
@@ -8259,7 +8253,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>468</v>
+        <v>63</v>
       </c>
       <c r="H143" s="3" t="s">
         <v>469</v>
@@ -8291,7 +8285,7 @@
         <v>9</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D144" s="2">
         <v>2009.0</v>
@@ -8299,11 +8293,9 @@
       <c r="E144" s="2">
         <v>10.0</v>
       </c>
-      <c r="F144" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F144" s="1"/>
       <c r="G144" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H144" s="3" t="s">
         <v>471</v>
@@ -8335,17 +8327,19 @@
         <v>9</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="D145" s="2">
-        <v>2009.0</v>
+        <v>2002.0</v>
       </c>
       <c r="E145" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="F145" s="1"/>
+        <v>9.0</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G145" s="1" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="H145" s="3" t="s">
         <v>473</v>
@@ -8377,10 +8371,10 @@
         <v>9</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>141</v>
+        <v>313</v>
       </c>
       <c r="D146" s="2">
-        <v>2002.0</v>
+        <v>1951.0</v>
       </c>
       <c r="E146" s="2">
         <v>9.0</v>
@@ -8389,7 +8383,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>141</v>
+        <v>313</v>
       </c>
       <c r="H146" s="3" t="s">
         <v>475</v>
@@ -8421,10 +8415,10 @@
         <v>9</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>315</v>
+        <v>44</v>
       </c>
       <c r="D147" s="2">
-        <v>1951.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E147" s="2">
         <v>9.0</v>
@@ -8433,7 +8427,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>315</v>
+        <v>44</v>
       </c>
       <c r="H147" s="3" t="s">
         <v>477</v>
@@ -8465,10 +8459,10 @@
         <v>9</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>44</v>
+        <v>156</v>
       </c>
       <c r="D148" s="2">
-        <v>2021.0</v>
+        <v>1998.0</v>
       </c>
       <c r="E148" s="2">
         <v>9.0</v>
@@ -8477,10 +8471,10 @@
         <v>36</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>44</v>
+        <v>479</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
@@ -8503,16 +8497,16 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="D149" s="2">
-        <v>1998.0</v>
+        <v>2003.0</v>
       </c>
       <c r="E149" s="2">
         <v>9.0</v>
@@ -8521,7 +8515,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>481</v>
+        <v>239</v>
       </c>
       <c r="H149" s="3" t="s">
         <v>482</v>
@@ -8553,22 +8547,20 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>239</v>
+        <v>10</v>
       </c>
       <c r="D150" s="2">
-        <v>2003.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E150" s="2">
         <v>9.0</v>
       </c>
-      <c r="F150" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F150" s="1"/>
       <c r="G150" s="1" t="s">
-        <v>239</v>
+        <v>484</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
@@ -8591,13 +8583,13 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D151" s="2">
         <v>2021.0</v>
@@ -8605,12 +8597,14 @@
       <c r="E151" s="2">
         <v>9.0</v>
       </c>
-      <c r="F151" s="1"/>
+      <c r="F151" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G151" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
@@ -8633,28 +8627,26 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D152" s="2">
-        <v>2021.0</v>
+        <v>1982.0</v>
       </c>
       <c r="E152" s="2">
         <v>9.0</v>
       </c>
-      <c r="F152" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F152" s="1"/>
       <c r="G152" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
@@ -8677,23 +8669,25 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D153" s="2">
-        <v>1982.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E153" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="F153" s="1"/>
+        <v>8.0</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G153" s="1" t="s">
-        <v>492</v>
+        <v>10</v>
       </c>
       <c r="H153" s="3" t="s">
         <v>493</v>
@@ -8725,10 +8719,10 @@
         <v>9</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>10</v>
+        <v>313</v>
       </c>
       <c r="D154" s="2">
-        <v>1981.0</v>
+        <v>1998.0</v>
       </c>
       <c r="E154" s="2">
         <v>8.0</v>
@@ -8737,7 +8731,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>10</v>
+        <v>313</v>
       </c>
       <c r="H154" s="3" t="s">
         <v>495</v>
@@ -8769,10 +8763,10 @@
         <v>9</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="D155" s="2">
-        <v>1998.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E155" s="2">
         <v>8.0</v>
@@ -8781,7 +8775,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="H155" s="3" t="s">
         <v>497</v>
@@ -8813,10 +8807,10 @@
         <v>9</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>358</v>
+        <v>63</v>
       </c>
       <c r="D156" s="2">
-        <v>2018.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E156" s="2">
         <v>8.0</v>
@@ -8825,7 +8819,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>358</v>
+        <v>63</v>
       </c>
       <c r="H156" s="3" t="s">
         <v>499</v>
@@ -8857,10 +8851,10 @@
         <v>9</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D157" s="2">
-        <v>2017.0</v>
+        <v>2014.0</v>
       </c>
       <c r="E157" s="2">
         <v>8.0</v>
@@ -8869,7 +8863,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="H157" s="3" t="s">
         <v>501</v>
@@ -8901,19 +8895,17 @@
         <v>9</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="D158" s="2">
-        <v>2014.0</v>
+        <v>2024.0</v>
       </c>
       <c r="E158" s="2">
         <v>8.0</v>
       </c>
-      <c r="F158" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F158" s="1"/>
       <c r="G158" s="1" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>503</v>
@@ -8945,17 +8937,17 @@
         <v>9</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="D159" s="2">
-        <v>2024.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E159" s="2">
         <v>8.0</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="H159" s="3" t="s">
         <v>505</v>
@@ -8987,20 +8979,20 @@
         <v>9</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>63</v>
+        <v>507</v>
       </c>
       <c r="D160" s="2">
-        <v>2011.0</v>
+        <v>2014.0</v>
       </c>
       <c r="E160" s="2">
         <v>8.0</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1" t="s">
-        <v>63</v>
+        <v>328</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -9023,24 +9015,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>509</v>
+        <v>446</v>
       </c>
       <c r="D161" s="2">
-        <v>2014.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E161" s="2">
         <v>8.0</v>
       </c>
       <c r="F161" s="1"/>
-      <c r="G161" s="1" t="s">
-        <v>330</v>
-      </c>
+      <c r="G161" s="1"/>
       <c r="H161" s="3" t="s">
         <v>510</v>
       </c>
@@ -9071,16 +9061,20 @@
         <v>9</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>448</v>
+        <v>63</v>
       </c>
       <c r="D162" s="2">
-        <v>2019.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E162" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="F162" s="1"/>
-      <c r="G162" s="1"/>
+        <v>7.0</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="H162" s="3" t="s">
         <v>512</v>
       </c>
@@ -9111,10 +9105,10 @@
         <v>9</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D163" s="2">
-        <v>2012.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E163" s="2">
         <v>7.0</v>
@@ -9123,10 +9117,10 @@
         <v>36</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>63</v>
+        <v>514</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -9149,28 +9143,26 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>44</v>
+        <v>517</v>
       </c>
       <c r="D164" s="2">
-        <v>2016.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E164" s="2">
         <v>7.0</v>
       </c>
-      <c r="F164" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F164" s="1"/>
       <c r="G164" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -9193,26 +9185,28 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>519</v>
+        <v>20</v>
       </c>
       <c r="D165" s="2">
-        <v>2009.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E165" s="2">
         <v>7.0</v>
       </c>
-      <c r="F165" s="1"/>
+      <c r="F165" s="1" t="s">
+        <v>520</v>
+      </c>
       <c r="G165" s="1" t="s">
-        <v>519</v>
+        <v>20</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -9235,25 +9229,25 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D166" s="2">
-        <v>2010.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E166" s="2">
         <v>7.0</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>522</v>
+        <v>36</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H166" s="3" t="s">
         <v>523</v>
@@ -9285,10 +9279,10 @@
         <v>9</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="D167" s="2">
-        <v>2019.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E167" s="2">
         <v>7.0</v>
@@ -9297,7 +9291,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="H167" s="3" t="s">
         <v>525</v>
@@ -9329,19 +9323,17 @@
         <v>9</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="D168" s="2">
-        <v>2016.0</v>
+        <v>2005.0</v>
       </c>
       <c r="E168" s="2">
         <v>7.0</v>
       </c>
-      <c r="F168" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F168" s="1"/>
       <c r="G168" s="1" t="s">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="H168" s="3" t="s">
         <v>527</v>
@@ -9373,17 +9365,17 @@
         <v>9</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="D169" s="2">
-        <v>2005.0</v>
+        <v>1964.0</v>
       </c>
       <c r="E169" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="F169" s="1"/>
       <c r="G169" s="1" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="H169" s="3" t="s">
         <v>529</v>
@@ -9415,17 +9407,19 @@
         <v>9</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="D170" s="2">
-        <v>1964.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E170" s="2">
         <v>6.0</v>
       </c>
-      <c r="F170" s="1"/>
+      <c r="F170" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G170" s="1" t="s">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="H170" s="3" t="s">
         <v>531</v>
@@ -9457,22 +9451,22 @@
         <v>9</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>63</v>
+        <v>434</v>
       </c>
       <c r="D171" s="2">
-        <v>2018.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E171" s="2">
         <v>6.0</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>36</v>
+        <v>533</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>63</v>
+        <v>434</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -9495,13 +9489,13 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>436</v>
+        <v>77</v>
       </c>
       <c r="D172" s="2">
         <v>2010.0</v>
@@ -9510,13 +9504,13 @@
         <v>6.0</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>535</v>
+        <v>36</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>436</v>
+        <v>536</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
@@ -9539,16 +9533,16 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="D173" s="2">
-        <v>2010.0</v>
+        <v>1985.0</v>
       </c>
       <c r="E173" s="2">
         <v>6.0</v>
@@ -9557,7 +9551,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>538</v>
+        <v>141</v>
       </c>
       <c r="H173" s="3" t="s">
         <v>539</v>
@@ -9589,20 +9583,16 @@
         <v>9</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>141</v>
+        <v>507</v>
       </c>
       <c r="D174" s="2">
-        <v>1985.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E174" s="2">
         <v>6.0</v>
       </c>
-      <c r="F174" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>141</v>
-      </c>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1"/>
       <c r="H174" s="3" t="s">
         <v>541</v>
       </c>
@@ -9633,18 +9623,22 @@
         <v>9</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="D175" s="2">
-        <v>2019.0</v>
+        <v>2006.0</v>
       </c>
       <c r="E175" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="F175" s="1"/>
-      <c r="G175" s="1"/>
+        <v>5.0</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>543</v>
+      </c>
       <c r="H175" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
@@ -9667,25 +9661,23 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>545</v>
+        <v>72</v>
       </c>
       <c r="D176" s="2">
-        <v>2006.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E176" s="2">
         <v>5.0</v>
       </c>
-      <c r="F176" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F176" s="1"/>
       <c r="G176" s="1" t="s">
-        <v>545</v>
+        <v>72</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>546</v>
@@ -9717,17 +9709,19 @@
         <v>9</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>72</v>
+        <v>230</v>
       </c>
       <c r="D177" s="2">
-        <v>2016.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E177" s="2">
         <v>5.0</v>
       </c>
-      <c r="F177" s="1"/>
+      <c r="F177" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G177" s="1" t="s">
-        <v>72</v>
+        <v>230</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>548</v>
@@ -9759,10 +9753,10 @@
         <v>9</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="D178" s="2">
-        <v>2018.0</v>
+        <v>1978.0</v>
       </c>
       <c r="E178" s="2">
         <v>5.0</v>
@@ -9771,10 +9765,10 @@
         <v>36</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>230</v>
+        <v>550</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I178" s="1"/>
       <c r="J178" s="1"/>
@@ -9797,25 +9791,23 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D179" s="2">
-        <v>1978.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E179" s="2">
         <v>5.0</v>
       </c>
-      <c r="F179" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F179" s="1"/>
       <c r="G179" s="1" t="s">
-        <v>552</v>
+        <v>63</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>553</v>
@@ -9847,17 +9839,19 @@
         <v>9</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D180" s="2">
-        <v>2019.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E180" s="2">
         <v>5.0</v>
       </c>
-      <c r="F180" s="1"/>
+      <c r="F180" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G180" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>555</v>
@@ -9889,10 +9883,10 @@
         <v>9</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D181" s="2">
-        <v>2021.0</v>
+        <v>2002.0</v>
       </c>
       <c r="E181" s="2">
         <v>5.0</v>
@@ -9901,7 +9895,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="H181" s="3" t="s">
         <v>557</v>
@@ -9933,10 +9927,10 @@
         <v>9</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D182" s="2">
-        <v>2002.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E182" s="2">
         <v>5.0</v>
@@ -9945,7 +9939,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>559</v>
@@ -9977,10 +9971,10 @@
         <v>9</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D183" s="2">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E183" s="2">
         <v>5.0</v>
@@ -9989,10 +9983,10 @@
         <v>36</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>72</v>
+        <v>561</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I183" s="1"/>
       <c r="J183" s="1"/>
@@ -10015,16 +10009,16 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="D184" s="2">
-        <v>2022.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E184" s="2">
         <v>5.0</v>
@@ -10033,10 +10027,10 @@
         <v>36</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I184" s="1"/>
       <c r="J184" s="1"/>
@@ -10059,16 +10053,16 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="D185" s="2">
-        <v>2011.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E185" s="2">
         <v>5.0</v>
@@ -10077,7 +10071,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>566</v>
+        <v>204</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>567</v>
@@ -10109,19 +10103,17 @@
         <v>9</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="D186" s="2">
-        <v>2017.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E186" s="2">
         <v>5.0</v>
       </c>
-      <c r="F186" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F186" s="1"/>
       <c r="G186" s="1" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>569</v>
@@ -10156,7 +10148,7 @@
         <v>63</v>
       </c>
       <c r="D187" s="2">
-        <v>2009.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E187" s="2">
         <v>5.0</v>
@@ -10194,22 +10186,16 @@
       <c r="B188" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D188" s="2">
-        <v>2018.0</v>
-      </c>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
       <c r="E188" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F188" s="1"/>
-      <c r="G188" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H188" s="3" t="s">
-        <v>573</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
       <c r="K188" s="1"/>
@@ -10231,21 +10217,29 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
+      <c r="C189" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D189" s="2">
+        <v>2018.0</v>
+      </c>
       <c r="E189" s="2">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G189" s="1"/>
-      <c r="H189" s="1"/>
+      <c r="G189" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>574</v>
+      </c>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
       <c r="K189" s="1"/>
@@ -10266,30 +10260,14 @@
       <c r="Z189" s="1"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D190" s="2">
-        <v>2018.0</v>
-      </c>
-      <c r="E190" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H190" s="3" t="s">
-        <v>576</v>
-      </c>
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="1"/>
+      <c r="G190" s="1"/>
+      <c r="H190" s="1"/>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
@@ -33053,7 +33031,7 @@
     <hyperlink r:id="rId60" ref="H60"/>
     <hyperlink r:id="rId61" ref="H61"/>
     <hyperlink r:id="rId62" ref="H62"/>
-    <hyperlink r:id="rId63" ref="H63"/>
+    <hyperlink r:id="rId63" ref="H64"/>
     <hyperlink r:id="rId64" ref="H65"/>
     <hyperlink r:id="rId65" ref="H66"/>
     <hyperlink r:id="rId66" ref="H67"/>
@@ -33110,8 +33088,8 @@
     <hyperlink r:id="rId117" ref="H118"/>
     <hyperlink r:id="rId118" ref="H119"/>
     <hyperlink r:id="rId119" ref="H120"/>
-    <hyperlink r:id="rId120" ref="H121"/>
-    <hyperlink r:id="rId121" ref="H122"/>
+    <hyperlink r:id="rId120" ref="H122"/>
+    <hyperlink r:id="rId121" ref="H123"/>
     <hyperlink r:id="rId122" ref="H124"/>
     <hyperlink r:id="rId123" ref="H125"/>
     <hyperlink r:id="rId124" ref="H126"/>
@@ -33176,9 +33154,8 @@
     <hyperlink r:id="rId183" ref="H185"/>
     <hyperlink r:id="rId184" ref="H186"/>
     <hyperlink r:id="rId185" ref="H187"/>
-    <hyperlink r:id="rId186" ref="H188"/>
-    <hyperlink r:id="rId187" ref="H190"/>
+    <hyperlink r:id="rId186" ref="H189"/>
   </hyperlinks>
-  <drawing r:id="rId188"/>
+  <drawing r:id="rId187"/>
 </worksheet>
 </file>